--- a/sheet-template/IIS-website-content.xlsx
+++ b/sheet-template/IIS-website-content.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Media" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Press" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Undergrads" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -483,92 +484,126 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>You reached it from the "Lab members: edit this site" link at the bottom of the website. Please do not share the password or this link outside the group.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Tabs: People, Projects, Papers, Media, Press. One row per item. Do not rename the tabs or the column headings.</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Tabs: People, Projects, Papers, Media, Press, Undergrads. One row per item. Do not rename the tabs or the column headings.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>PHOTOS: paste a link to your photo in the "photo" column of the People tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Google Drive: upload the photo, Share &gt; General access &gt; "Anyone with the link", then Copy link and paste it.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  - Google Drive: upload the photo, Share &gt; General access &gt; "Anyone with the link", then Copy link and paste it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  - Or any public https:// image address (jpg, png or webp, under 8 MB). Square crops look best.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-    </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>LINKING: people, projects and areas are matched by NAME. Spell them exactly as they appear in their own tab. Separate several with a semicolon ( ; ).</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>LINKING: people, projects and areas are matched by NAME. Spell them exactly as they appear in their own tab. Separate several with a semicolon ( ; ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>A paper appears on a project page and on its authors' pages when you put the project title in "projects" and the names in "people".</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Do not change the "id" column: it forms the page address. Leave it empty for new rows.</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>To hide a row without deleting it, set "visible" to FALSE.</t>
+          <t>Do not change the "id" column: it forms the page address. Leave it empty for new rows.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Web addresses must start with https://</t>
+          <t>To hide a row without deleting it, set "visible" to FALSE.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>If a row has a mistake, the website keeps showing the last good version and the administrator is emailed what to fix.</t>
+          <t>Web addresses must start with https://</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>If a row has a mistake, the website keeps showing the last good version and the administrator is emailed what to fix. File &gt; Version history can undo any edit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>ORCID: put your ORCID iD in the "orcid" column of the People tab (it looks like 0000-0002-1825-0097). New papers on your ORCID record are added to the website automatically every week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>To correct an automatic paper, add a row for it in the Papers tab with the same link; your row wins. To remove one, add that row and set "visible" to FALSE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>UNDERGRADUATE ALUMNI: one row per person in the Undergrads tab: name, year (and an optional note). They appear in a pop-up under People &gt; Alumni.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Research areas (use these names in the "areas" column): Intelligent systems; HCI; Accessibility &amp; AAC; Crowdsourcing; Interaction science</t>
         </is>
@@ -585,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R300"/>
+  <dimension ref="A1:T300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -597,15 +632,17 @@
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -656,45 +693,55 @@
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>joined</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
           <t>photo</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>now</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>advisor</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>chia</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>featured</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>contact</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>visible</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -746,23 +793,25 @@
       <c r="K2" s="5" t="inlineStr"/>
       <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="Q2" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="R2" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr"/>
-      <c r="R2" s="7" t="inlineStr">
+      <c r="S2" s="5" t="inlineStr"/>
+      <c r="T2" s="7" t="inlineStr">
         <is>
           <t>pok</t>
         </is>
@@ -810,7 +859,9 @@
       <c r="O3" s="5" t="inlineStr"/>
       <c r="P3" s="5" t="inlineStr"/>
       <c r="Q3" s="5" t="inlineStr"/>
-      <c r="R3" s="7" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="7" t="inlineStr">
         <is>
           <t>ff</t>
         </is>
@@ -849,16 +900,18 @@
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>Per Ola Kristensson</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="7" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="7" t="inlineStr">
         <is>
           <t>jl</t>
         </is>
@@ -906,7 +959,9 @@
       <c r="O5" s="5" t="inlineStr"/>
       <c r="P5" s="5" t="inlineStr"/>
       <c r="Q5" s="5" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr">
+      <c r="R5" s="5" t="inlineStr"/>
+      <c r="S5" s="5" t="inlineStr"/>
+      <c r="T5" s="7" t="inlineStr">
         <is>
           <t>jc</t>
         </is>
@@ -954,7 +1009,9 @@
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="7" t="inlineStr">
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="7" t="inlineStr">
         <is>
           <t>ch</t>
         </is>
@@ -1002,7 +1059,9 @@
       <c r="O7" s="5" t="inlineStr"/>
       <c r="P7" s="5" t="inlineStr"/>
       <c r="Q7" s="5" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="7" t="inlineStr">
         <is>
           <t>ah</t>
         </is>
@@ -1050,7 +1109,9 @@
       <c r="O8" s="5" t="inlineStr"/>
       <c r="P8" s="5" t="inlineStr"/>
       <c r="Q8" s="5" t="inlineStr"/>
-      <c r="R8" s="7" t="inlineStr">
+      <c r="R8" s="5" t="inlineStr"/>
+      <c r="S8" s="5" t="inlineStr"/>
+      <c r="T8" s="7" t="inlineStr">
         <is>
           <t>zl</t>
         </is>
@@ -1098,7 +1159,9 @@
       <c r="O9" s="5" t="inlineStr"/>
       <c r="P9" s="5" t="inlineStr"/>
       <c r="Q9" s="5" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr">
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr"/>
+      <c r="T9" s="7" t="inlineStr">
         <is>
           <t>ab</t>
         </is>
@@ -1146,7 +1209,9 @@
       <c r="O10" s="5" t="inlineStr"/>
       <c r="P10" s="5" t="inlineStr"/>
       <c r="Q10" s="5" t="inlineStr"/>
-      <c r="R10" s="7" t="inlineStr">
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="5" t="inlineStr"/>
+      <c r="T10" s="7" t="inlineStr">
         <is>
           <t>bs</t>
         </is>
@@ -1186,15 +1251,17 @@
       <c r="K11" s="5" t="inlineStr"/>
       <c r="L11" s="5" t="inlineStr"/>
       <c r="M11" s="5" t="inlineStr"/>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="O11" s="5" t="inlineStr"/>
-      <c r="P11" s="5" t="inlineStr"/>
       <c r="Q11" s="5" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr">
+      <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr"/>
+      <c r="T11" s="7" t="inlineStr">
         <is>
           <t>is</t>
         </is>
@@ -1234,15 +1301,17 @@
       <c r="K12" s="5" t="inlineStr"/>
       <c r="L12" s="5" t="inlineStr"/>
       <c r="M12" s="5" t="inlineStr"/>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="O12" s="5" t="inlineStr"/>
-      <c r="P12" s="5" t="inlineStr"/>
       <c r="Q12" s="5" t="inlineStr"/>
-      <c r="R12" s="7" t="inlineStr">
+      <c r="R12" s="5" t="inlineStr"/>
+      <c r="S12" s="5" t="inlineStr"/>
+      <c r="T12" s="7" t="inlineStr">
         <is>
           <t>ss</t>
         </is>
@@ -1282,15 +1351,17 @@
       <c r="K13" s="5" t="inlineStr"/>
       <c r="L13" s="5" t="inlineStr"/>
       <c r="M13" s="5" t="inlineStr"/>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="O13" s="5" t="inlineStr"/>
-      <c r="P13" s="5" t="inlineStr"/>
       <c r="Q13" s="5" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr">
+      <c r="R13" s="5" t="inlineStr"/>
+      <c r="S13" s="5" t="inlineStr"/>
+      <c r="T13" s="7" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
@@ -1330,15 +1401,17 @@
       <c r="K14" s="5" t="inlineStr"/>
       <c r="L14" s="5" t="inlineStr"/>
       <c r="M14" s="5" t="inlineStr"/>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="O14" s="5" t="inlineStr"/>
-      <c r="P14" s="5" t="inlineStr"/>
       <c r="Q14" s="5" t="inlineStr"/>
-      <c r="R14" s="7" t="inlineStr">
+      <c r="R14" s="5" t="inlineStr"/>
+      <c r="S14" s="5" t="inlineStr"/>
+      <c r="T14" s="7" t="inlineStr">
         <is>
           <t>oa</t>
         </is>
@@ -1377,16 +1450,18 @@
       <c r="J15" s="5" t="inlineStr"/>
       <c r="K15" s="5" t="inlineStr"/>
       <c r="L15" s="5" t="inlineStr"/>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr">
         <is>
           <t>John Dudley</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr"/>
-      <c r="O15" s="5" t="inlineStr"/>
       <c r="P15" s="5" t="inlineStr"/>
       <c r="Q15" s="5" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr">
+      <c r="R15" s="5" t="inlineStr"/>
+      <c r="S15" s="5" t="inlineStr"/>
+      <c r="T15" s="7" t="inlineStr">
         <is>
           <t>jdo</t>
         </is>
@@ -1435,18 +1510,20 @@
       <c r="L16" s="5" t="inlineStr"/>
       <c r="M16" s="5" t="inlineStr"/>
       <c r="N16" s="5" t="inlineStr"/>
-      <c r="O16" s="5" t="inlineStr">
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="P16" s="5" t="inlineStr">
+      <c r="R16" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Q16" s="5" t="inlineStr"/>
-      <c r="R16" s="7" t="inlineStr">
+      <c r="S16" s="5" t="inlineStr"/>
+      <c r="T16" s="7" t="inlineStr">
         <is>
           <t>jd</t>
         </is>
@@ -1470,7 +1547,9 @@
       <c r="O17" s="5" t="n"/>
       <c r="P17" s="5" t="n"/>
       <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="7" t="n"/>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="5" t="n"/>
+      <c r="T17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -1490,7 +1569,9 @@
       <c r="O18" s="5" t="n"/>
       <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="7" t="n"/>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -1510,7 +1591,9 @@
       <c r="O19" s="5" t="n"/>
       <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="7" t="n"/>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="5" t="n"/>
+      <c r="T19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -1530,7 +1613,9 @@
       <c r="O20" s="5" t="n"/>
       <c r="P20" s="5" t="n"/>
       <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="7" t="n"/>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n"/>
+      <c r="T20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -1550,7 +1635,9 @@
       <c r="O21" s="5" t="n"/>
       <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="7" t="n"/>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -1570,7 +1657,9 @@
       <c r="O22" s="5" t="n"/>
       <c r="P22" s="5" t="n"/>
       <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="7" t="n"/>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="5" t="n"/>
+      <c r="T22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -1590,7 +1679,9 @@
       <c r="O23" s="5" t="n"/>
       <c r="P23" s="5" t="n"/>
       <c r="Q23" s="5" t="n"/>
-      <c r="R23" s="7" t="n"/>
+      <c r="R23" s="5" t="n"/>
+      <c r="S23" s="5" t="n"/>
+      <c r="T23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -1610,7 +1701,9 @@
       <c r="O24" s="5" t="n"/>
       <c r="P24" s="5" t="n"/>
       <c r="Q24" s="5" t="n"/>
-      <c r="R24" s="7" t="n"/>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" s="5" t="n"/>
+      <c r="T24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -1630,7 +1723,9 @@
       <c r="O25" s="5" t="n"/>
       <c r="P25" s="5" t="n"/>
       <c r="Q25" s="5" t="n"/>
-      <c r="R25" s="7" t="n"/>
+      <c r="R25" s="5" t="n"/>
+      <c r="S25" s="5" t="n"/>
+      <c r="T25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
@@ -1650,7 +1745,9 @@
       <c r="O26" s="5" t="n"/>
       <c r="P26" s="5" t="n"/>
       <c r="Q26" s="5" t="n"/>
-      <c r="R26" s="7" t="n"/>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" s="5" t="n"/>
+      <c r="T26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -1670,7 +1767,9 @@
       <c r="O27" s="5" t="n"/>
       <c r="P27" s="5" t="n"/>
       <c r="Q27" s="5" t="n"/>
-      <c r="R27" s="7" t="n"/>
+      <c r="R27" s="5" t="n"/>
+      <c r="S27" s="5" t="n"/>
+      <c r="T27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -1690,7 +1789,9 @@
       <c r="O28" s="5" t="n"/>
       <c r="P28" s="5" t="n"/>
       <c r="Q28" s="5" t="n"/>
-      <c r="R28" s="7" t="n"/>
+      <c r="R28" s="5" t="n"/>
+      <c r="S28" s="5" t="n"/>
+      <c r="T28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -1710,7 +1811,9 @@
       <c r="O29" s="5" t="n"/>
       <c r="P29" s="5" t="n"/>
       <c r="Q29" s="5" t="n"/>
-      <c r="R29" s="7" t="n"/>
+      <c r="R29" s="5" t="n"/>
+      <c r="S29" s="5" t="n"/>
+      <c r="T29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -1730,7 +1833,9 @@
       <c r="O30" s="5" t="n"/>
       <c r="P30" s="5" t="n"/>
       <c r="Q30" s="5" t="n"/>
-      <c r="R30" s="7" t="n"/>
+      <c r="R30" s="5" t="n"/>
+      <c r="S30" s="5" t="n"/>
+      <c r="T30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -1750,7 +1855,9 @@
       <c r="O31" s="5" t="n"/>
       <c r="P31" s="5" t="n"/>
       <c r="Q31" s="5" t="n"/>
-      <c r="R31" s="7" t="n"/>
+      <c r="R31" s="5" t="n"/>
+      <c r="S31" s="5" t="n"/>
+      <c r="T31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -1770,7 +1877,9 @@
       <c r="O32" s="5" t="n"/>
       <c r="P32" s="5" t="n"/>
       <c r="Q32" s="5" t="n"/>
-      <c r="R32" s="7" t="n"/>
+      <c r="R32" s="5" t="n"/>
+      <c r="S32" s="5" t="n"/>
+      <c r="T32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
@@ -1790,7 +1899,9 @@
       <c r="O33" s="5" t="n"/>
       <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="n"/>
-      <c r="R33" s="7" t="n"/>
+      <c r="R33" s="5" t="n"/>
+      <c r="S33" s="5" t="n"/>
+      <c r="T33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -1810,7 +1921,9 @@
       <c r="O34" s="5" t="n"/>
       <c r="P34" s="5" t="n"/>
       <c r="Q34" s="5" t="n"/>
-      <c r="R34" s="7" t="n"/>
+      <c r="R34" s="5" t="n"/>
+      <c r="S34" s="5" t="n"/>
+      <c r="T34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -1830,7 +1943,9 @@
       <c r="O35" s="5" t="n"/>
       <c r="P35" s="5" t="n"/>
       <c r="Q35" s="5" t="n"/>
-      <c r="R35" s="7" t="n"/>
+      <c r="R35" s="5" t="n"/>
+      <c r="S35" s="5" t="n"/>
+      <c r="T35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -1850,7 +1965,9 @@
       <c r="O36" s="5" t="n"/>
       <c r="P36" s="5" t="n"/>
       <c r="Q36" s="5" t="n"/>
-      <c r="R36" s="7" t="n"/>
+      <c r="R36" s="5" t="n"/>
+      <c r="S36" s="5" t="n"/>
+      <c r="T36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -1870,7 +1987,9 @@
       <c r="O37" s="5" t="n"/>
       <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="n"/>
-      <c r="R37" s="7" t="n"/>
+      <c r="R37" s="5" t="n"/>
+      <c r="S37" s="5" t="n"/>
+      <c r="T37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -1890,7 +2009,9 @@
       <c r="O38" s="5" t="n"/>
       <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5" t="n"/>
-      <c r="R38" s="7" t="n"/>
+      <c r="R38" s="5" t="n"/>
+      <c r="S38" s="5" t="n"/>
+      <c r="T38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -1910,7 +2031,9 @@
       <c r="O39" s="5" t="n"/>
       <c r="P39" s="5" t="n"/>
       <c r="Q39" s="5" t="n"/>
-      <c r="R39" s="7" t="n"/>
+      <c r="R39" s="5" t="n"/>
+      <c r="S39" s="5" t="n"/>
+      <c r="T39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -1930,7 +2053,9 @@
       <c r="O40" s="5" t="n"/>
       <c r="P40" s="5" t="n"/>
       <c r="Q40" s="5" t="n"/>
-      <c r="R40" s="7" t="n"/>
+      <c r="R40" s="5" t="n"/>
+      <c r="S40" s="5" t="n"/>
+      <c r="T40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -1950,7 +2075,9 @@
       <c r="O41" s="5" t="n"/>
       <c r="P41" s="5" t="n"/>
       <c r="Q41" s="5" t="n"/>
-      <c r="R41" s="7" t="n"/>
+      <c r="R41" s="5" t="n"/>
+      <c r="S41" s="5" t="n"/>
+      <c r="T41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -1970,7 +2097,9 @@
       <c r="O42" s="5" t="n"/>
       <c r="P42" s="5" t="n"/>
       <c r="Q42" s="5" t="n"/>
-      <c r="R42" s="7" t="n"/>
+      <c r="R42" s="5" t="n"/>
+      <c r="S42" s="5" t="n"/>
+      <c r="T42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -1990,7 +2119,9 @@
       <c r="O43" s="5" t="n"/>
       <c r="P43" s="5" t="n"/>
       <c r="Q43" s="5" t="n"/>
-      <c r="R43" s="7" t="n"/>
+      <c r="R43" s="5" t="n"/>
+      <c r="S43" s="5" t="n"/>
+      <c r="T43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -2010,7 +2141,9 @@
       <c r="O44" s="5" t="n"/>
       <c r="P44" s="5" t="n"/>
       <c r="Q44" s="5" t="n"/>
-      <c r="R44" s="7" t="n"/>
+      <c r="R44" s="5" t="n"/>
+      <c r="S44" s="5" t="n"/>
+      <c r="T44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
@@ -2030,7 +2163,9 @@
       <c r="O45" s="5" t="n"/>
       <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5" t="n"/>
-      <c r="R45" s="7" t="n"/>
+      <c r="R45" s="5" t="n"/>
+      <c r="S45" s="5" t="n"/>
+      <c r="T45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -2050,7 +2185,9 @@
       <c r="O46" s="5" t="n"/>
       <c r="P46" s="5" t="n"/>
       <c r="Q46" s="5" t="n"/>
-      <c r="R46" s="7" t="n"/>
+      <c r="R46" s="5" t="n"/>
+      <c r="S46" s="5" t="n"/>
+      <c r="T46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -2070,7 +2207,9 @@
       <c r="O47" s="5" t="n"/>
       <c r="P47" s="5" t="n"/>
       <c r="Q47" s="5" t="n"/>
-      <c r="R47" s="7" t="n"/>
+      <c r="R47" s="5" t="n"/>
+      <c r="S47" s="5" t="n"/>
+      <c r="T47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -2090,7 +2229,9 @@
       <c r="O48" s="5" t="n"/>
       <c r="P48" s="5" t="n"/>
       <c r="Q48" s="5" t="n"/>
-      <c r="R48" s="7" t="n"/>
+      <c r="R48" s="5" t="n"/>
+      <c r="S48" s="5" t="n"/>
+      <c r="T48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -2110,7 +2251,9 @@
       <c r="O49" s="5" t="n"/>
       <c r="P49" s="5" t="n"/>
       <c r="Q49" s="5" t="n"/>
-      <c r="R49" s="7" t="n"/>
+      <c r="R49" s="5" t="n"/>
+      <c r="S49" s="5" t="n"/>
+      <c r="T49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -2130,7 +2273,9 @@
       <c r="O50" s="5" t="n"/>
       <c r="P50" s="5" t="n"/>
       <c r="Q50" s="5" t="n"/>
-      <c r="R50" s="7" t="n"/>
+      <c r="R50" s="5" t="n"/>
+      <c r="S50" s="5" t="n"/>
+      <c r="T50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -2150,7 +2295,9 @@
       <c r="O51" s="5" t="n"/>
       <c r="P51" s="5" t="n"/>
       <c r="Q51" s="5" t="n"/>
-      <c r="R51" s="7" t="n"/>
+      <c r="R51" s="5" t="n"/>
+      <c r="S51" s="5" t="n"/>
+      <c r="T51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
@@ -2170,7 +2317,9 @@
       <c r="O52" s="5" t="n"/>
       <c r="P52" s="5" t="n"/>
       <c r="Q52" s="5" t="n"/>
-      <c r="R52" s="7" t="n"/>
+      <c r="R52" s="5" t="n"/>
+      <c r="S52" s="5" t="n"/>
+      <c r="T52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
@@ -2190,7 +2339,9 @@
       <c r="O53" s="5" t="n"/>
       <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5" t="n"/>
-      <c r="R53" s="7" t="n"/>
+      <c r="R53" s="5" t="n"/>
+      <c r="S53" s="5" t="n"/>
+      <c r="T53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -2210,7 +2361,9 @@
       <c r="O54" s="5" t="n"/>
       <c r="P54" s="5" t="n"/>
       <c r="Q54" s="5" t="n"/>
-      <c r="R54" s="7" t="n"/>
+      <c r="R54" s="5" t="n"/>
+      <c r="S54" s="5" t="n"/>
+      <c r="T54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -2230,7 +2383,9 @@
       <c r="O55" s="5" t="n"/>
       <c r="P55" s="5" t="n"/>
       <c r="Q55" s="5" t="n"/>
-      <c r="R55" s="7" t="n"/>
+      <c r="R55" s="5" t="n"/>
+      <c r="S55" s="5" t="n"/>
+      <c r="T55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
@@ -2250,7 +2405,9 @@
       <c r="O56" s="5" t="n"/>
       <c r="P56" s="5" t="n"/>
       <c r="Q56" s="5" t="n"/>
-      <c r="R56" s="7" t="n"/>
+      <c r="R56" s="5" t="n"/>
+      <c r="S56" s="5" t="n"/>
+      <c r="T56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
@@ -2270,7 +2427,9 @@
       <c r="O57" s="5" t="n"/>
       <c r="P57" s="5" t="n"/>
       <c r="Q57" s="5" t="n"/>
-      <c r="R57" s="7" t="n"/>
+      <c r="R57" s="5" t="n"/>
+      <c r="S57" s="5" t="n"/>
+      <c r="T57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -2290,7 +2449,9 @@
       <c r="O58" s="5" t="n"/>
       <c r="P58" s="5" t="n"/>
       <c r="Q58" s="5" t="n"/>
-      <c r="R58" s="7" t="n"/>
+      <c r="R58" s="5" t="n"/>
+      <c r="S58" s="5" t="n"/>
+      <c r="T58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -2310,7 +2471,9 @@
       <c r="O59" s="5" t="n"/>
       <c r="P59" s="5" t="n"/>
       <c r="Q59" s="5" t="n"/>
-      <c r="R59" s="7" t="n"/>
+      <c r="R59" s="5" t="n"/>
+      <c r="S59" s="5" t="n"/>
+      <c r="T59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n"/>
@@ -2330,7 +2493,9 @@
       <c r="O60" s="5" t="n"/>
       <c r="P60" s="5" t="n"/>
       <c r="Q60" s="5" t="n"/>
-      <c r="R60" s="7" t="n"/>
+      <c r="R60" s="5" t="n"/>
+      <c r="S60" s="5" t="n"/>
+      <c r="T60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n"/>
@@ -2350,7 +2515,9 @@
       <c r="O61" s="5" t="n"/>
       <c r="P61" s="5" t="n"/>
       <c r="Q61" s="5" t="n"/>
-      <c r="R61" s="7" t="n"/>
+      <c r="R61" s="5" t="n"/>
+      <c r="S61" s="5" t="n"/>
+      <c r="T61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -2370,7 +2537,9 @@
       <c r="O62" s="5" t="n"/>
       <c r="P62" s="5" t="n"/>
       <c r="Q62" s="5" t="n"/>
-      <c r="R62" s="7" t="n"/>
+      <c r="R62" s="5" t="n"/>
+      <c r="S62" s="5" t="n"/>
+      <c r="T62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -2390,7 +2559,9 @@
       <c r="O63" s="5" t="n"/>
       <c r="P63" s="5" t="n"/>
       <c r="Q63" s="5" t="n"/>
-      <c r="R63" s="7" t="n"/>
+      <c r="R63" s="5" t="n"/>
+      <c r="S63" s="5" t="n"/>
+      <c r="T63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
@@ -2410,7 +2581,9 @@
       <c r="O64" s="5" t="n"/>
       <c r="P64" s="5" t="n"/>
       <c r="Q64" s="5" t="n"/>
-      <c r="R64" s="7" t="n"/>
+      <c r="R64" s="5" t="n"/>
+      <c r="S64" s="5" t="n"/>
+      <c r="T64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>
@@ -2430,7 +2603,9 @@
       <c r="O65" s="5" t="n"/>
       <c r="P65" s="5" t="n"/>
       <c r="Q65" s="5" t="n"/>
-      <c r="R65" s="7" t="n"/>
+      <c r="R65" s="5" t="n"/>
+      <c r="S65" s="5" t="n"/>
+      <c r="T65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -2450,7 +2625,9 @@
       <c r="O66" s="5" t="n"/>
       <c r="P66" s="5" t="n"/>
       <c r="Q66" s="5" t="n"/>
-      <c r="R66" s="7" t="n"/>
+      <c r="R66" s="5" t="n"/>
+      <c r="S66" s="5" t="n"/>
+      <c r="T66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -2470,7 +2647,9 @@
       <c r="O67" s="5" t="n"/>
       <c r="P67" s="5" t="n"/>
       <c r="Q67" s="5" t="n"/>
-      <c r="R67" s="7" t="n"/>
+      <c r="R67" s="5" t="n"/>
+      <c r="S67" s="5" t="n"/>
+      <c r="T67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n"/>
@@ -2490,7 +2669,9 @@
       <c r="O68" s="5" t="n"/>
       <c r="P68" s="5" t="n"/>
       <c r="Q68" s="5" t="n"/>
-      <c r="R68" s="7" t="n"/>
+      <c r="R68" s="5" t="n"/>
+      <c r="S68" s="5" t="n"/>
+      <c r="T68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n"/>
@@ -2510,7 +2691,9 @@
       <c r="O69" s="5" t="n"/>
       <c r="P69" s="5" t="n"/>
       <c r="Q69" s="5" t="n"/>
-      <c r="R69" s="7" t="n"/>
+      <c r="R69" s="5" t="n"/>
+      <c r="S69" s="5" t="n"/>
+      <c r="T69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -2530,7 +2713,9 @@
       <c r="O70" s="5" t="n"/>
       <c r="P70" s="5" t="n"/>
       <c r="Q70" s="5" t="n"/>
-      <c r="R70" s="7" t="n"/>
+      <c r="R70" s="5" t="n"/>
+      <c r="S70" s="5" t="n"/>
+      <c r="T70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -2550,7 +2735,9 @@
       <c r="O71" s="5" t="n"/>
       <c r="P71" s="5" t="n"/>
       <c r="Q71" s="5" t="n"/>
-      <c r="R71" s="7" t="n"/>
+      <c r="R71" s="5" t="n"/>
+      <c r="S71" s="5" t="n"/>
+      <c r="T71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n"/>
@@ -2570,7 +2757,9 @@
       <c r="O72" s="5" t="n"/>
       <c r="P72" s="5" t="n"/>
       <c r="Q72" s="5" t="n"/>
-      <c r="R72" s="7" t="n"/>
+      <c r="R72" s="5" t="n"/>
+      <c r="S72" s="5" t="n"/>
+      <c r="T72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n"/>
@@ -2590,7 +2779,9 @@
       <c r="O73" s="5" t="n"/>
       <c r="P73" s="5" t="n"/>
       <c r="Q73" s="5" t="n"/>
-      <c r="R73" s="7" t="n"/>
+      <c r="R73" s="5" t="n"/>
+      <c r="S73" s="5" t="n"/>
+      <c r="T73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -2610,7 +2801,9 @@
       <c r="O74" s="5" t="n"/>
       <c r="P74" s="5" t="n"/>
       <c r="Q74" s="5" t="n"/>
-      <c r="R74" s="7" t="n"/>
+      <c r="R74" s="5" t="n"/>
+      <c r="S74" s="5" t="n"/>
+      <c r="T74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -2630,7 +2823,9 @@
       <c r="O75" s="5" t="n"/>
       <c r="P75" s="5" t="n"/>
       <c r="Q75" s="5" t="n"/>
-      <c r="R75" s="7" t="n"/>
+      <c r="R75" s="5" t="n"/>
+      <c r="S75" s="5" t="n"/>
+      <c r="T75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n"/>
@@ -2650,7 +2845,9 @@
       <c r="O76" s="5" t="n"/>
       <c r="P76" s="5" t="n"/>
       <c r="Q76" s="5" t="n"/>
-      <c r="R76" s="7" t="n"/>
+      <c r="R76" s="5" t="n"/>
+      <c r="S76" s="5" t="n"/>
+      <c r="T76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n"/>
@@ -2670,7 +2867,9 @@
       <c r="O77" s="5" t="n"/>
       <c r="P77" s="5" t="n"/>
       <c r="Q77" s="5" t="n"/>
-      <c r="R77" s="7" t="n"/>
+      <c r="R77" s="5" t="n"/>
+      <c r="S77" s="5" t="n"/>
+      <c r="T77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -2690,7 +2889,9 @@
       <c r="O78" s="5" t="n"/>
       <c r="P78" s="5" t="n"/>
       <c r="Q78" s="5" t="n"/>
-      <c r="R78" s="7" t="n"/>
+      <c r="R78" s="5" t="n"/>
+      <c r="S78" s="5" t="n"/>
+      <c r="T78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -2710,7 +2911,9 @@
       <c r="O79" s="5" t="n"/>
       <c r="P79" s="5" t="n"/>
       <c r="Q79" s="5" t="n"/>
-      <c r="R79" s="7" t="n"/>
+      <c r="R79" s="5" t="n"/>
+      <c r="S79" s="5" t="n"/>
+      <c r="T79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n"/>
@@ -2730,7 +2933,9 @@
       <c r="O80" s="5" t="n"/>
       <c r="P80" s="5" t="n"/>
       <c r="Q80" s="5" t="n"/>
-      <c r="R80" s="7" t="n"/>
+      <c r="R80" s="5" t="n"/>
+      <c r="S80" s="5" t="n"/>
+      <c r="T80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n"/>
@@ -2750,7 +2955,9 @@
       <c r="O81" s="5" t="n"/>
       <c r="P81" s="5" t="n"/>
       <c r="Q81" s="5" t="n"/>
-      <c r="R81" s="7" t="n"/>
+      <c r="R81" s="5" t="n"/>
+      <c r="S81" s="5" t="n"/>
+      <c r="T81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -2770,7 +2977,9 @@
       <c r="O82" s="5" t="n"/>
       <c r="P82" s="5" t="n"/>
       <c r="Q82" s="5" t="n"/>
-      <c r="R82" s="7" t="n"/>
+      <c r="R82" s="5" t="n"/>
+      <c r="S82" s="5" t="n"/>
+      <c r="T82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -2790,7 +2999,9 @@
       <c r="O83" s="5" t="n"/>
       <c r="P83" s="5" t="n"/>
       <c r="Q83" s="5" t="n"/>
-      <c r="R83" s="7" t="n"/>
+      <c r="R83" s="5" t="n"/>
+      <c r="S83" s="5" t="n"/>
+      <c r="T83" s="7" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n"/>
@@ -2810,7 +3021,9 @@
       <c r="O84" s="5" t="n"/>
       <c r="P84" s="5" t="n"/>
       <c r="Q84" s="5" t="n"/>
-      <c r="R84" s="7" t="n"/>
+      <c r="R84" s="5" t="n"/>
+      <c r="S84" s="5" t="n"/>
+      <c r="T84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n"/>
@@ -2830,7 +3043,9 @@
       <c r="O85" s="5" t="n"/>
       <c r="P85" s="5" t="n"/>
       <c r="Q85" s="5" t="n"/>
-      <c r="R85" s="7" t="n"/>
+      <c r="R85" s="5" t="n"/>
+      <c r="S85" s="5" t="n"/>
+      <c r="T85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n"/>
@@ -2850,7 +3065,9 @@
       <c r="O86" s="5" t="n"/>
       <c r="P86" s="5" t="n"/>
       <c r="Q86" s="5" t="n"/>
-      <c r="R86" s="7" t="n"/>
+      <c r="R86" s="5" t="n"/>
+      <c r="S86" s="5" t="n"/>
+      <c r="T86" s="7" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n"/>
@@ -2870,7 +3087,9 @@
       <c r="O87" s="5" t="n"/>
       <c r="P87" s="5" t="n"/>
       <c r="Q87" s="5" t="n"/>
-      <c r="R87" s="7" t="n"/>
+      <c r="R87" s="5" t="n"/>
+      <c r="S87" s="5" t="n"/>
+      <c r="T87" s="7" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n"/>
@@ -2890,7 +3109,9 @@
       <c r="O88" s="5" t="n"/>
       <c r="P88" s="5" t="n"/>
       <c r="Q88" s="5" t="n"/>
-      <c r="R88" s="7" t="n"/>
+      <c r="R88" s="5" t="n"/>
+      <c r="S88" s="5" t="n"/>
+      <c r="T88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n"/>
@@ -2910,7 +3131,9 @@
       <c r="O89" s="5" t="n"/>
       <c r="P89" s="5" t="n"/>
       <c r="Q89" s="5" t="n"/>
-      <c r="R89" s="7" t="n"/>
+      <c r="R89" s="5" t="n"/>
+      <c r="S89" s="5" t="n"/>
+      <c r="T89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n"/>
@@ -2930,7 +3153,9 @@
       <c r="O90" s="5" t="n"/>
       <c r="P90" s="5" t="n"/>
       <c r="Q90" s="5" t="n"/>
-      <c r="R90" s="7" t="n"/>
+      <c r="R90" s="5" t="n"/>
+      <c r="S90" s="5" t="n"/>
+      <c r="T90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n"/>
@@ -2950,7 +3175,9 @@
       <c r="O91" s="5" t="n"/>
       <c r="P91" s="5" t="n"/>
       <c r="Q91" s="5" t="n"/>
-      <c r="R91" s="7" t="n"/>
+      <c r="R91" s="5" t="n"/>
+      <c r="S91" s="5" t="n"/>
+      <c r="T91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n"/>
@@ -2970,7 +3197,9 @@
       <c r="O92" s="5" t="n"/>
       <c r="P92" s="5" t="n"/>
       <c r="Q92" s="5" t="n"/>
-      <c r="R92" s="7" t="n"/>
+      <c r="R92" s="5" t="n"/>
+      <c r="S92" s="5" t="n"/>
+      <c r="T92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n"/>
@@ -2990,7 +3219,9 @@
       <c r="O93" s="5" t="n"/>
       <c r="P93" s="5" t="n"/>
       <c r="Q93" s="5" t="n"/>
-      <c r="R93" s="7" t="n"/>
+      <c r="R93" s="5" t="n"/>
+      <c r="S93" s="5" t="n"/>
+      <c r="T93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n"/>
@@ -3010,7 +3241,9 @@
       <c r="O94" s="5" t="n"/>
       <c r="P94" s="5" t="n"/>
       <c r="Q94" s="5" t="n"/>
-      <c r="R94" s="7" t="n"/>
+      <c r="R94" s="5" t="n"/>
+      <c r="S94" s="5" t="n"/>
+      <c r="T94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n"/>
@@ -3030,7 +3263,9 @@
       <c r="O95" s="5" t="n"/>
       <c r="P95" s="5" t="n"/>
       <c r="Q95" s="5" t="n"/>
-      <c r="R95" s="7" t="n"/>
+      <c r="R95" s="5" t="n"/>
+      <c r="S95" s="5" t="n"/>
+      <c r="T95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n"/>
@@ -3050,7 +3285,9 @@
       <c r="O96" s="5" t="n"/>
       <c r="P96" s="5" t="n"/>
       <c r="Q96" s="5" t="n"/>
-      <c r="R96" s="7" t="n"/>
+      <c r="R96" s="5" t="n"/>
+      <c r="S96" s="5" t="n"/>
+      <c r="T96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n"/>
@@ -3070,7 +3307,9 @@
       <c r="O97" s="5" t="n"/>
       <c r="P97" s="5" t="n"/>
       <c r="Q97" s="5" t="n"/>
-      <c r="R97" s="7" t="n"/>
+      <c r="R97" s="5" t="n"/>
+      <c r="S97" s="5" t="n"/>
+      <c r="T97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n"/>
@@ -3090,7 +3329,9 @@
       <c r="O98" s="5" t="n"/>
       <c r="P98" s="5" t="n"/>
       <c r="Q98" s="5" t="n"/>
-      <c r="R98" s="7" t="n"/>
+      <c r="R98" s="5" t="n"/>
+      <c r="S98" s="5" t="n"/>
+      <c r="T98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n"/>
@@ -3110,7 +3351,9 @@
       <c r="O99" s="5" t="n"/>
       <c r="P99" s="5" t="n"/>
       <c r="Q99" s="5" t="n"/>
-      <c r="R99" s="7" t="n"/>
+      <c r="R99" s="5" t="n"/>
+      <c r="S99" s="5" t="n"/>
+      <c r="T99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n"/>
@@ -3130,7 +3373,9 @@
       <c r="O100" s="5" t="n"/>
       <c r="P100" s="5" t="n"/>
       <c r="Q100" s="5" t="n"/>
-      <c r="R100" s="7" t="n"/>
+      <c r="R100" s="5" t="n"/>
+      <c r="S100" s="5" t="n"/>
+      <c r="T100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n"/>
@@ -3150,7 +3395,9 @@
       <c r="O101" s="5" t="n"/>
       <c r="P101" s="5" t="n"/>
       <c r="Q101" s="5" t="n"/>
-      <c r="R101" s="7" t="n"/>
+      <c r="R101" s="5" t="n"/>
+      <c r="S101" s="5" t="n"/>
+      <c r="T101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n"/>
@@ -3170,7 +3417,9 @@
       <c r="O102" s="5" t="n"/>
       <c r="P102" s="5" t="n"/>
       <c r="Q102" s="5" t="n"/>
-      <c r="R102" s="7" t="n"/>
+      <c r="R102" s="5" t="n"/>
+      <c r="S102" s="5" t="n"/>
+      <c r="T102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n"/>
@@ -3190,7 +3439,9 @@
       <c r="O103" s="5" t="n"/>
       <c r="P103" s="5" t="n"/>
       <c r="Q103" s="5" t="n"/>
-      <c r="R103" s="7" t="n"/>
+      <c r="R103" s="5" t="n"/>
+      <c r="S103" s="5" t="n"/>
+      <c r="T103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n"/>
@@ -3210,7 +3461,9 @@
       <c r="O104" s="5" t="n"/>
       <c r="P104" s="5" t="n"/>
       <c r="Q104" s="5" t="n"/>
-      <c r="R104" s="7" t="n"/>
+      <c r="R104" s="5" t="n"/>
+      <c r="S104" s="5" t="n"/>
+      <c r="T104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n"/>
@@ -3230,7 +3483,9 @@
       <c r="O105" s="5" t="n"/>
       <c r="P105" s="5" t="n"/>
       <c r="Q105" s="5" t="n"/>
-      <c r="R105" s="7" t="n"/>
+      <c r="R105" s="5" t="n"/>
+      <c r="S105" s="5" t="n"/>
+      <c r="T105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n"/>
@@ -3250,7 +3505,9 @@
       <c r="O106" s="5" t="n"/>
       <c r="P106" s="5" t="n"/>
       <c r="Q106" s="5" t="n"/>
-      <c r="R106" s="7" t="n"/>
+      <c r="R106" s="5" t="n"/>
+      <c r="S106" s="5" t="n"/>
+      <c r="T106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n"/>
@@ -3270,7 +3527,9 @@
       <c r="O107" s="5" t="n"/>
       <c r="P107" s="5" t="n"/>
       <c r="Q107" s="5" t="n"/>
-      <c r="R107" s="7" t="n"/>
+      <c r="R107" s="5" t="n"/>
+      <c r="S107" s="5" t="n"/>
+      <c r="T107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n"/>
@@ -3290,7 +3549,9 @@
       <c r="O108" s="5" t="n"/>
       <c r="P108" s="5" t="n"/>
       <c r="Q108" s="5" t="n"/>
-      <c r="R108" s="7" t="n"/>
+      <c r="R108" s="5" t="n"/>
+      <c r="S108" s="5" t="n"/>
+      <c r="T108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n"/>
@@ -3310,7 +3571,9 @@
       <c r="O109" s="5" t="n"/>
       <c r="P109" s="5" t="n"/>
       <c r="Q109" s="5" t="n"/>
-      <c r="R109" s="7" t="n"/>
+      <c r="R109" s="5" t="n"/>
+      <c r="S109" s="5" t="n"/>
+      <c r="T109" s="7" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n"/>
@@ -3330,7 +3593,9 @@
       <c r="O110" s="5" t="n"/>
       <c r="P110" s="5" t="n"/>
       <c r="Q110" s="5" t="n"/>
-      <c r="R110" s="7" t="n"/>
+      <c r="R110" s="5" t="n"/>
+      <c r="S110" s="5" t="n"/>
+      <c r="T110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n"/>
@@ -3350,7 +3615,9 @@
       <c r="O111" s="5" t="n"/>
       <c r="P111" s="5" t="n"/>
       <c r="Q111" s="5" t="n"/>
-      <c r="R111" s="7" t="n"/>
+      <c r="R111" s="5" t="n"/>
+      <c r="S111" s="5" t="n"/>
+      <c r="T111" s="7" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="n"/>
@@ -3370,7 +3637,9 @@
       <c r="O112" s="5" t="n"/>
       <c r="P112" s="5" t="n"/>
       <c r="Q112" s="5" t="n"/>
-      <c r="R112" s="7" t="n"/>
+      <c r="R112" s="5" t="n"/>
+      <c r="S112" s="5" t="n"/>
+      <c r="T112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n"/>
@@ -3390,7 +3659,9 @@
       <c r="O113" s="5" t="n"/>
       <c r="P113" s="5" t="n"/>
       <c r="Q113" s="5" t="n"/>
-      <c r="R113" s="7" t="n"/>
+      <c r="R113" s="5" t="n"/>
+      <c r="S113" s="5" t="n"/>
+      <c r="T113" s="7" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n"/>
@@ -3410,7 +3681,9 @@
       <c r="O114" s="5" t="n"/>
       <c r="P114" s="5" t="n"/>
       <c r="Q114" s="5" t="n"/>
-      <c r="R114" s="7" t="n"/>
+      <c r="R114" s="5" t="n"/>
+      <c r="S114" s="5" t="n"/>
+      <c r="T114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n"/>
@@ -3430,7 +3703,9 @@
       <c r="O115" s="5" t="n"/>
       <c r="P115" s="5" t="n"/>
       <c r="Q115" s="5" t="n"/>
-      <c r="R115" s="7" t="n"/>
+      <c r="R115" s="5" t="n"/>
+      <c r="S115" s="5" t="n"/>
+      <c r="T115" s="7" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n"/>
@@ -3450,7 +3725,9 @@
       <c r="O116" s="5" t="n"/>
       <c r="P116" s="5" t="n"/>
       <c r="Q116" s="5" t="n"/>
-      <c r="R116" s="7" t="n"/>
+      <c r="R116" s="5" t="n"/>
+      <c r="S116" s="5" t="n"/>
+      <c r="T116" s="7" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n"/>
@@ -3470,7 +3747,9 @@
       <c r="O117" s="5" t="n"/>
       <c r="P117" s="5" t="n"/>
       <c r="Q117" s="5" t="n"/>
-      <c r="R117" s="7" t="n"/>
+      <c r="R117" s="5" t="n"/>
+      <c r="S117" s="5" t="n"/>
+      <c r="T117" s="7" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="n"/>
@@ -3490,7 +3769,9 @@
       <c r="O118" s="5" t="n"/>
       <c r="P118" s="5" t="n"/>
       <c r="Q118" s="5" t="n"/>
-      <c r="R118" s="7" t="n"/>
+      <c r="R118" s="5" t="n"/>
+      <c r="S118" s="5" t="n"/>
+      <c r="T118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n"/>
@@ -3510,7 +3791,9 @@
       <c r="O119" s="5" t="n"/>
       <c r="P119" s="5" t="n"/>
       <c r="Q119" s="5" t="n"/>
-      <c r="R119" s="7" t="n"/>
+      <c r="R119" s="5" t="n"/>
+      <c r="S119" s="5" t="n"/>
+      <c r="T119" s="7" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n"/>
@@ -3530,7 +3813,9 @@
       <c r="O120" s="5" t="n"/>
       <c r="P120" s="5" t="n"/>
       <c r="Q120" s="5" t="n"/>
-      <c r="R120" s="7" t="n"/>
+      <c r="R120" s="5" t="n"/>
+      <c r="S120" s="5" t="n"/>
+      <c r="T120" s="7" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n"/>
@@ -3550,7 +3835,9 @@
       <c r="O121" s="5" t="n"/>
       <c r="P121" s="5" t="n"/>
       <c r="Q121" s="5" t="n"/>
-      <c r="R121" s="7" t="n"/>
+      <c r="R121" s="5" t="n"/>
+      <c r="S121" s="5" t="n"/>
+      <c r="T121" s="7" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="n"/>
@@ -3570,7 +3857,9 @@
       <c r="O122" s="5" t="n"/>
       <c r="P122" s="5" t="n"/>
       <c r="Q122" s="5" t="n"/>
-      <c r="R122" s="7" t="n"/>
+      <c r="R122" s="5" t="n"/>
+      <c r="S122" s="5" t="n"/>
+      <c r="T122" s="7" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n"/>
@@ -3590,7 +3879,9 @@
       <c r="O123" s="5" t="n"/>
       <c r="P123" s="5" t="n"/>
       <c r="Q123" s="5" t="n"/>
-      <c r="R123" s="7" t="n"/>
+      <c r="R123" s="5" t="n"/>
+      <c r="S123" s="5" t="n"/>
+      <c r="T123" s="7" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="n"/>
@@ -3610,7 +3901,9 @@
       <c r="O124" s="5" t="n"/>
       <c r="P124" s="5" t="n"/>
       <c r="Q124" s="5" t="n"/>
-      <c r="R124" s="7" t="n"/>
+      <c r="R124" s="5" t="n"/>
+      <c r="S124" s="5" t="n"/>
+      <c r="T124" s="7" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n"/>
@@ -3630,7 +3923,9 @@
       <c r="O125" s="5" t="n"/>
       <c r="P125" s="5" t="n"/>
       <c r="Q125" s="5" t="n"/>
-      <c r="R125" s="7" t="n"/>
+      <c r="R125" s="5" t="n"/>
+      <c r="S125" s="5" t="n"/>
+      <c r="T125" s="7" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n"/>
@@ -3650,7 +3945,9 @@
       <c r="O126" s="5" t="n"/>
       <c r="P126" s="5" t="n"/>
       <c r="Q126" s="5" t="n"/>
-      <c r="R126" s="7" t="n"/>
+      <c r="R126" s="5" t="n"/>
+      <c r="S126" s="5" t="n"/>
+      <c r="T126" s="7" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n"/>
@@ -3670,7 +3967,9 @@
       <c r="O127" s="5" t="n"/>
       <c r="P127" s="5" t="n"/>
       <c r="Q127" s="5" t="n"/>
-      <c r="R127" s="7" t="n"/>
+      <c r="R127" s="5" t="n"/>
+      <c r="S127" s="5" t="n"/>
+      <c r="T127" s="7" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="n"/>
@@ -3690,7 +3989,9 @@
       <c r="O128" s="5" t="n"/>
       <c r="P128" s="5" t="n"/>
       <c r="Q128" s="5" t="n"/>
-      <c r="R128" s="7" t="n"/>
+      <c r="R128" s="5" t="n"/>
+      <c r="S128" s="5" t="n"/>
+      <c r="T128" s="7" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n"/>
@@ -3710,7 +4011,9 @@
       <c r="O129" s="5" t="n"/>
       <c r="P129" s="5" t="n"/>
       <c r="Q129" s="5" t="n"/>
-      <c r="R129" s="7" t="n"/>
+      <c r="R129" s="5" t="n"/>
+      <c r="S129" s="5" t="n"/>
+      <c r="T129" s="7" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n"/>
@@ -3730,7 +4033,9 @@
       <c r="O130" s="5" t="n"/>
       <c r="P130" s="5" t="n"/>
       <c r="Q130" s="5" t="n"/>
-      <c r="R130" s="7" t="n"/>
+      <c r="R130" s="5" t="n"/>
+      <c r="S130" s="5" t="n"/>
+      <c r="T130" s="7" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n"/>
@@ -3750,7 +4055,9 @@
       <c r="O131" s="5" t="n"/>
       <c r="P131" s="5" t="n"/>
       <c r="Q131" s="5" t="n"/>
-      <c r="R131" s="7" t="n"/>
+      <c r="R131" s="5" t="n"/>
+      <c r="S131" s="5" t="n"/>
+      <c r="T131" s="7" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="n"/>
@@ -3770,7 +4077,9 @@
       <c r="O132" s="5" t="n"/>
       <c r="P132" s="5" t="n"/>
       <c r="Q132" s="5" t="n"/>
-      <c r="R132" s="7" t="n"/>
+      <c r="R132" s="5" t="n"/>
+      <c r="S132" s="5" t="n"/>
+      <c r="T132" s="7" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n"/>
@@ -3790,7 +4099,9 @@
       <c r="O133" s="5" t="n"/>
       <c r="P133" s="5" t="n"/>
       <c r="Q133" s="5" t="n"/>
-      <c r="R133" s="7" t="n"/>
+      <c r="R133" s="5" t="n"/>
+      <c r="S133" s="5" t="n"/>
+      <c r="T133" s="7" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="n"/>
@@ -3810,7 +4121,9 @@
       <c r="O134" s="5" t="n"/>
       <c r="P134" s="5" t="n"/>
       <c r="Q134" s="5" t="n"/>
-      <c r="R134" s="7" t="n"/>
+      <c r="R134" s="5" t="n"/>
+      <c r="S134" s="5" t="n"/>
+      <c r="T134" s="7" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n"/>
@@ -3830,7 +4143,9 @@
       <c r="O135" s="5" t="n"/>
       <c r="P135" s="5" t="n"/>
       <c r="Q135" s="5" t="n"/>
-      <c r="R135" s="7" t="n"/>
+      <c r="R135" s="5" t="n"/>
+      <c r="S135" s="5" t="n"/>
+      <c r="T135" s="7" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="n"/>
@@ -3850,7 +4165,9 @@
       <c r="O136" s="5" t="n"/>
       <c r="P136" s="5" t="n"/>
       <c r="Q136" s="5" t="n"/>
-      <c r="R136" s="7" t="n"/>
+      <c r="R136" s="5" t="n"/>
+      <c r="S136" s="5" t="n"/>
+      <c r="T136" s="7" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n"/>
@@ -3870,7 +4187,9 @@
       <c r="O137" s="5" t="n"/>
       <c r="P137" s="5" t="n"/>
       <c r="Q137" s="5" t="n"/>
-      <c r="R137" s="7" t="n"/>
+      <c r="R137" s="5" t="n"/>
+      <c r="S137" s="5" t="n"/>
+      <c r="T137" s="7" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="n"/>
@@ -3890,7 +4209,9 @@
       <c r="O138" s="5" t="n"/>
       <c r="P138" s="5" t="n"/>
       <c r="Q138" s="5" t="n"/>
-      <c r="R138" s="7" t="n"/>
+      <c r="R138" s="5" t="n"/>
+      <c r="S138" s="5" t="n"/>
+      <c r="T138" s="7" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n"/>
@@ -3910,7 +4231,9 @@
       <c r="O139" s="5" t="n"/>
       <c r="P139" s="5" t="n"/>
       <c r="Q139" s="5" t="n"/>
-      <c r="R139" s="7" t="n"/>
+      <c r="R139" s="5" t="n"/>
+      <c r="S139" s="5" t="n"/>
+      <c r="T139" s="7" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="n"/>
@@ -3930,7 +4253,9 @@
       <c r="O140" s="5" t="n"/>
       <c r="P140" s="5" t="n"/>
       <c r="Q140" s="5" t="n"/>
-      <c r="R140" s="7" t="n"/>
+      <c r="R140" s="5" t="n"/>
+      <c r="S140" s="5" t="n"/>
+      <c r="T140" s="7" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n"/>
@@ -3950,7 +4275,9 @@
       <c r="O141" s="5" t="n"/>
       <c r="P141" s="5" t="n"/>
       <c r="Q141" s="5" t="n"/>
-      <c r="R141" s="7" t="n"/>
+      <c r="R141" s="5" t="n"/>
+      <c r="S141" s="5" t="n"/>
+      <c r="T141" s="7" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="n"/>
@@ -3970,7 +4297,9 @@
       <c r="O142" s="5" t="n"/>
       <c r="P142" s="5" t="n"/>
       <c r="Q142" s="5" t="n"/>
-      <c r="R142" s="7" t="n"/>
+      <c r="R142" s="5" t="n"/>
+      <c r="S142" s="5" t="n"/>
+      <c r="T142" s="7" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n"/>
@@ -3990,7 +4319,9 @@
       <c r="O143" s="5" t="n"/>
       <c r="P143" s="5" t="n"/>
       <c r="Q143" s="5" t="n"/>
-      <c r="R143" s="7" t="n"/>
+      <c r="R143" s="5" t="n"/>
+      <c r="S143" s="5" t="n"/>
+      <c r="T143" s="7" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="n"/>
@@ -4010,7 +4341,9 @@
       <c r="O144" s="5" t="n"/>
       <c r="P144" s="5" t="n"/>
       <c r="Q144" s="5" t="n"/>
-      <c r="R144" s="7" t="n"/>
+      <c r="R144" s="5" t="n"/>
+      <c r="S144" s="5" t="n"/>
+      <c r="T144" s="7" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n"/>
@@ -4030,7 +4363,9 @@
       <c r="O145" s="5" t="n"/>
       <c r="P145" s="5" t="n"/>
       <c r="Q145" s="5" t="n"/>
-      <c r="R145" s="7" t="n"/>
+      <c r="R145" s="5" t="n"/>
+      <c r="S145" s="5" t="n"/>
+      <c r="T145" s="7" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="n"/>
@@ -4050,7 +4385,9 @@
       <c r="O146" s="5" t="n"/>
       <c r="P146" s="5" t="n"/>
       <c r="Q146" s="5" t="n"/>
-      <c r="R146" s="7" t="n"/>
+      <c r="R146" s="5" t="n"/>
+      <c r="S146" s="5" t="n"/>
+      <c r="T146" s="7" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n"/>
@@ -4070,7 +4407,9 @@
       <c r="O147" s="5" t="n"/>
       <c r="P147" s="5" t="n"/>
       <c r="Q147" s="5" t="n"/>
-      <c r="R147" s="7" t="n"/>
+      <c r="R147" s="5" t="n"/>
+      <c r="S147" s="5" t="n"/>
+      <c r="T147" s="7" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="n"/>
@@ -4090,7 +4429,9 @@
       <c r="O148" s="5" t="n"/>
       <c r="P148" s="5" t="n"/>
       <c r="Q148" s="5" t="n"/>
-      <c r="R148" s="7" t="n"/>
+      <c r="R148" s="5" t="n"/>
+      <c r="S148" s="5" t="n"/>
+      <c r="T148" s="7" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n"/>
@@ -4110,7 +4451,9 @@
       <c r="O149" s="5" t="n"/>
       <c r="P149" s="5" t="n"/>
       <c r="Q149" s="5" t="n"/>
-      <c r="R149" s="7" t="n"/>
+      <c r="R149" s="5" t="n"/>
+      <c r="S149" s="5" t="n"/>
+      <c r="T149" s="7" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="n"/>
@@ -4130,7 +4473,9 @@
       <c r="O150" s="5" t="n"/>
       <c r="P150" s="5" t="n"/>
       <c r="Q150" s="5" t="n"/>
-      <c r="R150" s="7" t="n"/>
+      <c r="R150" s="5" t="n"/>
+      <c r="S150" s="5" t="n"/>
+      <c r="T150" s="7" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n"/>
@@ -4150,7 +4495,9 @@
       <c r="O151" s="5" t="n"/>
       <c r="P151" s="5" t="n"/>
       <c r="Q151" s="5" t="n"/>
-      <c r="R151" s="7" t="n"/>
+      <c r="R151" s="5" t="n"/>
+      <c r="S151" s="5" t="n"/>
+      <c r="T151" s="7" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="n"/>
@@ -4170,7 +4517,9 @@
       <c r="O152" s="5" t="n"/>
       <c r="P152" s="5" t="n"/>
       <c r="Q152" s="5" t="n"/>
-      <c r="R152" s="7" t="n"/>
+      <c r="R152" s="5" t="n"/>
+      <c r="S152" s="5" t="n"/>
+      <c r="T152" s="7" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="5" t="n"/>
@@ -4190,7 +4539,9 @@
       <c r="O153" s="5" t="n"/>
       <c r="P153" s="5" t="n"/>
       <c r="Q153" s="5" t="n"/>
-      <c r="R153" s="7" t="n"/>
+      <c r="R153" s="5" t="n"/>
+      <c r="S153" s="5" t="n"/>
+      <c r="T153" s="7" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="5" t="n"/>
@@ -4210,7 +4561,9 @@
       <c r="O154" s="5" t="n"/>
       <c r="P154" s="5" t="n"/>
       <c r="Q154" s="5" t="n"/>
-      <c r="R154" s="7" t="n"/>
+      <c r="R154" s="5" t="n"/>
+      <c r="S154" s="5" t="n"/>
+      <c r="T154" s="7" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="n"/>
@@ -4230,7 +4583,9 @@
       <c r="O155" s="5" t="n"/>
       <c r="P155" s="5" t="n"/>
       <c r="Q155" s="5" t="n"/>
-      <c r="R155" s="7" t="n"/>
+      <c r="R155" s="5" t="n"/>
+      <c r="S155" s="5" t="n"/>
+      <c r="T155" s="7" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="n"/>
@@ -4250,7 +4605,9 @@
       <c r="O156" s="5" t="n"/>
       <c r="P156" s="5" t="n"/>
       <c r="Q156" s="5" t="n"/>
-      <c r="R156" s="7" t="n"/>
+      <c r="R156" s="5" t="n"/>
+      <c r="S156" s="5" t="n"/>
+      <c r="T156" s="7" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="n"/>
@@ -4270,7 +4627,9 @@
       <c r="O157" s="5" t="n"/>
       <c r="P157" s="5" t="n"/>
       <c r="Q157" s="5" t="n"/>
-      <c r="R157" s="7" t="n"/>
+      <c r="R157" s="5" t="n"/>
+      <c r="S157" s="5" t="n"/>
+      <c r="T157" s="7" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="n"/>
@@ -4290,7 +4649,9 @@
       <c r="O158" s="5" t="n"/>
       <c r="P158" s="5" t="n"/>
       <c r="Q158" s="5" t="n"/>
-      <c r="R158" s="7" t="n"/>
+      <c r="R158" s="5" t="n"/>
+      <c r="S158" s="5" t="n"/>
+      <c r="T158" s="7" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="n"/>
@@ -4310,7 +4671,9 @@
       <c r="O159" s="5" t="n"/>
       <c r="P159" s="5" t="n"/>
       <c r="Q159" s="5" t="n"/>
-      <c r="R159" s="7" t="n"/>
+      <c r="R159" s="5" t="n"/>
+      <c r="S159" s="5" t="n"/>
+      <c r="T159" s="7" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="5" t="n"/>
@@ -4330,7 +4693,9 @@
       <c r="O160" s="5" t="n"/>
       <c r="P160" s="5" t="n"/>
       <c r="Q160" s="5" t="n"/>
-      <c r="R160" s="7" t="n"/>
+      <c r="R160" s="5" t="n"/>
+      <c r="S160" s="5" t="n"/>
+      <c r="T160" s="7" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="n"/>
@@ -4350,7 +4715,9 @@
       <c r="O161" s="5" t="n"/>
       <c r="P161" s="5" t="n"/>
       <c r="Q161" s="5" t="n"/>
-      <c r="R161" s="7" t="n"/>
+      <c r="R161" s="5" t="n"/>
+      <c r="S161" s="5" t="n"/>
+      <c r="T161" s="7" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="5" t="n"/>
@@ -4370,7 +4737,9 @@
       <c r="O162" s="5" t="n"/>
       <c r="P162" s="5" t="n"/>
       <c r="Q162" s="5" t="n"/>
-      <c r="R162" s="7" t="n"/>
+      <c r="R162" s="5" t="n"/>
+      <c r="S162" s="5" t="n"/>
+      <c r="T162" s="7" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="5" t="n"/>
@@ -4390,7 +4759,9 @@
       <c r="O163" s="5" t="n"/>
       <c r="P163" s="5" t="n"/>
       <c r="Q163" s="5" t="n"/>
-      <c r="R163" s="7" t="n"/>
+      <c r="R163" s="5" t="n"/>
+      <c r="S163" s="5" t="n"/>
+      <c r="T163" s="7" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="n"/>
@@ -4410,7 +4781,9 @@
       <c r="O164" s="5" t="n"/>
       <c r="P164" s="5" t="n"/>
       <c r="Q164" s="5" t="n"/>
-      <c r="R164" s="7" t="n"/>
+      <c r="R164" s="5" t="n"/>
+      <c r="S164" s="5" t="n"/>
+      <c r="T164" s="7" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="n"/>
@@ -4430,7 +4803,9 @@
       <c r="O165" s="5" t="n"/>
       <c r="P165" s="5" t="n"/>
       <c r="Q165" s="5" t="n"/>
-      <c r="R165" s="7" t="n"/>
+      <c r="R165" s="5" t="n"/>
+      <c r="S165" s="5" t="n"/>
+      <c r="T165" s="7" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="5" t="n"/>
@@ -4450,7 +4825,9 @@
       <c r="O166" s="5" t="n"/>
       <c r="P166" s="5" t="n"/>
       <c r="Q166" s="5" t="n"/>
-      <c r="R166" s="7" t="n"/>
+      <c r="R166" s="5" t="n"/>
+      <c r="S166" s="5" t="n"/>
+      <c r="T166" s="7" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="n"/>
@@ -4470,7 +4847,9 @@
       <c r="O167" s="5" t="n"/>
       <c r="P167" s="5" t="n"/>
       <c r="Q167" s="5" t="n"/>
-      <c r="R167" s="7" t="n"/>
+      <c r="R167" s="5" t="n"/>
+      <c r="S167" s="5" t="n"/>
+      <c r="T167" s="7" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n"/>
@@ -4490,7 +4869,9 @@
       <c r="O168" s="5" t="n"/>
       <c r="P168" s="5" t="n"/>
       <c r="Q168" s="5" t="n"/>
-      <c r="R168" s="7" t="n"/>
+      <c r="R168" s="5" t="n"/>
+      <c r="S168" s="5" t="n"/>
+      <c r="T168" s="7" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="n"/>
@@ -4510,7 +4891,9 @@
       <c r="O169" s="5" t="n"/>
       <c r="P169" s="5" t="n"/>
       <c r="Q169" s="5" t="n"/>
-      <c r="R169" s="7" t="n"/>
+      <c r="R169" s="5" t="n"/>
+      <c r="S169" s="5" t="n"/>
+      <c r="T169" s="7" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="n"/>
@@ -4530,7 +4913,9 @@
       <c r="O170" s="5" t="n"/>
       <c r="P170" s="5" t="n"/>
       <c r="Q170" s="5" t="n"/>
-      <c r="R170" s="7" t="n"/>
+      <c r="R170" s="5" t="n"/>
+      <c r="S170" s="5" t="n"/>
+      <c r="T170" s="7" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="5" t="n"/>
@@ -4550,7 +4935,9 @@
       <c r="O171" s="5" t="n"/>
       <c r="P171" s="5" t="n"/>
       <c r="Q171" s="5" t="n"/>
-      <c r="R171" s="7" t="n"/>
+      <c r="R171" s="5" t="n"/>
+      <c r="S171" s="5" t="n"/>
+      <c r="T171" s="7" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="n"/>
@@ -4570,7 +4957,9 @@
       <c r="O172" s="5" t="n"/>
       <c r="P172" s="5" t="n"/>
       <c r="Q172" s="5" t="n"/>
-      <c r="R172" s="7" t="n"/>
+      <c r="R172" s="5" t="n"/>
+      <c r="S172" s="5" t="n"/>
+      <c r="T172" s="7" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="5" t="n"/>
@@ -4590,7 +4979,9 @@
       <c r="O173" s="5" t="n"/>
       <c r="P173" s="5" t="n"/>
       <c r="Q173" s="5" t="n"/>
-      <c r="R173" s="7" t="n"/>
+      <c r="R173" s="5" t="n"/>
+      <c r="S173" s="5" t="n"/>
+      <c r="T173" s="7" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="5" t="n"/>
@@ -4610,7 +5001,9 @@
       <c r="O174" s="5" t="n"/>
       <c r="P174" s="5" t="n"/>
       <c r="Q174" s="5" t="n"/>
-      <c r="R174" s="7" t="n"/>
+      <c r="R174" s="5" t="n"/>
+      <c r="S174" s="5" t="n"/>
+      <c r="T174" s="7" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="5" t="n"/>
@@ -4630,7 +5023,9 @@
       <c r="O175" s="5" t="n"/>
       <c r="P175" s="5" t="n"/>
       <c r="Q175" s="5" t="n"/>
-      <c r="R175" s="7" t="n"/>
+      <c r="R175" s="5" t="n"/>
+      <c r="S175" s="5" t="n"/>
+      <c r="T175" s="7" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="5" t="n"/>
@@ -4650,7 +5045,9 @@
       <c r="O176" s="5" t="n"/>
       <c r="P176" s="5" t="n"/>
       <c r="Q176" s="5" t="n"/>
-      <c r="R176" s="7" t="n"/>
+      <c r="R176" s="5" t="n"/>
+      <c r="S176" s="5" t="n"/>
+      <c r="T176" s="7" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="5" t="n"/>
@@ -4670,7 +5067,9 @@
       <c r="O177" s="5" t="n"/>
       <c r="P177" s="5" t="n"/>
       <c r="Q177" s="5" t="n"/>
-      <c r="R177" s="7" t="n"/>
+      <c r="R177" s="5" t="n"/>
+      <c r="S177" s="5" t="n"/>
+      <c r="T177" s="7" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="5" t="n"/>
@@ -4690,7 +5089,9 @@
       <c r="O178" s="5" t="n"/>
       <c r="P178" s="5" t="n"/>
       <c r="Q178" s="5" t="n"/>
-      <c r="R178" s="7" t="n"/>
+      <c r="R178" s="5" t="n"/>
+      <c r="S178" s="5" t="n"/>
+      <c r="T178" s="7" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n"/>
@@ -4710,7 +5111,9 @@
       <c r="O179" s="5" t="n"/>
       <c r="P179" s="5" t="n"/>
       <c r="Q179" s="5" t="n"/>
-      <c r="R179" s="7" t="n"/>
+      <c r="R179" s="5" t="n"/>
+      <c r="S179" s="5" t="n"/>
+      <c r="T179" s="7" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n"/>
@@ -4730,7 +5133,9 @@
       <c r="O180" s="5" t="n"/>
       <c r="P180" s="5" t="n"/>
       <c r="Q180" s="5" t="n"/>
-      <c r="R180" s="7" t="n"/>
+      <c r="R180" s="5" t="n"/>
+      <c r="S180" s="5" t="n"/>
+      <c r="T180" s="7" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="5" t="n"/>
@@ -4750,7 +5155,9 @@
       <c r="O181" s="5" t="n"/>
       <c r="P181" s="5" t="n"/>
       <c r="Q181" s="5" t="n"/>
-      <c r="R181" s="7" t="n"/>
+      <c r="R181" s="5" t="n"/>
+      <c r="S181" s="5" t="n"/>
+      <c r="T181" s="7" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="n"/>
@@ -4770,7 +5177,9 @@
       <c r="O182" s="5" t="n"/>
       <c r="P182" s="5" t="n"/>
       <c r="Q182" s="5" t="n"/>
-      <c r="R182" s="7" t="n"/>
+      <c r="R182" s="5" t="n"/>
+      <c r="S182" s="5" t="n"/>
+      <c r="T182" s="7" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="5" t="n"/>
@@ -4790,7 +5199,9 @@
       <c r="O183" s="5" t="n"/>
       <c r="P183" s="5" t="n"/>
       <c r="Q183" s="5" t="n"/>
-      <c r="R183" s="7" t="n"/>
+      <c r="R183" s="5" t="n"/>
+      <c r="S183" s="5" t="n"/>
+      <c r="T183" s="7" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="5" t="n"/>
@@ -4810,7 +5221,9 @@
       <c r="O184" s="5" t="n"/>
       <c r="P184" s="5" t="n"/>
       <c r="Q184" s="5" t="n"/>
-      <c r="R184" s="7" t="n"/>
+      <c r="R184" s="5" t="n"/>
+      <c r="S184" s="5" t="n"/>
+      <c r="T184" s="7" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="5" t="n"/>
@@ -4830,7 +5243,9 @@
       <c r="O185" s="5" t="n"/>
       <c r="P185" s="5" t="n"/>
       <c r="Q185" s="5" t="n"/>
-      <c r="R185" s="7" t="n"/>
+      <c r="R185" s="5" t="n"/>
+      <c r="S185" s="5" t="n"/>
+      <c r="T185" s="7" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="5" t="n"/>
@@ -4850,7 +5265,9 @@
       <c r="O186" s="5" t="n"/>
       <c r="P186" s="5" t="n"/>
       <c r="Q186" s="5" t="n"/>
-      <c r="R186" s="7" t="n"/>
+      <c r="R186" s="5" t="n"/>
+      <c r="S186" s="5" t="n"/>
+      <c r="T186" s="7" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="5" t="n"/>
@@ -4870,7 +5287,9 @@
       <c r="O187" s="5" t="n"/>
       <c r="P187" s="5" t="n"/>
       <c r="Q187" s="5" t="n"/>
-      <c r="R187" s="7" t="n"/>
+      <c r="R187" s="5" t="n"/>
+      <c r="S187" s="5" t="n"/>
+      <c r="T187" s="7" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="n"/>
@@ -4890,7 +5309,9 @@
       <c r="O188" s="5" t="n"/>
       <c r="P188" s="5" t="n"/>
       <c r="Q188" s="5" t="n"/>
-      <c r="R188" s="7" t="n"/>
+      <c r="R188" s="5" t="n"/>
+      <c r="S188" s="5" t="n"/>
+      <c r="T188" s="7" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="5" t="n"/>
@@ -4910,7 +5331,9 @@
       <c r="O189" s="5" t="n"/>
       <c r="P189" s="5" t="n"/>
       <c r="Q189" s="5" t="n"/>
-      <c r="R189" s="7" t="n"/>
+      <c r="R189" s="5" t="n"/>
+      <c r="S189" s="5" t="n"/>
+      <c r="T189" s="7" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="n"/>
@@ -4930,7 +5353,9 @@
       <c r="O190" s="5" t="n"/>
       <c r="P190" s="5" t="n"/>
       <c r="Q190" s="5" t="n"/>
-      <c r="R190" s="7" t="n"/>
+      <c r="R190" s="5" t="n"/>
+      <c r="S190" s="5" t="n"/>
+      <c r="T190" s="7" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="5" t="n"/>
@@ -4950,7 +5375,9 @@
       <c r="O191" s="5" t="n"/>
       <c r="P191" s="5" t="n"/>
       <c r="Q191" s="5" t="n"/>
-      <c r="R191" s="7" t="n"/>
+      <c r="R191" s="5" t="n"/>
+      <c r="S191" s="5" t="n"/>
+      <c r="T191" s="7" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="5" t="n"/>
@@ -4970,7 +5397,9 @@
       <c r="O192" s="5" t="n"/>
       <c r="P192" s="5" t="n"/>
       <c r="Q192" s="5" t="n"/>
-      <c r="R192" s="7" t="n"/>
+      <c r="R192" s="5" t="n"/>
+      <c r="S192" s="5" t="n"/>
+      <c r="T192" s="7" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="5" t="n"/>
@@ -4990,7 +5419,9 @@
       <c r="O193" s="5" t="n"/>
       <c r="P193" s="5" t="n"/>
       <c r="Q193" s="5" t="n"/>
-      <c r="R193" s="7" t="n"/>
+      <c r="R193" s="5" t="n"/>
+      <c r="S193" s="5" t="n"/>
+      <c r="T193" s="7" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="5" t="n"/>
@@ -5010,7 +5441,9 @@
       <c r="O194" s="5" t="n"/>
       <c r="P194" s="5" t="n"/>
       <c r="Q194" s="5" t="n"/>
-      <c r="R194" s="7" t="n"/>
+      <c r="R194" s="5" t="n"/>
+      <c r="S194" s="5" t="n"/>
+      <c r="T194" s="7" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="5" t="n"/>
@@ -5030,7 +5463,9 @@
       <c r="O195" s="5" t="n"/>
       <c r="P195" s="5" t="n"/>
       <c r="Q195" s="5" t="n"/>
-      <c r="R195" s="7" t="n"/>
+      <c r="R195" s="5" t="n"/>
+      <c r="S195" s="5" t="n"/>
+      <c r="T195" s="7" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="5" t="n"/>
@@ -5050,7 +5485,9 @@
       <c r="O196" s="5" t="n"/>
       <c r="P196" s="5" t="n"/>
       <c r="Q196" s="5" t="n"/>
-      <c r="R196" s="7" t="n"/>
+      <c r="R196" s="5" t="n"/>
+      <c r="S196" s="5" t="n"/>
+      <c r="T196" s="7" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="5" t="n"/>
@@ -5070,7 +5507,9 @@
       <c r="O197" s="5" t="n"/>
       <c r="P197" s="5" t="n"/>
       <c r="Q197" s="5" t="n"/>
-      <c r="R197" s="7" t="n"/>
+      <c r="R197" s="5" t="n"/>
+      <c r="S197" s="5" t="n"/>
+      <c r="T197" s="7" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="5" t="n"/>
@@ -5090,7 +5529,9 @@
       <c r="O198" s="5" t="n"/>
       <c r="P198" s="5" t="n"/>
       <c r="Q198" s="5" t="n"/>
-      <c r="R198" s="7" t="n"/>
+      <c r="R198" s="5" t="n"/>
+      <c r="S198" s="5" t="n"/>
+      <c r="T198" s="7" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="5" t="n"/>
@@ -5110,7 +5551,9 @@
       <c r="O199" s="5" t="n"/>
       <c r="P199" s="5" t="n"/>
       <c r="Q199" s="5" t="n"/>
-      <c r="R199" s="7" t="n"/>
+      <c r="R199" s="5" t="n"/>
+      <c r="S199" s="5" t="n"/>
+      <c r="T199" s="7" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="n"/>
@@ -5130,7 +5573,9 @@
       <c r="O200" s="5" t="n"/>
       <c r="P200" s="5" t="n"/>
       <c r="Q200" s="5" t="n"/>
-      <c r="R200" s="7" t="n"/>
+      <c r="R200" s="5" t="n"/>
+      <c r="S200" s="5" t="n"/>
+      <c r="T200" s="7" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="5" t="n"/>
@@ -5150,7 +5595,9 @@
       <c r="O201" s="5" t="n"/>
       <c r="P201" s="5" t="n"/>
       <c r="Q201" s="5" t="n"/>
-      <c r="R201" s="7" t="n"/>
+      <c r="R201" s="5" t="n"/>
+      <c r="S201" s="5" t="n"/>
+      <c r="T201" s="7" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="5" t="n"/>
@@ -5170,7 +5617,9 @@
       <c r="O202" s="5" t="n"/>
       <c r="P202" s="5" t="n"/>
       <c r="Q202" s="5" t="n"/>
-      <c r="R202" s="7" t="n"/>
+      <c r="R202" s="5" t="n"/>
+      <c r="S202" s="5" t="n"/>
+      <c r="T202" s="7" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="5" t="n"/>
@@ -5190,7 +5639,9 @@
       <c r="O203" s="5" t="n"/>
       <c r="P203" s="5" t="n"/>
       <c r="Q203" s="5" t="n"/>
-      <c r="R203" s="7" t="n"/>
+      <c r="R203" s="5" t="n"/>
+      <c r="S203" s="5" t="n"/>
+      <c r="T203" s="7" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="5" t="n"/>
@@ -5210,7 +5661,9 @@
       <c r="O204" s="5" t="n"/>
       <c r="P204" s="5" t="n"/>
       <c r="Q204" s="5" t="n"/>
-      <c r="R204" s="7" t="n"/>
+      <c r="R204" s="5" t="n"/>
+      <c r="S204" s="5" t="n"/>
+      <c r="T204" s="7" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="5" t="n"/>
@@ -5230,7 +5683,9 @@
       <c r="O205" s="5" t="n"/>
       <c r="P205" s="5" t="n"/>
       <c r="Q205" s="5" t="n"/>
-      <c r="R205" s="7" t="n"/>
+      <c r="R205" s="5" t="n"/>
+      <c r="S205" s="5" t="n"/>
+      <c r="T205" s="7" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="5" t="n"/>
@@ -5250,7 +5705,9 @@
       <c r="O206" s="5" t="n"/>
       <c r="P206" s="5" t="n"/>
       <c r="Q206" s="5" t="n"/>
-      <c r="R206" s="7" t="n"/>
+      <c r="R206" s="5" t="n"/>
+      <c r="S206" s="5" t="n"/>
+      <c r="T206" s="7" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="5" t="n"/>
@@ -5270,7 +5727,9 @@
       <c r="O207" s="5" t="n"/>
       <c r="P207" s="5" t="n"/>
       <c r="Q207" s="5" t="n"/>
-      <c r="R207" s="7" t="n"/>
+      <c r="R207" s="5" t="n"/>
+      <c r="S207" s="5" t="n"/>
+      <c r="T207" s="7" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="5" t="n"/>
@@ -5290,7 +5749,9 @@
       <c r="O208" s="5" t="n"/>
       <c r="P208" s="5" t="n"/>
       <c r="Q208" s="5" t="n"/>
-      <c r="R208" s="7" t="n"/>
+      <c r="R208" s="5" t="n"/>
+      <c r="S208" s="5" t="n"/>
+      <c r="T208" s="7" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="5" t="n"/>
@@ -5310,7 +5771,9 @@
       <c r="O209" s="5" t="n"/>
       <c r="P209" s="5" t="n"/>
       <c r="Q209" s="5" t="n"/>
-      <c r="R209" s="7" t="n"/>
+      <c r="R209" s="5" t="n"/>
+      <c r="S209" s="5" t="n"/>
+      <c r="T209" s="7" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="5" t="n"/>
@@ -5330,7 +5793,9 @@
       <c r="O210" s="5" t="n"/>
       <c r="P210" s="5" t="n"/>
       <c r="Q210" s="5" t="n"/>
-      <c r="R210" s="7" t="n"/>
+      <c r="R210" s="5" t="n"/>
+      <c r="S210" s="5" t="n"/>
+      <c r="T210" s="7" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="5" t="n"/>
@@ -5350,7 +5815,9 @@
       <c r="O211" s="5" t="n"/>
       <c r="P211" s="5" t="n"/>
       <c r="Q211" s="5" t="n"/>
-      <c r="R211" s="7" t="n"/>
+      <c r="R211" s="5" t="n"/>
+      <c r="S211" s="5" t="n"/>
+      <c r="T211" s="7" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="5" t="n"/>
@@ -5370,7 +5837,9 @@
       <c r="O212" s="5" t="n"/>
       <c r="P212" s="5" t="n"/>
       <c r="Q212" s="5" t="n"/>
-      <c r="R212" s="7" t="n"/>
+      <c r="R212" s="5" t="n"/>
+      <c r="S212" s="5" t="n"/>
+      <c r="T212" s="7" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="5" t="n"/>
@@ -5390,7 +5859,9 @@
       <c r="O213" s="5" t="n"/>
       <c r="P213" s="5" t="n"/>
       <c r="Q213" s="5" t="n"/>
-      <c r="R213" s="7" t="n"/>
+      <c r="R213" s="5" t="n"/>
+      <c r="S213" s="5" t="n"/>
+      <c r="T213" s="7" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="5" t="n"/>
@@ -5410,7 +5881,9 @@
       <c r="O214" s="5" t="n"/>
       <c r="P214" s="5" t="n"/>
       <c r="Q214" s="5" t="n"/>
-      <c r="R214" s="7" t="n"/>
+      <c r="R214" s="5" t="n"/>
+      <c r="S214" s="5" t="n"/>
+      <c r="T214" s="7" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="5" t="n"/>
@@ -5430,7 +5903,9 @@
       <c r="O215" s="5" t="n"/>
       <c r="P215" s="5" t="n"/>
       <c r="Q215" s="5" t="n"/>
-      <c r="R215" s="7" t="n"/>
+      <c r="R215" s="5" t="n"/>
+      <c r="S215" s="5" t="n"/>
+      <c r="T215" s="7" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="5" t="n"/>
@@ -5450,7 +5925,9 @@
       <c r="O216" s="5" t="n"/>
       <c r="P216" s="5" t="n"/>
       <c r="Q216" s="5" t="n"/>
-      <c r="R216" s="7" t="n"/>
+      <c r="R216" s="5" t="n"/>
+      <c r="S216" s="5" t="n"/>
+      <c r="T216" s="7" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="5" t="n"/>
@@ -5470,7 +5947,9 @@
       <c r="O217" s="5" t="n"/>
       <c r="P217" s="5" t="n"/>
       <c r="Q217" s="5" t="n"/>
-      <c r="R217" s="7" t="n"/>
+      <c r="R217" s="5" t="n"/>
+      <c r="S217" s="5" t="n"/>
+      <c r="T217" s="7" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="5" t="n"/>
@@ -5490,7 +5969,9 @@
       <c r="O218" s="5" t="n"/>
       <c r="P218" s="5" t="n"/>
       <c r="Q218" s="5" t="n"/>
-      <c r="R218" s="7" t="n"/>
+      <c r="R218" s="5" t="n"/>
+      <c r="S218" s="5" t="n"/>
+      <c r="T218" s="7" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="5" t="n"/>
@@ -5510,7 +5991,9 @@
       <c r="O219" s="5" t="n"/>
       <c r="P219" s="5" t="n"/>
       <c r="Q219" s="5" t="n"/>
-      <c r="R219" s="7" t="n"/>
+      <c r="R219" s="5" t="n"/>
+      <c r="S219" s="5" t="n"/>
+      <c r="T219" s="7" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="5" t="n"/>
@@ -5530,7 +6013,9 @@
       <c r="O220" s="5" t="n"/>
       <c r="P220" s="5" t="n"/>
       <c r="Q220" s="5" t="n"/>
-      <c r="R220" s="7" t="n"/>
+      <c r="R220" s="5" t="n"/>
+      <c r="S220" s="5" t="n"/>
+      <c r="T220" s="7" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="5" t="n"/>
@@ -5550,7 +6035,9 @@
       <c r="O221" s="5" t="n"/>
       <c r="P221" s="5" t="n"/>
       <c r="Q221" s="5" t="n"/>
-      <c r="R221" s="7" t="n"/>
+      <c r="R221" s="5" t="n"/>
+      <c r="S221" s="5" t="n"/>
+      <c r="T221" s="7" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="5" t="n"/>
@@ -5570,7 +6057,9 @@
       <c r="O222" s="5" t="n"/>
       <c r="P222" s="5" t="n"/>
       <c r="Q222" s="5" t="n"/>
-      <c r="R222" s="7" t="n"/>
+      <c r="R222" s="5" t="n"/>
+      <c r="S222" s="5" t="n"/>
+      <c r="T222" s="7" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="5" t="n"/>
@@ -5590,7 +6079,9 @@
       <c r="O223" s="5" t="n"/>
       <c r="P223" s="5" t="n"/>
       <c r="Q223" s="5" t="n"/>
-      <c r="R223" s="7" t="n"/>
+      <c r="R223" s="5" t="n"/>
+      <c r="S223" s="5" t="n"/>
+      <c r="T223" s="7" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="5" t="n"/>
@@ -5610,7 +6101,9 @@
       <c r="O224" s="5" t="n"/>
       <c r="P224" s="5" t="n"/>
       <c r="Q224" s="5" t="n"/>
-      <c r="R224" s="7" t="n"/>
+      <c r="R224" s="5" t="n"/>
+      <c r="S224" s="5" t="n"/>
+      <c r="T224" s="7" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="5" t="n"/>
@@ -5630,7 +6123,9 @@
       <c r="O225" s="5" t="n"/>
       <c r="P225" s="5" t="n"/>
       <c r="Q225" s="5" t="n"/>
-      <c r="R225" s="7" t="n"/>
+      <c r="R225" s="5" t="n"/>
+      <c r="S225" s="5" t="n"/>
+      <c r="T225" s="7" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="5" t="n"/>
@@ -5650,7 +6145,9 @@
       <c r="O226" s="5" t="n"/>
       <c r="P226" s="5" t="n"/>
       <c r="Q226" s="5" t="n"/>
-      <c r="R226" s="7" t="n"/>
+      <c r="R226" s="5" t="n"/>
+      <c r="S226" s="5" t="n"/>
+      <c r="T226" s="7" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="5" t="n"/>
@@ -5670,7 +6167,9 @@
       <c r="O227" s="5" t="n"/>
       <c r="P227" s="5" t="n"/>
       <c r="Q227" s="5" t="n"/>
-      <c r="R227" s="7" t="n"/>
+      <c r="R227" s="5" t="n"/>
+      <c r="S227" s="5" t="n"/>
+      <c r="T227" s="7" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="5" t="n"/>
@@ -5690,7 +6189,9 @@
       <c r="O228" s="5" t="n"/>
       <c r="P228" s="5" t="n"/>
       <c r="Q228" s="5" t="n"/>
-      <c r="R228" s="7" t="n"/>
+      <c r="R228" s="5" t="n"/>
+      <c r="S228" s="5" t="n"/>
+      <c r="T228" s="7" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="5" t="n"/>
@@ -5710,7 +6211,9 @@
       <c r="O229" s="5" t="n"/>
       <c r="P229" s="5" t="n"/>
       <c r="Q229" s="5" t="n"/>
-      <c r="R229" s="7" t="n"/>
+      <c r="R229" s="5" t="n"/>
+      <c r="S229" s="5" t="n"/>
+      <c r="T229" s="7" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="5" t="n"/>
@@ -5730,7 +6233,9 @@
       <c r="O230" s="5" t="n"/>
       <c r="P230" s="5" t="n"/>
       <c r="Q230" s="5" t="n"/>
-      <c r="R230" s="7" t="n"/>
+      <c r="R230" s="5" t="n"/>
+      <c r="S230" s="5" t="n"/>
+      <c r="T230" s="7" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="5" t="n"/>
@@ -5750,7 +6255,9 @@
       <c r="O231" s="5" t="n"/>
       <c r="P231" s="5" t="n"/>
       <c r="Q231" s="5" t="n"/>
-      <c r="R231" s="7" t="n"/>
+      <c r="R231" s="5" t="n"/>
+      <c r="S231" s="5" t="n"/>
+      <c r="T231" s="7" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="5" t="n"/>
@@ -5770,7 +6277,9 @@
       <c r="O232" s="5" t="n"/>
       <c r="P232" s="5" t="n"/>
       <c r="Q232" s="5" t="n"/>
-      <c r="R232" s="7" t="n"/>
+      <c r="R232" s="5" t="n"/>
+      <c r="S232" s="5" t="n"/>
+      <c r="T232" s="7" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="5" t="n"/>
@@ -5790,7 +6299,9 @@
       <c r="O233" s="5" t="n"/>
       <c r="P233" s="5" t="n"/>
       <c r="Q233" s="5" t="n"/>
-      <c r="R233" s="7" t="n"/>
+      <c r="R233" s="5" t="n"/>
+      <c r="S233" s="5" t="n"/>
+      <c r="T233" s="7" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="5" t="n"/>
@@ -5810,7 +6321,9 @@
       <c r="O234" s="5" t="n"/>
       <c r="P234" s="5" t="n"/>
       <c r="Q234" s="5" t="n"/>
-      <c r="R234" s="7" t="n"/>
+      <c r="R234" s="5" t="n"/>
+      <c r="S234" s="5" t="n"/>
+      <c r="T234" s="7" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="5" t="n"/>
@@ -5830,7 +6343,9 @@
       <c r="O235" s="5" t="n"/>
       <c r="P235" s="5" t="n"/>
       <c r="Q235" s="5" t="n"/>
-      <c r="R235" s="7" t="n"/>
+      <c r="R235" s="5" t="n"/>
+      <c r="S235" s="5" t="n"/>
+      <c r="T235" s="7" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="5" t="n"/>
@@ -5850,7 +6365,9 @@
       <c r="O236" s="5" t="n"/>
       <c r="P236" s="5" t="n"/>
       <c r="Q236" s="5" t="n"/>
-      <c r="R236" s="7" t="n"/>
+      <c r="R236" s="5" t="n"/>
+      <c r="S236" s="5" t="n"/>
+      <c r="T236" s="7" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="5" t="n"/>
@@ -5870,7 +6387,9 @@
       <c r="O237" s="5" t="n"/>
       <c r="P237" s="5" t="n"/>
       <c r="Q237" s="5" t="n"/>
-      <c r="R237" s="7" t="n"/>
+      <c r="R237" s="5" t="n"/>
+      <c r="S237" s="5" t="n"/>
+      <c r="T237" s="7" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="5" t="n"/>
@@ -5890,7 +6409,9 @@
       <c r="O238" s="5" t="n"/>
       <c r="P238" s="5" t="n"/>
       <c r="Q238" s="5" t="n"/>
-      <c r="R238" s="7" t="n"/>
+      <c r="R238" s="5" t="n"/>
+      <c r="S238" s="5" t="n"/>
+      <c r="T238" s="7" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="5" t="n"/>
@@ -5910,7 +6431,9 @@
       <c r="O239" s="5" t="n"/>
       <c r="P239" s="5" t="n"/>
       <c r="Q239" s="5" t="n"/>
-      <c r="R239" s="7" t="n"/>
+      <c r="R239" s="5" t="n"/>
+      <c r="S239" s="5" t="n"/>
+      <c r="T239" s="7" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="5" t="n"/>
@@ -5930,7 +6453,9 @@
       <c r="O240" s="5" t="n"/>
       <c r="P240" s="5" t="n"/>
       <c r="Q240" s="5" t="n"/>
-      <c r="R240" s="7" t="n"/>
+      <c r="R240" s="5" t="n"/>
+      <c r="S240" s="5" t="n"/>
+      <c r="T240" s="7" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="5" t="n"/>
@@ -5950,7 +6475,9 @@
       <c r="O241" s="5" t="n"/>
       <c r="P241" s="5" t="n"/>
       <c r="Q241" s="5" t="n"/>
-      <c r="R241" s="7" t="n"/>
+      <c r="R241" s="5" t="n"/>
+      <c r="S241" s="5" t="n"/>
+      <c r="T241" s="7" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="5" t="n"/>
@@ -5970,7 +6497,9 @@
       <c r="O242" s="5" t="n"/>
       <c r="P242" s="5" t="n"/>
       <c r="Q242" s="5" t="n"/>
-      <c r="R242" s="7" t="n"/>
+      <c r="R242" s="5" t="n"/>
+      <c r="S242" s="5" t="n"/>
+      <c r="T242" s="7" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="5" t="n"/>
@@ -5990,7 +6519,9 @@
       <c r="O243" s="5" t="n"/>
       <c r="P243" s="5" t="n"/>
       <c r="Q243" s="5" t="n"/>
-      <c r="R243" s="7" t="n"/>
+      <c r="R243" s="5" t="n"/>
+      <c r="S243" s="5" t="n"/>
+      <c r="T243" s="7" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="5" t="n"/>
@@ -6010,7 +6541,9 @@
       <c r="O244" s="5" t="n"/>
       <c r="P244" s="5" t="n"/>
       <c r="Q244" s="5" t="n"/>
-      <c r="R244" s="7" t="n"/>
+      <c r="R244" s="5" t="n"/>
+      <c r="S244" s="5" t="n"/>
+      <c r="T244" s="7" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="5" t="n"/>
@@ -6030,7 +6563,9 @@
       <c r="O245" s="5" t="n"/>
       <c r="P245" s="5" t="n"/>
       <c r="Q245" s="5" t="n"/>
-      <c r="R245" s="7" t="n"/>
+      <c r="R245" s="5" t="n"/>
+      <c r="S245" s="5" t="n"/>
+      <c r="T245" s="7" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="5" t="n"/>
@@ -6050,7 +6585,9 @@
       <c r="O246" s="5" t="n"/>
       <c r="P246" s="5" t="n"/>
       <c r="Q246" s="5" t="n"/>
-      <c r="R246" s="7" t="n"/>
+      <c r="R246" s="5" t="n"/>
+      <c r="S246" s="5" t="n"/>
+      <c r="T246" s="7" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="5" t="n"/>
@@ -6070,7 +6607,9 @@
       <c r="O247" s="5" t="n"/>
       <c r="P247" s="5" t="n"/>
       <c r="Q247" s="5" t="n"/>
-      <c r="R247" s="7" t="n"/>
+      <c r="R247" s="5" t="n"/>
+      <c r="S247" s="5" t="n"/>
+      <c r="T247" s="7" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="5" t="n"/>
@@ -6090,7 +6629,9 @@
       <c r="O248" s="5" t="n"/>
       <c r="P248" s="5" t="n"/>
       <c r="Q248" s="5" t="n"/>
-      <c r="R248" s="7" t="n"/>
+      <c r="R248" s="5" t="n"/>
+      <c r="S248" s="5" t="n"/>
+      <c r="T248" s="7" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="5" t="n"/>
@@ -6110,7 +6651,9 @@
       <c r="O249" s="5" t="n"/>
       <c r="P249" s="5" t="n"/>
       <c r="Q249" s="5" t="n"/>
-      <c r="R249" s="7" t="n"/>
+      <c r="R249" s="5" t="n"/>
+      <c r="S249" s="5" t="n"/>
+      <c r="T249" s="7" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="5" t="n"/>
@@ -6130,7 +6673,9 @@
       <c r="O250" s="5" t="n"/>
       <c r="P250" s="5" t="n"/>
       <c r="Q250" s="5" t="n"/>
-      <c r="R250" s="7" t="n"/>
+      <c r="R250" s="5" t="n"/>
+      <c r="S250" s="5" t="n"/>
+      <c r="T250" s="7" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="5" t="n"/>
@@ -6150,7 +6695,9 @@
       <c r="O251" s="5" t="n"/>
       <c r="P251" s="5" t="n"/>
       <c r="Q251" s="5" t="n"/>
-      <c r="R251" s="7" t="n"/>
+      <c r="R251" s="5" t="n"/>
+      <c r="S251" s="5" t="n"/>
+      <c r="T251" s="7" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="5" t="n"/>
@@ -6170,7 +6717,9 @@
       <c r="O252" s="5" t="n"/>
       <c r="P252" s="5" t="n"/>
       <c r="Q252" s="5" t="n"/>
-      <c r="R252" s="7" t="n"/>
+      <c r="R252" s="5" t="n"/>
+      <c r="S252" s="5" t="n"/>
+      <c r="T252" s="7" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="5" t="n"/>
@@ -6190,7 +6739,9 @@
       <c r="O253" s="5" t="n"/>
       <c r="P253" s="5" t="n"/>
       <c r="Q253" s="5" t="n"/>
-      <c r="R253" s="7" t="n"/>
+      <c r="R253" s="5" t="n"/>
+      <c r="S253" s="5" t="n"/>
+      <c r="T253" s="7" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="5" t="n"/>
@@ -6210,7 +6761,9 @@
       <c r="O254" s="5" t="n"/>
       <c r="P254" s="5" t="n"/>
       <c r="Q254" s="5" t="n"/>
-      <c r="R254" s="7" t="n"/>
+      <c r="R254" s="5" t="n"/>
+      <c r="S254" s="5" t="n"/>
+      <c r="T254" s="7" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="5" t="n"/>
@@ -6230,7 +6783,9 @@
       <c r="O255" s="5" t="n"/>
       <c r="P255" s="5" t="n"/>
       <c r="Q255" s="5" t="n"/>
-      <c r="R255" s="7" t="n"/>
+      <c r="R255" s="5" t="n"/>
+      <c r="S255" s="5" t="n"/>
+      <c r="T255" s="7" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="5" t="n"/>
@@ -6250,7 +6805,9 @@
       <c r="O256" s="5" t="n"/>
       <c r="P256" s="5" t="n"/>
       <c r="Q256" s="5" t="n"/>
-      <c r="R256" s="7" t="n"/>
+      <c r="R256" s="5" t="n"/>
+      <c r="S256" s="5" t="n"/>
+      <c r="T256" s="7" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="5" t="n"/>
@@ -6270,7 +6827,9 @@
       <c r="O257" s="5" t="n"/>
       <c r="P257" s="5" t="n"/>
       <c r="Q257" s="5" t="n"/>
-      <c r="R257" s="7" t="n"/>
+      <c r="R257" s="5" t="n"/>
+      <c r="S257" s="5" t="n"/>
+      <c r="T257" s="7" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="5" t="n"/>
@@ -6290,7 +6849,9 @@
       <c r="O258" s="5" t="n"/>
       <c r="P258" s="5" t="n"/>
       <c r="Q258" s="5" t="n"/>
-      <c r="R258" s="7" t="n"/>
+      <c r="R258" s="5" t="n"/>
+      <c r="S258" s="5" t="n"/>
+      <c r="T258" s="7" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="5" t="n"/>
@@ -6310,7 +6871,9 @@
       <c r="O259" s="5" t="n"/>
       <c r="P259" s="5" t="n"/>
       <c r="Q259" s="5" t="n"/>
-      <c r="R259" s="7" t="n"/>
+      <c r="R259" s="5" t="n"/>
+      <c r="S259" s="5" t="n"/>
+      <c r="T259" s="7" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="5" t="n"/>
@@ -6330,7 +6893,9 @@
       <c r="O260" s="5" t="n"/>
       <c r="P260" s="5" t="n"/>
       <c r="Q260" s="5" t="n"/>
-      <c r="R260" s="7" t="n"/>
+      <c r="R260" s="5" t="n"/>
+      <c r="S260" s="5" t="n"/>
+      <c r="T260" s="7" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="5" t="n"/>
@@ -6350,7 +6915,9 @@
       <c r="O261" s="5" t="n"/>
       <c r="P261" s="5" t="n"/>
       <c r="Q261" s="5" t="n"/>
-      <c r="R261" s="7" t="n"/>
+      <c r="R261" s="5" t="n"/>
+      <c r="S261" s="5" t="n"/>
+      <c r="T261" s="7" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="5" t="n"/>
@@ -6370,7 +6937,9 @@
       <c r="O262" s="5" t="n"/>
       <c r="P262" s="5" t="n"/>
       <c r="Q262" s="5" t="n"/>
-      <c r="R262" s="7" t="n"/>
+      <c r="R262" s="5" t="n"/>
+      <c r="S262" s="5" t="n"/>
+      <c r="T262" s="7" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="5" t="n"/>
@@ -6390,7 +6959,9 @@
       <c r="O263" s="5" t="n"/>
       <c r="P263" s="5" t="n"/>
       <c r="Q263" s="5" t="n"/>
-      <c r="R263" s="7" t="n"/>
+      <c r="R263" s="5" t="n"/>
+      <c r="S263" s="5" t="n"/>
+      <c r="T263" s="7" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="5" t="n"/>
@@ -6410,7 +6981,9 @@
       <c r="O264" s="5" t="n"/>
       <c r="P264" s="5" t="n"/>
       <c r="Q264" s="5" t="n"/>
-      <c r="R264" s="7" t="n"/>
+      <c r="R264" s="5" t="n"/>
+      <c r="S264" s="5" t="n"/>
+      <c r="T264" s="7" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="5" t="n"/>
@@ -6430,7 +7003,9 @@
       <c r="O265" s="5" t="n"/>
       <c r="P265" s="5" t="n"/>
       <c r="Q265" s="5" t="n"/>
-      <c r="R265" s="7" t="n"/>
+      <c r="R265" s="5" t="n"/>
+      <c r="S265" s="5" t="n"/>
+      <c r="T265" s="7" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="5" t="n"/>
@@ -6450,7 +7025,9 @@
       <c r="O266" s="5" t="n"/>
       <c r="P266" s="5" t="n"/>
       <c r="Q266" s="5" t="n"/>
-      <c r="R266" s="7" t="n"/>
+      <c r="R266" s="5" t="n"/>
+      <c r="S266" s="5" t="n"/>
+      <c r="T266" s="7" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="5" t="n"/>
@@ -6470,7 +7047,9 @@
       <c r="O267" s="5" t="n"/>
       <c r="P267" s="5" t="n"/>
       <c r="Q267" s="5" t="n"/>
-      <c r="R267" s="7" t="n"/>
+      <c r="R267" s="5" t="n"/>
+      <c r="S267" s="5" t="n"/>
+      <c r="T267" s="7" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="5" t="n"/>
@@ -6490,7 +7069,9 @@
       <c r="O268" s="5" t="n"/>
       <c r="P268" s="5" t="n"/>
       <c r="Q268" s="5" t="n"/>
-      <c r="R268" s="7" t="n"/>
+      <c r="R268" s="5" t="n"/>
+      <c r="S268" s="5" t="n"/>
+      <c r="T268" s="7" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="5" t="n"/>
@@ -6510,7 +7091,9 @@
       <c r="O269" s="5" t="n"/>
       <c r="P269" s="5" t="n"/>
       <c r="Q269" s="5" t="n"/>
-      <c r="R269" s="7" t="n"/>
+      <c r="R269" s="5" t="n"/>
+      <c r="S269" s="5" t="n"/>
+      <c r="T269" s="7" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="5" t="n"/>
@@ -6530,7 +7113,9 @@
       <c r="O270" s="5" t="n"/>
       <c r="P270" s="5" t="n"/>
       <c r="Q270" s="5" t="n"/>
-      <c r="R270" s="7" t="n"/>
+      <c r="R270" s="5" t="n"/>
+      <c r="S270" s="5" t="n"/>
+      <c r="T270" s="7" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="5" t="n"/>
@@ -6550,7 +7135,9 @@
       <c r="O271" s="5" t="n"/>
       <c r="P271" s="5" t="n"/>
       <c r="Q271" s="5" t="n"/>
-      <c r="R271" s="7" t="n"/>
+      <c r="R271" s="5" t="n"/>
+      <c r="S271" s="5" t="n"/>
+      <c r="T271" s="7" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="5" t="n"/>
@@ -6570,7 +7157,9 @@
       <c r="O272" s="5" t="n"/>
       <c r="P272" s="5" t="n"/>
       <c r="Q272" s="5" t="n"/>
-      <c r="R272" s="7" t="n"/>
+      <c r="R272" s="5" t="n"/>
+      <c r="S272" s="5" t="n"/>
+      <c r="T272" s="7" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="5" t="n"/>
@@ -6590,7 +7179,9 @@
       <c r="O273" s="5" t="n"/>
       <c r="P273" s="5" t="n"/>
       <c r="Q273" s="5" t="n"/>
-      <c r="R273" s="7" t="n"/>
+      <c r="R273" s="5" t="n"/>
+      <c r="S273" s="5" t="n"/>
+      <c r="T273" s="7" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="5" t="n"/>
@@ -6610,7 +7201,9 @@
       <c r="O274" s="5" t="n"/>
       <c r="P274" s="5" t="n"/>
       <c r="Q274" s="5" t="n"/>
-      <c r="R274" s="7" t="n"/>
+      <c r="R274" s="5" t="n"/>
+      <c r="S274" s="5" t="n"/>
+      <c r="T274" s="7" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="5" t="n"/>
@@ -6630,7 +7223,9 @@
       <c r="O275" s="5" t="n"/>
       <c r="P275" s="5" t="n"/>
       <c r="Q275" s="5" t="n"/>
-      <c r="R275" s="7" t="n"/>
+      <c r="R275" s="5" t="n"/>
+      <c r="S275" s="5" t="n"/>
+      <c r="T275" s="7" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="5" t="n"/>
@@ -6650,7 +7245,9 @@
       <c r="O276" s="5" t="n"/>
       <c r="P276" s="5" t="n"/>
       <c r="Q276" s="5" t="n"/>
-      <c r="R276" s="7" t="n"/>
+      <c r="R276" s="5" t="n"/>
+      <c r="S276" s="5" t="n"/>
+      <c r="T276" s="7" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="5" t="n"/>
@@ -6670,7 +7267,9 @@
       <c r="O277" s="5" t="n"/>
       <c r="P277" s="5" t="n"/>
       <c r="Q277" s="5" t="n"/>
-      <c r="R277" s="7" t="n"/>
+      <c r="R277" s="5" t="n"/>
+      <c r="S277" s="5" t="n"/>
+      <c r="T277" s="7" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="5" t="n"/>
@@ -6690,7 +7289,9 @@
       <c r="O278" s="5" t="n"/>
       <c r="P278" s="5" t="n"/>
       <c r="Q278" s="5" t="n"/>
-      <c r="R278" s="7" t="n"/>
+      <c r="R278" s="5" t="n"/>
+      <c r="S278" s="5" t="n"/>
+      <c r="T278" s="7" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="5" t="n"/>
@@ -6710,7 +7311,9 @@
       <c r="O279" s="5" t="n"/>
       <c r="P279" s="5" t="n"/>
       <c r="Q279" s="5" t="n"/>
-      <c r="R279" s="7" t="n"/>
+      <c r="R279" s="5" t="n"/>
+      <c r="S279" s="5" t="n"/>
+      <c r="T279" s="7" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="5" t="n"/>
@@ -6730,7 +7333,9 @@
       <c r="O280" s="5" t="n"/>
       <c r="P280" s="5" t="n"/>
       <c r="Q280" s="5" t="n"/>
-      <c r="R280" s="7" t="n"/>
+      <c r="R280" s="5" t="n"/>
+      <c r="S280" s="5" t="n"/>
+      <c r="T280" s="7" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="5" t="n"/>
@@ -6750,7 +7355,9 @@
       <c r="O281" s="5" t="n"/>
       <c r="P281" s="5" t="n"/>
       <c r="Q281" s="5" t="n"/>
-      <c r="R281" s="7" t="n"/>
+      <c r="R281" s="5" t="n"/>
+      <c r="S281" s="5" t="n"/>
+      <c r="T281" s="7" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="5" t="n"/>
@@ -6770,7 +7377,9 @@
       <c r="O282" s="5" t="n"/>
       <c r="P282" s="5" t="n"/>
       <c r="Q282" s="5" t="n"/>
-      <c r="R282" s="7" t="n"/>
+      <c r="R282" s="5" t="n"/>
+      <c r="S282" s="5" t="n"/>
+      <c r="T282" s="7" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="5" t="n"/>
@@ -6790,7 +7399,9 @@
       <c r="O283" s="5" t="n"/>
       <c r="P283" s="5" t="n"/>
       <c r="Q283" s="5" t="n"/>
-      <c r="R283" s="7" t="n"/>
+      <c r="R283" s="5" t="n"/>
+      <c r="S283" s="5" t="n"/>
+      <c r="T283" s="7" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="5" t="n"/>
@@ -6810,7 +7421,9 @@
       <c r="O284" s="5" t="n"/>
       <c r="P284" s="5" t="n"/>
       <c r="Q284" s="5" t="n"/>
-      <c r="R284" s="7" t="n"/>
+      <c r="R284" s="5" t="n"/>
+      <c r="S284" s="5" t="n"/>
+      <c r="T284" s="7" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="5" t="n"/>
@@ -6830,7 +7443,9 @@
       <c r="O285" s="5" t="n"/>
       <c r="P285" s="5" t="n"/>
       <c r="Q285" s="5" t="n"/>
-      <c r="R285" s="7" t="n"/>
+      <c r="R285" s="5" t="n"/>
+      <c r="S285" s="5" t="n"/>
+      <c r="T285" s="7" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="5" t="n"/>
@@ -6850,7 +7465,9 @@
       <c r="O286" s="5" t="n"/>
       <c r="P286" s="5" t="n"/>
       <c r="Q286" s="5" t="n"/>
-      <c r="R286" s="7" t="n"/>
+      <c r="R286" s="5" t="n"/>
+      <c r="S286" s="5" t="n"/>
+      <c r="T286" s="7" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="5" t="n"/>
@@ -6870,7 +7487,9 @@
       <c r="O287" s="5" t="n"/>
       <c r="P287" s="5" t="n"/>
       <c r="Q287" s="5" t="n"/>
-      <c r="R287" s="7" t="n"/>
+      <c r="R287" s="5" t="n"/>
+      <c r="S287" s="5" t="n"/>
+      <c r="T287" s="7" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="5" t="n"/>
@@ -6890,7 +7509,9 @@
       <c r="O288" s="5" t="n"/>
       <c r="P288" s="5" t="n"/>
       <c r="Q288" s="5" t="n"/>
-      <c r="R288" s="7" t="n"/>
+      <c r="R288" s="5" t="n"/>
+      <c r="S288" s="5" t="n"/>
+      <c r="T288" s="7" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="5" t="n"/>
@@ -6910,7 +7531,9 @@
       <c r="O289" s="5" t="n"/>
       <c r="P289" s="5" t="n"/>
       <c r="Q289" s="5" t="n"/>
-      <c r="R289" s="7" t="n"/>
+      <c r="R289" s="5" t="n"/>
+      <c r="S289" s="5" t="n"/>
+      <c r="T289" s="7" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="5" t="n"/>
@@ -6930,7 +7553,9 @@
       <c r="O290" s="5" t="n"/>
       <c r="P290" s="5" t="n"/>
       <c r="Q290" s="5" t="n"/>
-      <c r="R290" s="7" t="n"/>
+      <c r="R290" s="5" t="n"/>
+      <c r="S290" s="5" t="n"/>
+      <c r="T290" s="7" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="5" t="n"/>
@@ -6950,7 +7575,9 @@
       <c r="O291" s="5" t="n"/>
       <c r="P291" s="5" t="n"/>
       <c r="Q291" s="5" t="n"/>
-      <c r="R291" s="7" t="n"/>
+      <c r="R291" s="5" t="n"/>
+      <c r="S291" s="5" t="n"/>
+      <c r="T291" s="7" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="5" t="n"/>
@@ -6970,7 +7597,9 @@
       <c r="O292" s="5" t="n"/>
       <c r="P292" s="5" t="n"/>
       <c r="Q292" s="5" t="n"/>
-      <c r="R292" s="7" t="n"/>
+      <c r="R292" s="5" t="n"/>
+      <c r="S292" s="5" t="n"/>
+      <c r="T292" s="7" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="5" t="n"/>
@@ -6990,7 +7619,9 @@
       <c r="O293" s="5" t="n"/>
       <c r="P293" s="5" t="n"/>
       <c r="Q293" s="5" t="n"/>
-      <c r="R293" s="7" t="n"/>
+      <c r="R293" s="5" t="n"/>
+      <c r="S293" s="5" t="n"/>
+      <c r="T293" s="7" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="5" t="n"/>
@@ -7010,7 +7641,9 @@
       <c r="O294" s="5" t="n"/>
       <c r="P294" s="5" t="n"/>
       <c r="Q294" s="5" t="n"/>
-      <c r="R294" s="7" t="n"/>
+      <c r="R294" s="5" t="n"/>
+      <c r="S294" s="5" t="n"/>
+      <c r="T294" s="7" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="5" t="n"/>
@@ -7030,7 +7663,9 @@
       <c r="O295" s="5" t="n"/>
       <c r="P295" s="5" t="n"/>
       <c r="Q295" s="5" t="n"/>
-      <c r="R295" s="7" t="n"/>
+      <c r="R295" s="5" t="n"/>
+      <c r="S295" s="5" t="n"/>
+      <c r="T295" s="7" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="5" t="n"/>
@@ -7050,7 +7685,9 @@
       <c r="O296" s="5" t="n"/>
       <c r="P296" s="5" t="n"/>
       <c r="Q296" s="5" t="n"/>
-      <c r="R296" s="7" t="n"/>
+      <c r="R296" s="5" t="n"/>
+      <c r="S296" s="5" t="n"/>
+      <c r="T296" s="7" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="5" t="n"/>
@@ -7070,7 +7707,9 @@
       <c r="O297" s="5" t="n"/>
       <c r="P297" s="5" t="n"/>
       <c r="Q297" s="5" t="n"/>
-      <c r="R297" s="7" t="n"/>
+      <c r="R297" s="5" t="n"/>
+      <c r="S297" s="5" t="n"/>
+      <c r="T297" s="7" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="5" t="n"/>
@@ -7090,7 +7729,9 @@
       <c r="O298" s="5" t="n"/>
       <c r="P298" s="5" t="n"/>
       <c r="Q298" s="5" t="n"/>
-      <c r="R298" s="7" t="n"/>
+      <c r="R298" s="5" t="n"/>
+      <c r="S298" s="5" t="n"/>
+      <c r="T298" s="7" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="5" t="n"/>
@@ -7110,7 +7751,9 @@
       <c r="O299" s="5" t="n"/>
       <c r="P299" s="5" t="n"/>
       <c r="Q299" s="5" t="n"/>
-      <c r="R299" s="7" t="n"/>
+      <c r="R299" s="5" t="n"/>
+      <c r="S299" s="5" t="n"/>
+      <c r="T299" s="7" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="5" t="n"/>
@@ -7130,7 +7773,9 @@
       <c r="O300" s="5" t="n"/>
       <c r="P300" s="5" t="n"/>
       <c r="Q300" s="5" t="n"/>
-      <c r="R300" s="7" t="n"/>
+      <c r="R300" s="5" t="n"/>
+      <c r="S300" s="5" t="n"/>
+      <c r="T300" s="7" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="6">
@@ -7140,16 +7785,16 @@
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"current,alumni"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
     <dataValidation sqref="P2:P500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R2:R500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="S2:S500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11018,7 +11663,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -16404,7 +17049,7 @@
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
@@ -23880,4 +24525,2150 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E300"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="7" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n"/>
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n"/>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n"/>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n"/>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n"/>
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n"/>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n"/>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n"/>
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="7" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n"/>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n"/>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="7" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n"/>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n"/>
+      <c r="B60" s="5" t="n"/>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="7" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n"/>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n"/>
+      <c r="B62" s="5" t="n"/>
+      <c r="C62" s="5" t="n"/>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="7" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n"/>
+      <c r="B63" s="5" t="n"/>
+      <c r="C63" s="5" t="n"/>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="7" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n"/>
+      <c r="B64" s="5" t="n"/>
+      <c r="C64" s="5" t="n"/>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="7" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n"/>
+      <c r="B65" s="5" t="n"/>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="7" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n"/>
+      <c r="B66" s="5" t="n"/>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="7" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n"/>
+      <c r="B67" s="5" t="n"/>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="7" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n"/>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="7" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n"/>
+      <c r="B69" s="5" t="n"/>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="7" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n"/>
+      <c r="B70" s="5" t="n"/>
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="7" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n"/>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n"/>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="7" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n"/>
+      <c r="B73" s="5" t="n"/>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n"/>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="7" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n"/>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n"/>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="7" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n"/>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="7" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n"/>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="7" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n"/>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="5" t="n"/>
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="n"/>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="7" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n"/>
+      <c r="B81" s="5" t="n"/>
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="5" t="n"/>
+      <c r="E81" s="7" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n"/>
+      <c r="B82" s="5" t="n"/>
+      <c r="C82" s="5" t="n"/>
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="7" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n"/>
+      <c r="B83" s="5" t="n"/>
+      <c r="C83" s="5" t="n"/>
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="7" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n"/>
+      <c r="B84" s="5" t="n"/>
+      <c r="C84" s="5" t="n"/>
+      <c r="D84" s="5" t="n"/>
+      <c r="E84" s="7" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n"/>
+      <c r="B85" s="5" t="n"/>
+      <c r="C85" s="5" t="n"/>
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="7" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n"/>
+      <c r="B86" s="5" t="n"/>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="7" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n"/>
+      <c r="B87" s="5" t="n"/>
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="7" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n"/>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="7" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n"/>
+      <c r="B89" s="5" t="n"/>
+      <c r="C89" s="5" t="n"/>
+      <c r="D89" s="5" t="n"/>
+      <c r="E89" s="7" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n"/>
+      <c r="B90" s="5" t="n"/>
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="5" t="n"/>
+      <c r="E90" s="7" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n"/>
+      <c r="B91" s="5" t="n"/>
+      <c r="C91" s="5" t="n"/>
+      <c r="D91" s="5" t="n"/>
+      <c r="E91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n"/>
+      <c r="B92" s="5" t="n"/>
+      <c r="C92" s="5" t="n"/>
+      <c r="D92" s="5" t="n"/>
+      <c r="E92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n"/>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="7" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n"/>
+      <c r="B94" s="5" t="n"/>
+      <c r="C94" s="5" t="n"/>
+      <c r="D94" s="5" t="n"/>
+      <c r="E94" s="7" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n"/>
+      <c r="B95" s="5" t="n"/>
+      <c r="C95" s="5" t="n"/>
+      <c r="D95" s="5" t="n"/>
+      <c r="E95" s="7" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n"/>
+      <c r="B96" s="5" t="n"/>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="7" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n"/>
+      <c r="B97" s="5" t="n"/>
+      <c r="C97" s="5" t="n"/>
+      <c r="D97" s="5" t="n"/>
+      <c r="E97" s="7" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n"/>
+      <c r="B98" s="5" t="n"/>
+      <c r="C98" s="5" t="n"/>
+      <c r="D98" s="5" t="n"/>
+      <c r="E98" s="7" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n"/>
+      <c r="B99" s="5" t="n"/>
+      <c r="C99" s="5" t="n"/>
+      <c r="D99" s="5" t="n"/>
+      <c r="E99" s="7" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n"/>
+      <c r="B100" s="5" t="n"/>
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="5" t="n"/>
+      <c r="E100" s="7" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n"/>
+      <c r="B101" s="5" t="n"/>
+      <c r="C101" s="5" t="n"/>
+      <c r="D101" s="5" t="n"/>
+      <c r="E101" s="7" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n"/>
+      <c r="B102" s="5" t="n"/>
+      <c r="C102" s="5" t="n"/>
+      <c r="D102" s="5" t="n"/>
+      <c r="E102" s="7" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n"/>
+      <c r="B103" s="5" t="n"/>
+      <c r="C103" s="5" t="n"/>
+      <c r="D103" s="5" t="n"/>
+      <c r="E103" s="7" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n"/>
+      <c r="B104" s="5" t="n"/>
+      <c r="C104" s="5" t="n"/>
+      <c r="D104" s="5" t="n"/>
+      <c r="E104" s="7" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="n"/>
+      <c r="B105" s="5" t="n"/>
+      <c r="C105" s="5" t="n"/>
+      <c r="D105" s="5" t="n"/>
+      <c r="E105" s="7" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n"/>
+      <c r="B106" s="5" t="n"/>
+      <c r="C106" s="5" t="n"/>
+      <c r="D106" s="5" t="n"/>
+      <c r="E106" s="7" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n"/>
+      <c r="B107" s="5" t="n"/>
+      <c r="C107" s="5" t="n"/>
+      <c r="D107" s="5" t="n"/>
+      <c r="E107" s="7" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n"/>
+      <c r="B108" s="5" t="n"/>
+      <c r="C108" s="5" t="n"/>
+      <c r="D108" s="5" t="n"/>
+      <c r="E108" s="7" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n"/>
+      <c r="B109" s="5" t="n"/>
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="5" t="n"/>
+      <c r="E109" s="7" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="n"/>
+      <c r="B110" s="5" t="n"/>
+      <c r="C110" s="5" t="n"/>
+      <c r="D110" s="5" t="n"/>
+      <c r="E110" s="7" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n"/>
+      <c r="B111" s="5" t="n"/>
+      <c r="C111" s="5" t="n"/>
+      <c r="D111" s="5" t="n"/>
+      <c r="E111" s="7" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="n"/>
+      <c r="B112" s="5" t="n"/>
+      <c r="C112" s="5" t="n"/>
+      <c r="D112" s="5" t="n"/>
+      <c r="E112" s="7" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n"/>
+      <c r="B113" s="5" t="n"/>
+      <c r="C113" s="5" t="n"/>
+      <c r="D113" s="5" t="n"/>
+      <c r="E113" s="7" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n"/>
+      <c r="B114" s="5" t="n"/>
+      <c r="C114" s="5" t="n"/>
+      <c r="D114" s="5" t="n"/>
+      <c r="E114" s="7" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n"/>
+      <c r="B115" s="5" t="n"/>
+      <c r="C115" s="5" t="n"/>
+      <c r="D115" s="5" t="n"/>
+      <c r="E115" s="7" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n"/>
+      <c r="B116" s="5" t="n"/>
+      <c r="C116" s="5" t="n"/>
+      <c r="D116" s="5" t="n"/>
+      <c r="E116" s="7" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n"/>
+      <c r="B117" s="5" t="n"/>
+      <c r="C117" s="5" t="n"/>
+      <c r="D117" s="5" t="n"/>
+      <c r="E117" s="7" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n"/>
+      <c r="B118" s="5" t="n"/>
+      <c r="C118" s="5" t="n"/>
+      <c r="D118" s="5" t="n"/>
+      <c r="E118" s="7" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n"/>
+      <c r="B119" s="5" t="n"/>
+      <c r="C119" s="5" t="n"/>
+      <c r="D119" s="5" t="n"/>
+      <c r="E119" s="7" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n"/>
+      <c r="B120" s="5" t="n"/>
+      <c r="C120" s="5" t="n"/>
+      <c r="D120" s="5" t="n"/>
+      <c r="E120" s="7" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n"/>
+      <c r="B121" s="5" t="n"/>
+      <c r="C121" s="5" t="n"/>
+      <c r="D121" s="5" t="n"/>
+      <c r="E121" s="7" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="n"/>
+      <c r="B122" s="5" t="n"/>
+      <c r="C122" s="5" t="n"/>
+      <c r="D122" s="5" t="n"/>
+      <c r="E122" s="7" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n"/>
+      <c r="B123" s="5" t="n"/>
+      <c r="C123" s="5" t="n"/>
+      <c r="D123" s="5" t="n"/>
+      <c r="E123" s="7" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n"/>
+      <c r="B124" s="5" t="n"/>
+      <c r="C124" s="5" t="n"/>
+      <c r="D124" s="5" t="n"/>
+      <c r="E124" s="7" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n"/>
+      <c r="B125" s="5" t="n"/>
+      <c r="C125" s="5" t="n"/>
+      <c r="D125" s="5" t="n"/>
+      <c r="E125" s="7" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="n"/>
+      <c r="B126" s="5" t="n"/>
+      <c r="C126" s="5" t="n"/>
+      <c r="D126" s="5" t="n"/>
+      <c r="E126" s="7" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n"/>
+      <c r="B127" s="5" t="n"/>
+      <c r="C127" s="5" t="n"/>
+      <c r="D127" s="5" t="n"/>
+      <c r="E127" s="7" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="n"/>
+      <c r="B128" s="5" t="n"/>
+      <c r="C128" s="5" t="n"/>
+      <c r="D128" s="5" t="n"/>
+      <c r="E128" s="7" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n"/>
+      <c r="B129" s="5" t="n"/>
+      <c r="C129" s="5" t="n"/>
+      <c r="D129" s="5" t="n"/>
+      <c r="E129" s="7" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="n"/>
+      <c r="B130" s="5" t="n"/>
+      <c r="C130" s="5" t="n"/>
+      <c r="D130" s="5" t="n"/>
+      <c r="E130" s="7" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n"/>
+      <c r="B131" s="5" t="n"/>
+      <c r="C131" s="5" t="n"/>
+      <c r="D131" s="5" t="n"/>
+      <c r="E131" s="7" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="n"/>
+      <c r="B132" s="5" t="n"/>
+      <c r="C132" s="5" t="n"/>
+      <c r="D132" s="5" t="n"/>
+      <c r="E132" s="7" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n"/>
+      <c r="B133" s="5" t="n"/>
+      <c r="C133" s="5" t="n"/>
+      <c r="D133" s="5" t="n"/>
+      <c r="E133" s="7" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="n"/>
+      <c r="B134" s="5" t="n"/>
+      <c r="C134" s="5" t="n"/>
+      <c r="D134" s="5" t="n"/>
+      <c r="E134" s="7" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n"/>
+      <c r="B135" s="5" t="n"/>
+      <c r="C135" s="5" t="n"/>
+      <c r="D135" s="5" t="n"/>
+      <c r="E135" s="7" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="n"/>
+      <c r="B136" s="5" t="n"/>
+      <c r="C136" s="5" t="n"/>
+      <c r="D136" s="5" t="n"/>
+      <c r="E136" s="7" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n"/>
+      <c r="B137" s="5" t="n"/>
+      <c r="C137" s="5" t="n"/>
+      <c r="D137" s="5" t="n"/>
+      <c r="E137" s="7" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="n"/>
+      <c r="B138" s="5" t="n"/>
+      <c r="C138" s="5" t="n"/>
+      <c r="D138" s="5" t="n"/>
+      <c r="E138" s="7" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n"/>
+      <c r="B139" s="5" t="n"/>
+      <c r="C139" s="5" t="n"/>
+      <c r="D139" s="5" t="n"/>
+      <c r="E139" s="7" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="n"/>
+      <c r="B140" s="5" t="n"/>
+      <c r="C140" s="5" t="n"/>
+      <c r="D140" s="5" t="n"/>
+      <c r="E140" s="7" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n"/>
+      <c r="B141" s="5" t="n"/>
+      <c r="C141" s="5" t="n"/>
+      <c r="D141" s="5" t="n"/>
+      <c r="E141" s="7" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="n"/>
+      <c r="B142" s="5" t="n"/>
+      <c r="C142" s="5" t="n"/>
+      <c r="D142" s="5" t="n"/>
+      <c r="E142" s="7" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n"/>
+      <c r="B143" s="5" t="n"/>
+      <c r="C143" s="5" t="n"/>
+      <c r="D143" s="5" t="n"/>
+      <c r="E143" s="7" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="n"/>
+      <c r="B144" s="5" t="n"/>
+      <c r="C144" s="5" t="n"/>
+      <c r="D144" s="5" t="n"/>
+      <c r="E144" s="7" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n"/>
+      <c r="B145" s="5" t="n"/>
+      <c r="C145" s="5" t="n"/>
+      <c r="D145" s="5" t="n"/>
+      <c r="E145" s="7" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="n"/>
+      <c r="B146" s="5" t="n"/>
+      <c r="C146" s="5" t="n"/>
+      <c r="D146" s="5" t="n"/>
+      <c r="E146" s="7" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n"/>
+      <c r="B147" s="5" t="n"/>
+      <c r="C147" s="5" t="n"/>
+      <c r="D147" s="5" t="n"/>
+      <c r="E147" s="7" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="n"/>
+      <c r="B148" s="5" t="n"/>
+      <c r="C148" s="5" t="n"/>
+      <c r="D148" s="5" t="n"/>
+      <c r="E148" s="7" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n"/>
+      <c r="B149" s="5" t="n"/>
+      <c r="C149" s="5" t="n"/>
+      <c r="D149" s="5" t="n"/>
+      <c r="E149" s="7" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="n"/>
+      <c r="B150" s="5" t="n"/>
+      <c r="C150" s="5" t="n"/>
+      <c r="D150" s="5" t="n"/>
+      <c r="E150" s="7" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n"/>
+      <c r="B151" s="5" t="n"/>
+      <c r="C151" s="5" t="n"/>
+      <c r="D151" s="5" t="n"/>
+      <c r="E151" s="7" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="n"/>
+      <c r="B152" s="5" t="n"/>
+      <c r="C152" s="5" t="n"/>
+      <c r="D152" s="5" t="n"/>
+      <c r="E152" s="7" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="n"/>
+      <c r="B153" s="5" t="n"/>
+      <c r="C153" s="5" t="n"/>
+      <c r="D153" s="5" t="n"/>
+      <c r="E153" s="7" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="n"/>
+      <c r="B154" s="5" t="n"/>
+      <c r="C154" s="5" t="n"/>
+      <c r="D154" s="5" t="n"/>
+      <c r="E154" s="7" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n"/>
+      <c r="B155" s="5" t="n"/>
+      <c r="C155" s="5" t="n"/>
+      <c r="D155" s="5" t="n"/>
+      <c r="E155" s="7" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="n"/>
+      <c r="B156" s="5" t="n"/>
+      <c r="C156" s="5" t="n"/>
+      <c r="D156" s="5" t="n"/>
+      <c r="E156" s="7" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n"/>
+      <c r="B157" s="5" t="n"/>
+      <c r="C157" s="5" t="n"/>
+      <c r="D157" s="5" t="n"/>
+      <c r="E157" s="7" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="n"/>
+      <c r="B158" s="5" t="n"/>
+      <c r="C158" s="5" t="n"/>
+      <c r="D158" s="5" t="n"/>
+      <c r="E158" s="7" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="n"/>
+      <c r="B159" s="5" t="n"/>
+      <c r="C159" s="5" t="n"/>
+      <c r="D159" s="5" t="n"/>
+      <c r="E159" s="7" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="n"/>
+      <c r="B160" s="5" t="n"/>
+      <c r="C160" s="5" t="n"/>
+      <c r="D160" s="5" t="n"/>
+      <c r="E160" s="7" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="n"/>
+      <c r="B161" s="5" t="n"/>
+      <c r="C161" s="5" t="n"/>
+      <c r="D161" s="5" t="n"/>
+      <c r="E161" s="7" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="n"/>
+      <c r="B162" s="5" t="n"/>
+      <c r="C162" s="5" t="n"/>
+      <c r="D162" s="5" t="n"/>
+      <c r="E162" s="7" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="n"/>
+      <c r="B163" s="5" t="n"/>
+      <c r="C163" s="5" t="n"/>
+      <c r="D163" s="5" t="n"/>
+      <c r="E163" s="7" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="n"/>
+      <c r="B164" s="5" t="n"/>
+      <c r="C164" s="5" t="n"/>
+      <c r="D164" s="5" t="n"/>
+      <c r="E164" s="7" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="n"/>
+      <c r="B165" s="5" t="n"/>
+      <c r="C165" s="5" t="n"/>
+      <c r="D165" s="5" t="n"/>
+      <c r="E165" s="7" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="n"/>
+      <c r="B166" s="5" t="n"/>
+      <c r="C166" s="5" t="n"/>
+      <c r="D166" s="5" t="n"/>
+      <c r="E166" s="7" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="n"/>
+      <c r="B167" s="5" t="n"/>
+      <c r="C167" s="5" t="n"/>
+      <c r="D167" s="5" t="n"/>
+      <c r="E167" s="7" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="n"/>
+      <c r="B168" s="5" t="n"/>
+      <c r="C168" s="5" t="n"/>
+      <c r="D168" s="5" t="n"/>
+      <c r="E168" s="7" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="n"/>
+      <c r="B169" s="5" t="n"/>
+      <c r="C169" s="5" t="n"/>
+      <c r="D169" s="5" t="n"/>
+      <c r="E169" s="7" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="n"/>
+      <c r="B170" s="5" t="n"/>
+      <c r="C170" s="5" t="n"/>
+      <c r="D170" s="5" t="n"/>
+      <c r="E170" s="7" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="n"/>
+      <c r="B171" s="5" t="n"/>
+      <c r="C171" s="5" t="n"/>
+      <c r="D171" s="5" t="n"/>
+      <c r="E171" s="7" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="n"/>
+      <c r="B172" s="5" t="n"/>
+      <c r="C172" s="5" t="n"/>
+      <c r="D172" s="5" t="n"/>
+      <c r="E172" s="7" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="n"/>
+      <c r="B173" s="5" t="n"/>
+      <c r="C173" s="5" t="n"/>
+      <c r="D173" s="5" t="n"/>
+      <c r="E173" s="7" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="n"/>
+      <c r="B174" s="5" t="n"/>
+      <c r="C174" s="5" t="n"/>
+      <c r="D174" s="5" t="n"/>
+      <c r="E174" s="7" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="n"/>
+      <c r="B175" s="5" t="n"/>
+      <c r="C175" s="5" t="n"/>
+      <c r="D175" s="5" t="n"/>
+      <c r="E175" s="7" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n"/>
+      <c r="B176" s="5" t="n"/>
+      <c r="C176" s="5" t="n"/>
+      <c r="D176" s="5" t="n"/>
+      <c r="E176" s="7" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="n"/>
+      <c r="B177" s="5" t="n"/>
+      <c r="C177" s="5" t="n"/>
+      <c r="D177" s="5" t="n"/>
+      <c r="E177" s="7" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="n"/>
+      <c r="B178" s="5" t="n"/>
+      <c r="C178" s="5" t="n"/>
+      <c r="D178" s="5" t="n"/>
+      <c r="E178" s="7" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="n"/>
+      <c r="B179" s="5" t="n"/>
+      <c r="C179" s="5" t="n"/>
+      <c r="D179" s="5" t="n"/>
+      <c r="E179" s="7" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="n"/>
+      <c r="B180" s="5" t="n"/>
+      <c r="C180" s="5" t="n"/>
+      <c r="D180" s="5" t="n"/>
+      <c r="E180" s="7" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="n"/>
+      <c r="B181" s="5" t="n"/>
+      <c r="C181" s="5" t="n"/>
+      <c r="D181" s="5" t="n"/>
+      <c r="E181" s="7" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="n"/>
+      <c r="B182" s="5" t="n"/>
+      <c r="C182" s="5" t="n"/>
+      <c r="D182" s="5" t="n"/>
+      <c r="E182" s="7" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="n"/>
+      <c r="B183" s="5" t="n"/>
+      <c r="C183" s="5" t="n"/>
+      <c r="D183" s="5" t="n"/>
+      <c r="E183" s="7" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="n"/>
+      <c r="B184" s="5" t="n"/>
+      <c r="C184" s="5" t="n"/>
+      <c r="D184" s="5" t="n"/>
+      <c r="E184" s="7" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="n"/>
+      <c r="B185" s="5" t="n"/>
+      <c r="C185" s="5" t="n"/>
+      <c r="D185" s="5" t="n"/>
+      <c r="E185" s="7" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="n"/>
+      <c r="B186" s="5" t="n"/>
+      <c r="C186" s="5" t="n"/>
+      <c r="D186" s="5" t="n"/>
+      <c r="E186" s="7" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="n"/>
+      <c r="B187" s="5" t="n"/>
+      <c r="C187" s="5" t="n"/>
+      <c r="D187" s="5" t="n"/>
+      <c r="E187" s="7" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="n"/>
+      <c r="B188" s="5" t="n"/>
+      <c r="C188" s="5" t="n"/>
+      <c r="D188" s="5" t="n"/>
+      <c r="E188" s="7" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="n"/>
+      <c r="B189" s="5" t="n"/>
+      <c r="C189" s="5" t="n"/>
+      <c r="D189" s="5" t="n"/>
+      <c r="E189" s="7" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="n"/>
+      <c r="B190" s="5" t="n"/>
+      <c r="C190" s="5" t="n"/>
+      <c r="D190" s="5" t="n"/>
+      <c r="E190" s="7" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="n"/>
+      <c r="B191" s="5" t="n"/>
+      <c r="C191" s="5" t="n"/>
+      <c r="D191" s="5" t="n"/>
+      <c r="E191" s="7" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="n"/>
+      <c r="B192" s="5" t="n"/>
+      <c r="C192" s="5" t="n"/>
+      <c r="D192" s="5" t="n"/>
+      <c r="E192" s="7" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="n"/>
+      <c r="B193" s="5" t="n"/>
+      <c r="C193" s="5" t="n"/>
+      <c r="D193" s="5" t="n"/>
+      <c r="E193" s="7" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="n"/>
+      <c r="B194" s="5" t="n"/>
+      <c r="C194" s="5" t="n"/>
+      <c r="D194" s="5" t="n"/>
+      <c r="E194" s="7" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="n"/>
+      <c r="B195" s="5" t="n"/>
+      <c r="C195" s="5" t="n"/>
+      <c r="D195" s="5" t="n"/>
+      <c r="E195" s="7" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="n"/>
+      <c r="B196" s="5" t="n"/>
+      <c r="C196" s="5" t="n"/>
+      <c r="D196" s="5" t="n"/>
+      <c r="E196" s="7" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="n"/>
+      <c r="B197" s="5" t="n"/>
+      <c r="C197" s="5" t="n"/>
+      <c r="D197" s="5" t="n"/>
+      <c r="E197" s="7" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="n"/>
+      <c r="B198" s="5" t="n"/>
+      <c r="C198" s="5" t="n"/>
+      <c r="D198" s="5" t="n"/>
+      <c r="E198" s="7" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="n"/>
+      <c r="B199" s="5" t="n"/>
+      <c r="C199" s="5" t="n"/>
+      <c r="D199" s="5" t="n"/>
+      <c r="E199" s="7" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="n"/>
+      <c r="B200" s="5" t="n"/>
+      <c r="C200" s="5" t="n"/>
+      <c r="D200" s="5" t="n"/>
+      <c r="E200" s="7" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="n"/>
+      <c r="B201" s="5" t="n"/>
+      <c r="C201" s="5" t="n"/>
+      <c r="D201" s="5" t="n"/>
+      <c r="E201" s="7" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="n"/>
+      <c r="B202" s="5" t="n"/>
+      <c r="C202" s="5" t="n"/>
+      <c r="D202" s="5" t="n"/>
+      <c r="E202" s="7" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="n"/>
+      <c r="B203" s="5" t="n"/>
+      <c r="C203" s="5" t="n"/>
+      <c r="D203" s="5" t="n"/>
+      <c r="E203" s="7" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="n"/>
+      <c r="B204" s="5" t="n"/>
+      <c r="C204" s="5" t="n"/>
+      <c r="D204" s="5" t="n"/>
+      <c r="E204" s="7" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="n"/>
+      <c r="B205" s="5" t="n"/>
+      <c r="C205" s="5" t="n"/>
+      <c r="D205" s="5" t="n"/>
+      <c r="E205" s="7" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="n"/>
+      <c r="B206" s="5" t="n"/>
+      <c r="C206" s="5" t="n"/>
+      <c r="D206" s="5" t="n"/>
+      <c r="E206" s="7" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="n"/>
+      <c r="B207" s="5" t="n"/>
+      <c r="C207" s="5" t="n"/>
+      <c r="D207" s="5" t="n"/>
+      <c r="E207" s="7" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="n"/>
+      <c r="B208" s="5" t="n"/>
+      <c r="C208" s="5" t="n"/>
+      <c r="D208" s="5" t="n"/>
+      <c r="E208" s="7" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="n"/>
+      <c r="B209" s="5" t="n"/>
+      <c r="C209" s="5" t="n"/>
+      <c r="D209" s="5" t="n"/>
+      <c r="E209" s="7" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="n"/>
+      <c r="B210" s="5" t="n"/>
+      <c r="C210" s="5" t="n"/>
+      <c r="D210" s="5" t="n"/>
+      <c r="E210" s="7" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="n"/>
+      <c r="B211" s="5" t="n"/>
+      <c r="C211" s="5" t="n"/>
+      <c r="D211" s="5" t="n"/>
+      <c r="E211" s="7" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="n"/>
+      <c r="B212" s="5" t="n"/>
+      <c r="C212" s="5" t="n"/>
+      <c r="D212" s="5" t="n"/>
+      <c r="E212" s="7" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="n"/>
+      <c r="B213" s="5" t="n"/>
+      <c r="C213" s="5" t="n"/>
+      <c r="D213" s="5" t="n"/>
+      <c r="E213" s="7" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="n"/>
+      <c r="B214" s="5" t="n"/>
+      <c r="C214" s="5" t="n"/>
+      <c r="D214" s="5" t="n"/>
+      <c r="E214" s="7" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="n"/>
+      <c r="B215" s="5" t="n"/>
+      <c r="C215" s="5" t="n"/>
+      <c r="D215" s="5" t="n"/>
+      <c r="E215" s="7" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="n"/>
+      <c r="B216" s="5" t="n"/>
+      <c r="C216" s="5" t="n"/>
+      <c r="D216" s="5" t="n"/>
+      <c r="E216" s="7" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="n"/>
+      <c r="B217" s="5" t="n"/>
+      <c r="C217" s="5" t="n"/>
+      <c r="D217" s="5" t="n"/>
+      <c r="E217" s="7" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="n"/>
+      <c r="B218" s="5" t="n"/>
+      <c r="C218" s="5" t="n"/>
+      <c r="D218" s="5" t="n"/>
+      <c r="E218" s="7" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="n"/>
+      <c r="B219" s="5" t="n"/>
+      <c r="C219" s="5" t="n"/>
+      <c r="D219" s="5" t="n"/>
+      <c r="E219" s="7" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="n"/>
+      <c r="B220" s="5" t="n"/>
+      <c r="C220" s="5" t="n"/>
+      <c r="D220" s="5" t="n"/>
+      <c r="E220" s="7" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="n"/>
+      <c r="B221" s="5" t="n"/>
+      <c r="C221" s="5" t="n"/>
+      <c r="D221" s="5" t="n"/>
+      <c r="E221" s="7" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="n"/>
+      <c r="B222" s="5" t="n"/>
+      <c r="C222" s="5" t="n"/>
+      <c r="D222" s="5" t="n"/>
+      <c r="E222" s="7" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="n"/>
+      <c r="B223" s="5" t="n"/>
+      <c r="C223" s="5" t="n"/>
+      <c r="D223" s="5" t="n"/>
+      <c r="E223" s="7" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="n"/>
+      <c r="B224" s="5" t="n"/>
+      <c r="C224" s="5" t="n"/>
+      <c r="D224" s="5" t="n"/>
+      <c r="E224" s="7" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="n"/>
+      <c r="B225" s="5" t="n"/>
+      <c r="C225" s="5" t="n"/>
+      <c r="D225" s="5" t="n"/>
+      <c r="E225" s="7" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="n"/>
+      <c r="B226" s="5" t="n"/>
+      <c r="C226" s="5" t="n"/>
+      <c r="D226" s="5" t="n"/>
+      <c r="E226" s="7" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="n"/>
+      <c r="B227" s="5" t="n"/>
+      <c r="C227" s="5" t="n"/>
+      <c r="D227" s="5" t="n"/>
+      <c r="E227" s="7" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="n"/>
+      <c r="B228" s="5" t="n"/>
+      <c r="C228" s="5" t="n"/>
+      <c r="D228" s="5" t="n"/>
+      <c r="E228" s="7" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="n"/>
+      <c r="B229" s="5" t="n"/>
+      <c r="C229" s="5" t="n"/>
+      <c r="D229" s="5" t="n"/>
+      <c r="E229" s="7" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="5" t="n"/>
+      <c r="B230" s="5" t="n"/>
+      <c r="C230" s="5" t="n"/>
+      <c r="D230" s="5" t="n"/>
+      <c r="E230" s="7" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="n"/>
+      <c r="B231" s="5" t="n"/>
+      <c r="C231" s="5" t="n"/>
+      <c r="D231" s="5" t="n"/>
+      <c r="E231" s="7" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="n"/>
+      <c r="B232" s="5" t="n"/>
+      <c r="C232" s="5" t="n"/>
+      <c r="D232" s="5" t="n"/>
+      <c r="E232" s="7" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="n"/>
+      <c r="B233" s="5" t="n"/>
+      <c r="C233" s="5" t="n"/>
+      <c r="D233" s="5" t="n"/>
+      <c r="E233" s="7" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="5" t="n"/>
+      <c r="B234" s="5" t="n"/>
+      <c r="C234" s="5" t="n"/>
+      <c r="D234" s="5" t="n"/>
+      <c r="E234" s="7" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="n"/>
+      <c r="B235" s="5" t="n"/>
+      <c r="C235" s="5" t="n"/>
+      <c r="D235" s="5" t="n"/>
+      <c r="E235" s="7" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="n"/>
+      <c r="B236" s="5" t="n"/>
+      <c r="C236" s="5" t="n"/>
+      <c r="D236" s="5" t="n"/>
+      <c r="E236" s="7" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="n"/>
+      <c r="B237" s="5" t="n"/>
+      <c r="C237" s="5" t="n"/>
+      <c r="D237" s="5" t="n"/>
+      <c r="E237" s="7" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="n"/>
+      <c r="B238" s="5" t="n"/>
+      <c r="C238" s="5" t="n"/>
+      <c r="D238" s="5" t="n"/>
+      <c r="E238" s="7" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="n"/>
+      <c r="B239" s="5" t="n"/>
+      <c r="C239" s="5" t="n"/>
+      <c r="D239" s="5" t="n"/>
+      <c r="E239" s="7" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="n"/>
+      <c r="B240" s="5" t="n"/>
+      <c r="C240" s="5" t="n"/>
+      <c r="D240" s="5" t="n"/>
+      <c r="E240" s="7" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="5" t="n"/>
+      <c r="B241" s="5" t="n"/>
+      <c r="C241" s="5" t="n"/>
+      <c r="D241" s="5" t="n"/>
+      <c r="E241" s="7" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="5" t="n"/>
+      <c r="B242" s="5" t="n"/>
+      <c r="C242" s="5" t="n"/>
+      <c r="D242" s="5" t="n"/>
+      <c r="E242" s="7" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="n"/>
+      <c r="B243" s="5" t="n"/>
+      <c r="C243" s="5" t="n"/>
+      <c r="D243" s="5" t="n"/>
+      <c r="E243" s="7" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="n"/>
+      <c r="B244" s="5" t="n"/>
+      <c r="C244" s="5" t="n"/>
+      <c r="D244" s="5" t="n"/>
+      <c r="E244" s="7" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="n"/>
+      <c r="B245" s="5" t="n"/>
+      <c r="C245" s="5" t="n"/>
+      <c r="D245" s="5" t="n"/>
+      <c r="E245" s="7" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="n"/>
+      <c r="B246" s="5" t="n"/>
+      <c r="C246" s="5" t="n"/>
+      <c r="D246" s="5" t="n"/>
+      <c r="E246" s="7" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="5" t="n"/>
+      <c r="B247" s="5" t="n"/>
+      <c r="C247" s="5" t="n"/>
+      <c r="D247" s="5" t="n"/>
+      <c r="E247" s="7" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="5" t="n"/>
+      <c r="B248" s="5" t="n"/>
+      <c r="C248" s="5" t="n"/>
+      <c r="D248" s="5" t="n"/>
+      <c r="E248" s="7" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="n"/>
+      <c r="B249" s="5" t="n"/>
+      <c r="C249" s="5" t="n"/>
+      <c r="D249" s="5" t="n"/>
+      <c r="E249" s="7" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="5" t="n"/>
+      <c r="B250" s="5" t="n"/>
+      <c r="C250" s="5" t="n"/>
+      <c r="D250" s="5" t="n"/>
+      <c r="E250" s="7" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="n"/>
+      <c r="B251" s="5" t="n"/>
+      <c r="C251" s="5" t="n"/>
+      <c r="D251" s="5" t="n"/>
+      <c r="E251" s="7" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="5" t="n"/>
+      <c r="B252" s="5" t="n"/>
+      <c r="C252" s="5" t="n"/>
+      <c r="D252" s="5" t="n"/>
+      <c r="E252" s="7" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="n"/>
+      <c r="B253" s="5" t="n"/>
+      <c r="C253" s="5" t="n"/>
+      <c r="D253" s="5" t="n"/>
+      <c r="E253" s="7" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="5" t="n"/>
+      <c r="B254" s="5" t="n"/>
+      <c r="C254" s="5" t="n"/>
+      <c r="D254" s="5" t="n"/>
+      <c r="E254" s="7" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="n"/>
+      <c r="B255" s="5" t="n"/>
+      <c r="C255" s="5" t="n"/>
+      <c r="D255" s="5" t="n"/>
+      <c r="E255" s="7" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="5" t="n"/>
+      <c r="B256" s="5" t="n"/>
+      <c r="C256" s="5" t="n"/>
+      <c r="D256" s="5" t="n"/>
+      <c r="E256" s="7" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="n"/>
+      <c r="B257" s="5" t="n"/>
+      <c r="C257" s="5" t="n"/>
+      <c r="D257" s="5" t="n"/>
+      <c r="E257" s="7" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="5" t="n"/>
+      <c r="B258" s="5" t="n"/>
+      <c r="C258" s="5" t="n"/>
+      <c r="D258" s="5" t="n"/>
+      <c r="E258" s="7" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="n"/>
+      <c r="B259" s="5" t="n"/>
+      <c r="C259" s="5" t="n"/>
+      <c r="D259" s="5" t="n"/>
+      <c r="E259" s="7" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="n"/>
+      <c r="B260" s="5" t="n"/>
+      <c r="C260" s="5" t="n"/>
+      <c r="D260" s="5" t="n"/>
+      <c r="E260" s="7" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="n"/>
+      <c r="B261" s="5" t="n"/>
+      <c r="C261" s="5" t="n"/>
+      <c r="D261" s="5" t="n"/>
+      <c r="E261" s="7" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="5" t="n"/>
+      <c r="B262" s="5" t="n"/>
+      <c r="C262" s="5" t="n"/>
+      <c r="D262" s="5" t="n"/>
+      <c r="E262" s="7" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="n"/>
+      <c r="B263" s="5" t="n"/>
+      <c r="C263" s="5" t="n"/>
+      <c r="D263" s="5" t="n"/>
+      <c r="E263" s="7" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="5" t="n"/>
+      <c r="B264" s="5" t="n"/>
+      <c r="C264" s="5" t="n"/>
+      <c r="D264" s="5" t="n"/>
+      <c r="E264" s="7" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="n"/>
+      <c r="B265" s="5" t="n"/>
+      <c r="C265" s="5" t="n"/>
+      <c r="D265" s="5" t="n"/>
+      <c r="E265" s="7" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="5" t="n"/>
+      <c r="B266" s="5" t="n"/>
+      <c r="C266" s="5" t="n"/>
+      <c r="D266" s="5" t="n"/>
+      <c r="E266" s="7" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="n"/>
+      <c r="B267" s="5" t="n"/>
+      <c r="C267" s="5" t="n"/>
+      <c r="D267" s="5" t="n"/>
+      <c r="E267" s="7" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="5" t="n"/>
+      <c r="B268" s="5" t="n"/>
+      <c r="C268" s="5" t="n"/>
+      <c r="D268" s="5" t="n"/>
+      <c r="E268" s="7" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="n"/>
+      <c r="B269" s="5" t="n"/>
+      <c r="C269" s="5" t="n"/>
+      <c r="D269" s="5" t="n"/>
+      <c r="E269" s="7" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="5" t="n"/>
+      <c r="B270" s="5" t="n"/>
+      <c r="C270" s="5" t="n"/>
+      <c r="D270" s="5" t="n"/>
+      <c r="E270" s="7" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="n"/>
+      <c r="B271" s="5" t="n"/>
+      <c r="C271" s="5" t="n"/>
+      <c r="D271" s="5" t="n"/>
+      <c r="E271" s="7" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="5" t="n"/>
+      <c r="B272" s="5" t="n"/>
+      <c r="C272" s="5" t="n"/>
+      <c r="D272" s="5" t="n"/>
+      <c r="E272" s="7" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="n"/>
+      <c r="B273" s="5" t="n"/>
+      <c r="C273" s="5" t="n"/>
+      <c r="D273" s="5" t="n"/>
+      <c r="E273" s="7" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="5" t="n"/>
+      <c r="B274" s="5" t="n"/>
+      <c r="C274" s="5" t="n"/>
+      <c r="D274" s="5" t="n"/>
+      <c r="E274" s="7" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="n"/>
+      <c r="B275" s="5" t="n"/>
+      <c r="C275" s="5" t="n"/>
+      <c r="D275" s="5" t="n"/>
+      <c r="E275" s="7" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="5" t="n"/>
+      <c r="B276" s="5" t="n"/>
+      <c r="C276" s="5" t="n"/>
+      <c r="D276" s="5" t="n"/>
+      <c r="E276" s="7" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="n"/>
+      <c r="B277" s="5" t="n"/>
+      <c r="C277" s="5" t="n"/>
+      <c r="D277" s="5" t="n"/>
+      <c r="E277" s="7" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="5" t="n"/>
+      <c r="B278" s="5" t="n"/>
+      <c r="C278" s="5" t="n"/>
+      <c r="D278" s="5" t="n"/>
+      <c r="E278" s="7" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="n"/>
+      <c r="B279" s="5" t="n"/>
+      <c r="C279" s="5" t="n"/>
+      <c r="D279" s="5" t="n"/>
+      <c r="E279" s="7" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="5" t="n"/>
+      <c r="B280" s="5" t="n"/>
+      <c r="C280" s="5" t="n"/>
+      <c r="D280" s="5" t="n"/>
+      <c r="E280" s="7" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="n"/>
+      <c r="B281" s="5" t="n"/>
+      <c r="C281" s="5" t="n"/>
+      <c r="D281" s="5" t="n"/>
+      <c r="E281" s="7" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="5" t="n"/>
+      <c r="B282" s="5" t="n"/>
+      <c r="C282" s="5" t="n"/>
+      <c r="D282" s="5" t="n"/>
+      <c r="E282" s="7" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="n"/>
+      <c r="B283" s="5" t="n"/>
+      <c r="C283" s="5" t="n"/>
+      <c r="D283" s="5" t="n"/>
+      <c r="E283" s="7" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="5" t="n"/>
+      <c r="B284" s="5" t="n"/>
+      <c r="C284" s="5" t="n"/>
+      <c r="D284" s="5" t="n"/>
+      <c r="E284" s="7" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="n"/>
+      <c r="B285" s="5" t="n"/>
+      <c r="C285" s="5" t="n"/>
+      <c r="D285" s="5" t="n"/>
+      <c r="E285" s="7" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="5" t="n"/>
+      <c r="B286" s="5" t="n"/>
+      <c r="C286" s="5" t="n"/>
+      <c r="D286" s="5" t="n"/>
+      <c r="E286" s="7" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="n"/>
+      <c r="B287" s="5" t="n"/>
+      <c r="C287" s="5" t="n"/>
+      <c r="D287" s="5" t="n"/>
+      <c r="E287" s="7" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="5" t="n"/>
+      <c r="B288" s="5" t="n"/>
+      <c r="C288" s="5" t="n"/>
+      <c r="D288" s="5" t="n"/>
+      <c r="E288" s="7" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="n"/>
+      <c r="B289" s="5" t="n"/>
+      <c r="C289" s="5" t="n"/>
+      <c r="D289" s="5" t="n"/>
+      <c r="E289" s="7" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="5" t="n"/>
+      <c r="B290" s="5" t="n"/>
+      <c r="C290" s="5" t="n"/>
+      <c r="D290" s="5" t="n"/>
+      <c r="E290" s="7" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="n"/>
+      <c r="B291" s="5" t="n"/>
+      <c r="C291" s="5" t="n"/>
+      <c r="D291" s="5" t="n"/>
+      <c r="E291" s="7" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="5" t="n"/>
+      <c r="B292" s="5" t="n"/>
+      <c r="C292" s="5" t="n"/>
+      <c r="D292" s="5" t="n"/>
+      <c r="E292" s="7" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="n"/>
+      <c r="B293" s="5" t="n"/>
+      <c r="C293" s="5" t="n"/>
+      <c r="D293" s="5" t="n"/>
+      <c r="E293" s="7" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="5" t="n"/>
+      <c r="B294" s="5" t="n"/>
+      <c r="C294" s="5" t="n"/>
+      <c r="D294" s="5" t="n"/>
+      <c r="E294" s="7" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="n"/>
+      <c r="B295" s="5" t="n"/>
+      <c r="C295" s="5" t="n"/>
+      <c r="D295" s="5" t="n"/>
+      <c r="E295" s="7" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="5" t="n"/>
+      <c r="B296" s="5" t="n"/>
+      <c r="C296" s="5" t="n"/>
+      <c r="D296" s="5" t="n"/>
+      <c r="E296" s="7" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="n"/>
+      <c r="B297" s="5" t="n"/>
+      <c r="C297" s="5" t="n"/>
+      <c r="D297" s="5" t="n"/>
+      <c r="E297" s="7" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="5" t="n"/>
+      <c r="B298" s="5" t="n"/>
+      <c r="C298" s="5" t="n"/>
+      <c r="D298" s="5" t="n"/>
+      <c r="E298" s="7" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="n"/>
+      <c r="B299" s="5" t="n"/>
+      <c r="C299" s="5" t="n"/>
+      <c r="D299" s="5" t="n"/>
+      <c r="E299" s="7" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="5" t="n"/>
+      <c r="B300" s="5" t="n"/>
+      <c r="C300" s="5" t="n"/>
+      <c r="D300" s="5" t="n"/>
+      <c r="E300" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sheet-template/IIS-website-content.xlsx
+++ b/sheet-template/IIS-website-content.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Media" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Press" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Undergrads" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Areas" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,7 +497,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Tabs: People, Projects, Papers, Media, Press, Undergrads. One row per item. Do not rename the tabs or the column headings.</t>
+          <t>Tabs: People, Projects, Papers, Media, Press, Undergrads, Areas. One row per item. Do not rename the tabs or the column headings.</t>
         </is>
       </c>
     </row>
@@ -603,9 +604,9 @@
       <c r="A24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Research areas (use these names in the "areas" column): Intelligent systems; HCI; Accessibility &amp; AAC; Crowdsourcing; Interaction science</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>RESEARCH AREAS: the "areas" column must use the "short" names listed in the Areas tab. To add an area, add a row there (name, short, color like #0F8B8D) BEFORE using it elsewhere.</t>
         </is>
       </c>
     </row>
@@ -26671,4 +26672,2583 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F300"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Mixed Reality</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Mixed Reality</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>#0F8B8D</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Human-Robot Interaction</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Human-Robot Interaction</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>robot</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>#D9480F</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Text Entry</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Text Entry</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>typing</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>#2540FF</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>#C2255C</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Adaptive Interfaces</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Adaptive Interfaces</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>adaptive</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>#5E9E3B</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Hand Gestures</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Hand Gestures</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>gesture</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>#B7791F</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Human-AI Interaction</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Human-AI Interaction</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>hai</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>#7048E8</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Spatial Interaction Design</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Spatial Interaction Design</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>spatial</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>#0B7285</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n"/>
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n"/>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n"/>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n"/>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n"/>
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n"/>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n"/>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n"/>
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="7" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n"/>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n"/>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="7" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n"/>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n"/>
+      <c r="B60" s="5" t="n"/>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="7" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n"/>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n"/>
+      <c r="B62" s="5" t="n"/>
+      <c r="C62" s="5" t="n"/>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="7" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n"/>
+      <c r="B63" s="5" t="n"/>
+      <c r="C63" s="5" t="n"/>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="7" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n"/>
+      <c r="B64" s="5" t="n"/>
+      <c r="C64" s="5" t="n"/>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="7" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n"/>
+      <c r="B65" s="5" t="n"/>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="7" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n"/>
+      <c r="B66" s="5" t="n"/>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="7" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n"/>
+      <c r="B67" s="5" t="n"/>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="7" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n"/>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="7" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n"/>
+      <c r="B69" s="5" t="n"/>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="7" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n"/>
+      <c r="B70" s="5" t="n"/>
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="7" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n"/>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n"/>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="7" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n"/>
+      <c r="B73" s="5" t="n"/>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n"/>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="7" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n"/>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n"/>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="7" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n"/>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="7" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n"/>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="7" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n"/>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="5" t="n"/>
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="n"/>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="7" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n"/>
+      <c r="B81" s="5" t="n"/>
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="5" t="n"/>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="7" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n"/>
+      <c r="B82" s="5" t="n"/>
+      <c r="C82" s="5" t="n"/>
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="7" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n"/>
+      <c r="B83" s="5" t="n"/>
+      <c r="C83" s="5" t="n"/>
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="7" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n"/>
+      <c r="B84" s="5" t="n"/>
+      <c r="C84" s="5" t="n"/>
+      <c r="D84" s="5" t="n"/>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="7" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n"/>
+      <c r="B85" s="5" t="n"/>
+      <c r="C85" s="5" t="n"/>
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="7" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n"/>
+      <c r="B86" s="5" t="n"/>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="7" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n"/>
+      <c r="B87" s="5" t="n"/>
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="7" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n"/>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="7" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n"/>
+      <c r="B89" s="5" t="n"/>
+      <c r="C89" s="5" t="n"/>
+      <c r="D89" s="5" t="n"/>
+      <c r="E89" s="5" t="n"/>
+      <c r="F89" s="7" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n"/>
+      <c r="B90" s="5" t="n"/>
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="5" t="n"/>
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="7" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n"/>
+      <c r="B91" s="5" t="n"/>
+      <c r="C91" s="5" t="n"/>
+      <c r="D91" s="5" t="n"/>
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n"/>
+      <c r="B92" s="5" t="n"/>
+      <c r="C92" s="5" t="n"/>
+      <c r="D92" s="5" t="n"/>
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n"/>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="7" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n"/>
+      <c r="B94" s="5" t="n"/>
+      <c r="C94" s="5" t="n"/>
+      <c r="D94" s="5" t="n"/>
+      <c r="E94" s="5" t="n"/>
+      <c r="F94" s="7" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n"/>
+      <c r="B95" s="5" t="n"/>
+      <c r="C95" s="5" t="n"/>
+      <c r="D95" s="5" t="n"/>
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="7" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n"/>
+      <c r="B96" s="5" t="n"/>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="7" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n"/>
+      <c r="B97" s="5" t="n"/>
+      <c r="C97" s="5" t="n"/>
+      <c r="D97" s="5" t="n"/>
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="7" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n"/>
+      <c r="B98" s="5" t="n"/>
+      <c r="C98" s="5" t="n"/>
+      <c r="D98" s="5" t="n"/>
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="7" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n"/>
+      <c r="B99" s="5" t="n"/>
+      <c r="C99" s="5" t="n"/>
+      <c r="D99" s="5" t="n"/>
+      <c r="E99" s="5" t="n"/>
+      <c r="F99" s="7" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n"/>
+      <c r="B100" s="5" t="n"/>
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="5" t="n"/>
+      <c r="E100" s="5" t="n"/>
+      <c r="F100" s="7" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n"/>
+      <c r="B101" s="5" t="n"/>
+      <c r="C101" s="5" t="n"/>
+      <c r="D101" s="5" t="n"/>
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="7" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n"/>
+      <c r="B102" s="5" t="n"/>
+      <c r="C102" s="5" t="n"/>
+      <c r="D102" s="5" t="n"/>
+      <c r="E102" s="5" t="n"/>
+      <c r="F102" s="7" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n"/>
+      <c r="B103" s="5" t="n"/>
+      <c r="C103" s="5" t="n"/>
+      <c r="D103" s="5" t="n"/>
+      <c r="E103" s="5" t="n"/>
+      <c r="F103" s="7" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n"/>
+      <c r="B104" s="5" t="n"/>
+      <c r="C104" s="5" t="n"/>
+      <c r="D104" s="5" t="n"/>
+      <c r="E104" s="5" t="n"/>
+      <c r="F104" s="7" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="n"/>
+      <c r="B105" s="5" t="n"/>
+      <c r="C105" s="5" t="n"/>
+      <c r="D105" s="5" t="n"/>
+      <c r="E105" s="5" t="n"/>
+      <c r="F105" s="7" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n"/>
+      <c r="B106" s="5" t="n"/>
+      <c r="C106" s="5" t="n"/>
+      <c r="D106" s="5" t="n"/>
+      <c r="E106" s="5" t="n"/>
+      <c r="F106" s="7" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n"/>
+      <c r="B107" s="5" t="n"/>
+      <c r="C107" s="5" t="n"/>
+      <c r="D107" s="5" t="n"/>
+      <c r="E107" s="5" t="n"/>
+      <c r="F107" s="7" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n"/>
+      <c r="B108" s="5" t="n"/>
+      <c r="C108" s="5" t="n"/>
+      <c r="D108" s="5" t="n"/>
+      <c r="E108" s="5" t="n"/>
+      <c r="F108" s="7" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n"/>
+      <c r="B109" s="5" t="n"/>
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="5" t="n"/>
+      <c r="E109" s="5" t="n"/>
+      <c r="F109" s="7" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="n"/>
+      <c r="B110" s="5" t="n"/>
+      <c r="C110" s="5" t="n"/>
+      <c r="D110" s="5" t="n"/>
+      <c r="E110" s="5" t="n"/>
+      <c r="F110" s="7" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n"/>
+      <c r="B111" s="5" t="n"/>
+      <c r="C111" s="5" t="n"/>
+      <c r="D111" s="5" t="n"/>
+      <c r="E111" s="5" t="n"/>
+      <c r="F111" s="7" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="n"/>
+      <c r="B112" s="5" t="n"/>
+      <c r="C112" s="5" t="n"/>
+      <c r="D112" s="5" t="n"/>
+      <c r="E112" s="5" t="n"/>
+      <c r="F112" s="7" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n"/>
+      <c r="B113" s="5" t="n"/>
+      <c r="C113" s="5" t="n"/>
+      <c r="D113" s="5" t="n"/>
+      <c r="E113" s="5" t="n"/>
+      <c r="F113" s="7" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n"/>
+      <c r="B114" s="5" t="n"/>
+      <c r="C114" s="5" t="n"/>
+      <c r="D114" s="5" t="n"/>
+      <c r="E114" s="5" t="n"/>
+      <c r="F114" s="7" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n"/>
+      <c r="B115" s="5" t="n"/>
+      <c r="C115" s="5" t="n"/>
+      <c r="D115" s="5" t="n"/>
+      <c r="E115" s="5" t="n"/>
+      <c r="F115" s="7" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n"/>
+      <c r="B116" s="5" t="n"/>
+      <c r="C116" s="5" t="n"/>
+      <c r="D116" s="5" t="n"/>
+      <c r="E116" s="5" t="n"/>
+      <c r="F116" s="7" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n"/>
+      <c r="B117" s="5" t="n"/>
+      <c r="C117" s="5" t="n"/>
+      <c r="D117" s="5" t="n"/>
+      <c r="E117" s="5" t="n"/>
+      <c r="F117" s="7" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n"/>
+      <c r="B118" s="5" t="n"/>
+      <c r="C118" s="5" t="n"/>
+      <c r="D118" s="5" t="n"/>
+      <c r="E118" s="5" t="n"/>
+      <c r="F118" s="7" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n"/>
+      <c r="B119" s="5" t="n"/>
+      <c r="C119" s="5" t="n"/>
+      <c r="D119" s="5" t="n"/>
+      <c r="E119" s="5" t="n"/>
+      <c r="F119" s="7" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n"/>
+      <c r="B120" s="5" t="n"/>
+      <c r="C120" s="5" t="n"/>
+      <c r="D120" s="5" t="n"/>
+      <c r="E120" s="5" t="n"/>
+      <c r="F120" s="7" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n"/>
+      <c r="B121" s="5" t="n"/>
+      <c r="C121" s="5" t="n"/>
+      <c r="D121" s="5" t="n"/>
+      <c r="E121" s="5" t="n"/>
+      <c r="F121" s="7" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="n"/>
+      <c r="B122" s="5" t="n"/>
+      <c r="C122" s="5" t="n"/>
+      <c r="D122" s="5" t="n"/>
+      <c r="E122" s="5" t="n"/>
+      <c r="F122" s="7" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n"/>
+      <c r="B123" s="5" t="n"/>
+      <c r="C123" s="5" t="n"/>
+      <c r="D123" s="5" t="n"/>
+      <c r="E123" s="5" t="n"/>
+      <c r="F123" s="7" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n"/>
+      <c r="B124" s="5" t="n"/>
+      <c r="C124" s="5" t="n"/>
+      <c r="D124" s="5" t="n"/>
+      <c r="E124" s="5" t="n"/>
+      <c r="F124" s="7" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n"/>
+      <c r="B125" s="5" t="n"/>
+      <c r="C125" s="5" t="n"/>
+      <c r="D125" s="5" t="n"/>
+      <c r="E125" s="5" t="n"/>
+      <c r="F125" s="7" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="n"/>
+      <c r="B126" s="5" t="n"/>
+      <c r="C126" s="5" t="n"/>
+      <c r="D126" s="5" t="n"/>
+      <c r="E126" s="5" t="n"/>
+      <c r="F126" s="7" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n"/>
+      <c r="B127" s="5" t="n"/>
+      <c r="C127" s="5" t="n"/>
+      <c r="D127" s="5" t="n"/>
+      <c r="E127" s="5" t="n"/>
+      <c r="F127" s="7" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="n"/>
+      <c r="B128" s="5" t="n"/>
+      <c r="C128" s="5" t="n"/>
+      <c r="D128" s="5" t="n"/>
+      <c r="E128" s="5" t="n"/>
+      <c r="F128" s="7" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n"/>
+      <c r="B129" s="5" t="n"/>
+      <c r="C129" s="5" t="n"/>
+      <c r="D129" s="5" t="n"/>
+      <c r="E129" s="5" t="n"/>
+      <c r="F129" s="7" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="n"/>
+      <c r="B130" s="5" t="n"/>
+      <c r="C130" s="5" t="n"/>
+      <c r="D130" s="5" t="n"/>
+      <c r="E130" s="5" t="n"/>
+      <c r="F130" s="7" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n"/>
+      <c r="B131" s="5" t="n"/>
+      <c r="C131" s="5" t="n"/>
+      <c r="D131" s="5" t="n"/>
+      <c r="E131" s="5" t="n"/>
+      <c r="F131" s="7" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="n"/>
+      <c r="B132" s="5" t="n"/>
+      <c r="C132" s="5" t="n"/>
+      <c r="D132" s="5" t="n"/>
+      <c r="E132" s="5" t="n"/>
+      <c r="F132" s="7" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n"/>
+      <c r="B133" s="5" t="n"/>
+      <c r="C133" s="5" t="n"/>
+      <c r="D133" s="5" t="n"/>
+      <c r="E133" s="5" t="n"/>
+      <c r="F133" s="7" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="n"/>
+      <c r="B134" s="5" t="n"/>
+      <c r="C134" s="5" t="n"/>
+      <c r="D134" s="5" t="n"/>
+      <c r="E134" s="5" t="n"/>
+      <c r="F134" s="7" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n"/>
+      <c r="B135" s="5" t="n"/>
+      <c r="C135" s="5" t="n"/>
+      <c r="D135" s="5" t="n"/>
+      <c r="E135" s="5" t="n"/>
+      <c r="F135" s="7" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="n"/>
+      <c r="B136" s="5" t="n"/>
+      <c r="C136" s="5" t="n"/>
+      <c r="D136" s="5" t="n"/>
+      <c r="E136" s="5" t="n"/>
+      <c r="F136" s="7" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n"/>
+      <c r="B137" s="5" t="n"/>
+      <c r="C137" s="5" t="n"/>
+      <c r="D137" s="5" t="n"/>
+      <c r="E137" s="5" t="n"/>
+      <c r="F137" s="7" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="n"/>
+      <c r="B138" s="5" t="n"/>
+      <c r="C138" s="5" t="n"/>
+      <c r="D138" s="5" t="n"/>
+      <c r="E138" s="5" t="n"/>
+      <c r="F138" s="7" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n"/>
+      <c r="B139" s="5" t="n"/>
+      <c r="C139" s="5" t="n"/>
+      <c r="D139" s="5" t="n"/>
+      <c r="E139" s="5" t="n"/>
+      <c r="F139" s="7" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="n"/>
+      <c r="B140" s="5" t="n"/>
+      <c r="C140" s="5" t="n"/>
+      <c r="D140" s="5" t="n"/>
+      <c r="E140" s="5" t="n"/>
+      <c r="F140" s="7" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n"/>
+      <c r="B141" s="5" t="n"/>
+      <c r="C141" s="5" t="n"/>
+      <c r="D141" s="5" t="n"/>
+      <c r="E141" s="5" t="n"/>
+      <c r="F141" s="7" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="n"/>
+      <c r="B142" s="5" t="n"/>
+      <c r="C142" s="5" t="n"/>
+      <c r="D142" s="5" t="n"/>
+      <c r="E142" s="5" t="n"/>
+      <c r="F142" s="7" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n"/>
+      <c r="B143" s="5" t="n"/>
+      <c r="C143" s="5" t="n"/>
+      <c r="D143" s="5" t="n"/>
+      <c r="E143" s="5" t="n"/>
+      <c r="F143" s="7" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="n"/>
+      <c r="B144" s="5" t="n"/>
+      <c r="C144" s="5" t="n"/>
+      <c r="D144" s="5" t="n"/>
+      <c r="E144" s="5" t="n"/>
+      <c r="F144" s="7" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n"/>
+      <c r="B145" s="5" t="n"/>
+      <c r="C145" s="5" t="n"/>
+      <c r="D145" s="5" t="n"/>
+      <c r="E145" s="5" t="n"/>
+      <c r="F145" s="7" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="n"/>
+      <c r="B146" s="5" t="n"/>
+      <c r="C146" s="5" t="n"/>
+      <c r="D146" s="5" t="n"/>
+      <c r="E146" s="5" t="n"/>
+      <c r="F146" s="7" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n"/>
+      <c r="B147" s="5" t="n"/>
+      <c r="C147" s="5" t="n"/>
+      <c r="D147" s="5" t="n"/>
+      <c r="E147" s="5" t="n"/>
+      <c r="F147" s="7" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="n"/>
+      <c r="B148" s="5" t="n"/>
+      <c r="C148" s="5" t="n"/>
+      <c r="D148" s="5" t="n"/>
+      <c r="E148" s="5" t="n"/>
+      <c r="F148" s="7" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n"/>
+      <c r="B149" s="5" t="n"/>
+      <c r="C149" s="5" t="n"/>
+      <c r="D149" s="5" t="n"/>
+      <c r="E149" s="5" t="n"/>
+      <c r="F149" s="7" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="n"/>
+      <c r="B150" s="5" t="n"/>
+      <c r="C150" s="5" t="n"/>
+      <c r="D150" s="5" t="n"/>
+      <c r="E150" s="5" t="n"/>
+      <c r="F150" s="7" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n"/>
+      <c r="B151" s="5" t="n"/>
+      <c r="C151" s="5" t="n"/>
+      <c r="D151" s="5" t="n"/>
+      <c r="E151" s="5" t="n"/>
+      <c r="F151" s="7" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="n"/>
+      <c r="B152" s="5" t="n"/>
+      <c r="C152" s="5" t="n"/>
+      <c r="D152" s="5" t="n"/>
+      <c r="E152" s="5" t="n"/>
+      <c r="F152" s="7" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="n"/>
+      <c r="B153" s="5" t="n"/>
+      <c r="C153" s="5" t="n"/>
+      <c r="D153" s="5" t="n"/>
+      <c r="E153" s="5" t="n"/>
+      <c r="F153" s="7" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="n"/>
+      <c r="B154" s="5" t="n"/>
+      <c r="C154" s="5" t="n"/>
+      <c r="D154" s="5" t="n"/>
+      <c r="E154" s="5" t="n"/>
+      <c r="F154" s="7" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n"/>
+      <c r="B155" s="5" t="n"/>
+      <c r="C155" s="5" t="n"/>
+      <c r="D155" s="5" t="n"/>
+      <c r="E155" s="5" t="n"/>
+      <c r="F155" s="7" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="n"/>
+      <c r="B156" s="5" t="n"/>
+      <c r="C156" s="5" t="n"/>
+      <c r="D156" s="5" t="n"/>
+      <c r="E156" s="5" t="n"/>
+      <c r="F156" s="7" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n"/>
+      <c r="B157" s="5" t="n"/>
+      <c r="C157" s="5" t="n"/>
+      <c r="D157" s="5" t="n"/>
+      <c r="E157" s="5" t="n"/>
+      <c r="F157" s="7" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="n"/>
+      <c r="B158" s="5" t="n"/>
+      <c r="C158" s="5" t="n"/>
+      <c r="D158" s="5" t="n"/>
+      <c r="E158" s="5" t="n"/>
+      <c r="F158" s="7" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="n"/>
+      <c r="B159" s="5" t="n"/>
+      <c r="C159" s="5" t="n"/>
+      <c r="D159" s="5" t="n"/>
+      <c r="E159" s="5" t="n"/>
+      <c r="F159" s="7" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="n"/>
+      <c r="B160" s="5" t="n"/>
+      <c r="C160" s="5" t="n"/>
+      <c r="D160" s="5" t="n"/>
+      <c r="E160" s="5" t="n"/>
+      <c r="F160" s="7" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="n"/>
+      <c r="B161" s="5" t="n"/>
+      <c r="C161" s="5" t="n"/>
+      <c r="D161" s="5" t="n"/>
+      <c r="E161" s="5" t="n"/>
+      <c r="F161" s="7" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="n"/>
+      <c r="B162" s="5" t="n"/>
+      <c r="C162" s="5" t="n"/>
+      <c r="D162" s="5" t="n"/>
+      <c r="E162" s="5" t="n"/>
+      <c r="F162" s="7" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="n"/>
+      <c r="B163" s="5" t="n"/>
+      <c r="C163" s="5" t="n"/>
+      <c r="D163" s="5" t="n"/>
+      <c r="E163" s="5" t="n"/>
+      <c r="F163" s="7" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="n"/>
+      <c r="B164" s="5" t="n"/>
+      <c r="C164" s="5" t="n"/>
+      <c r="D164" s="5" t="n"/>
+      <c r="E164" s="5" t="n"/>
+      <c r="F164" s="7" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="n"/>
+      <c r="B165" s="5" t="n"/>
+      <c r="C165" s="5" t="n"/>
+      <c r="D165" s="5" t="n"/>
+      <c r="E165" s="5" t="n"/>
+      <c r="F165" s="7" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="n"/>
+      <c r="B166" s="5" t="n"/>
+      <c r="C166" s="5" t="n"/>
+      <c r="D166" s="5" t="n"/>
+      <c r="E166" s="5" t="n"/>
+      <c r="F166" s="7" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="n"/>
+      <c r="B167" s="5" t="n"/>
+      <c r="C167" s="5" t="n"/>
+      <c r="D167" s="5" t="n"/>
+      <c r="E167" s="5" t="n"/>
+      <c r="F167" s="7" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="n"/>
+      <c r="B168" s="5" t="n"/>
+      <c r="C168" s="5" t="n"/>
+      <c r="D168" s="5" t="n"/>
+      <c r="E168" s="5" t="n"/>
+      <c r="F168" s="7" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="n"/>
+      <c r="B169" s="5" t="n"/>
+      <c r="C169" s="5" t="n"/>
+      <c r="D169" s="5" t="n"/>
+      <c r="E169" s="5" t="n"/>
+      <c r="F169" s="7" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="n"/>
+      <c r="B170" s="5" t="n"/>
+      <c r="C170" s="5" t="n"/>
+      <c r="D170" s="5" t="n"/>
+      <c r="E170" s="5" t="n"/>
+      <c r="F170" s="7" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="n"/>
+      <c r="B171" s="5" t="n"/>
+      <c r="C171" s="5" t="n"/>
+      <c r="D171" s="5" t="n"/>
+      <c r="E171" s="5" t="n"/>
+      <c r="F171" s="7" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="n"/>
+      <c r="B172" s="5" t="n"/>
+      <c r="C172" s="5" t="n"/>
+      <c r="D172" s="5" t="n"/>
+      <c r="E172" s="5" t="n"/>
+      <c r="F172" s="7" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="n"/>
+      <c r="B173" s="5" t="n"/>
+      <c r="C173" s="5" t="n"/>
+      <c r="D173" s="5" t="n"/>
+      <c r="E173" s="5" t="n"/>
+      <c r="F173" s="7" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="n"/>
+      <c r="B174" s="5" t="n"/>
+      <c r="C174" s="5" t="n"/>
+      <c r="D174" s="5" t="n"/>
+      <c r="E174" s="5" t="n"/>
+      <c r="F174" s="7" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="n"/>
+      <c r="B175" s="5" t="n"/>
+      <c r="C175" s="5" t="n"/>
+      <c r="D175" s="5" t="n"/>
+      <c r="E175" s="5" t="n"/>
+      <c r="F175" s="7" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n"/>
+      <c r="B176" s="5" t="n"/>
+      <c r="C176" s="5" t="n"/>
+      <c r="D176" s="5" t="n"/>
+      <c r="E176" s="5" t="n"/>
+      <c r="F176" s="7" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="n"/>
+      <c r="B177" s="5" t="n"/>
+      <c r="C177" s="5" t="n"/>
+      <c r="D177" s="5" t="n"/>
+      <c r="E177" s="5" t="n"/>
+      <c r="F177" s="7" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="n"/>
+      <c r="B178" s="5" t="n"/>
+      <c r="C178" s="5" t="n"/>
+      <c r="D178" s="5" t="n"/>
+      <c r="E178" s="5" t="n"/>
+      <c r="F178" s="7" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="n"/>
+      <c r="B179" s="5" t="n"/>
+      <c r="C179" s="5" t="n"/>
+      <c r="D179" s="5" t="n"/>
+      <c r="E179" s="5" t="n"/>
+      <c r="F179" s="7" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="n"/>
+      <c r="B180" s="5" t="n"/>
+      <c r="C180" s="5" t="n"/>
+      <c r="D180" s="5" t="n"/>
+      <c r="E180" s="5" t="n"/>
+      <c r="F180" s="7" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="n"/>
+      <c r="B181" s="5" t="n"/>
+      <c r="C181" s="5" t="n"/>
+      <c r="D181" s="5" t="n"/>
+      <c r="E181" s="5" t="n"/>
+      <c r="F181" s="7" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="n"/>
+      <c r="B182" s="5" t="n"/>
+      <c r="C182" s="5" t="n"/>
+      <c r="D182" s="5" t="n"/>
+      <c r="E182" s="5" t="n"/>
+      <c r="F182" s="7" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="n"/>
+      <c r="B183" s="5" t="n"/>
+      <c r="C183" s="5" t="n"/>
+      <c r="D183" s="5" t="n"/>
+      <c r="E183" s="5" t="n"/>
+      <c r="F183" s="7" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="n"/>
+      <c r="B184" s="5" t="n"/>
+      <c r="C184" s="5" t="n"/>
+      <c r="D184" s="5" t="n"/>
+      <c r="E184" s="5" t="n"/>
+      <c r="F184" s="7" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="n"/>
+      <c r="B185" s="5" t="n"/>
+      <c r="C185" s="5" t="n"/>
+      <c r="D185" s="5" t="n"/>
+      <c r="E185" s="5" t="n"/>
+      <c r="F185" s="7" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="n"/>
+      <c r="B186" s="5" t="n"/>
+      <c r="C186" s="5" t="n"/>
+      <c r="D186" s="5" t="n"/>
+      <c r="E186" s="5" t="n"/>
+      <c r="F186" s="7" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="n"/>
+      <c r="B187" s="5" t="n"/>
+      <c r="C187" s="5" t="n"/>
+      <c r="D187" s="5" t="n"/>
+      <c r="E187" s="5" t="n"/>
+      <c r="F187" s="7" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="n"/>
+      <c r="B188" s="5" t="n"/>
+      <c r="C188" s="5" t="n"/>
+      <c r="D188" s="5" t="n"/>
+      <c r="E188" s="5" t="n"/>
+      <c r="F188" s="7" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="n"/>
+      <c r="B189" s="5" t="n"/>
+      <c r="C189" s="5" t="n"/>
+      <c r="D189" s="5" t="n"/>
+      <c r="E189" s="5" t="n"/>
+      <c r="F189" s="7" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="n"/>
+      <c r="B190" s="5" t="n"/>
+      <c r="C190" s="5" t="n"/>
+      <c r="D190" s="5" t="n"/>
+      <c r="E190" s="5" t="n"/>
+      <c r="F190" s="7" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="n"/>
+      <c r="B191" s="5" t="n"/>
+      <c r="C191" s="5" t="n"/>
+      <c r="D191" s="5" t="n"/>
+      <c r="E191" s="5" t="n"/>
+      <c r="F191" s="7" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="n"/>
+      <c r="B192" s="5" t="n"/>
+      <c r="C192" s="5" t="n"/>
+      <c r="D192" s="5" t="n"/>
+      <c r="E192" s="5" t="n"/>
+      <c r="F192" s="7" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="n"/>
+      <c r="B193" s="5" t="n"/>
+      <c r="C193" s="5" t="n"/>
+      <c r="D193" s="5" t="n"/>
+      <c r="E193" s="5" t="n"/>
+      <c r="F193" s="7" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="n"/>
+      <c r="B194" s="5" t="n"/>
+      <c r="C194" s="5" t="n"/>
+      <c r="D194" s="5" t="n"/>
+      <c r="E194" s="5" t="n"/>
+      <c r="F194" s="7" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="n"/>
+      <c r="B195" s="5" t="n"/>
+      <c r="C195" s="5" t="n"/>
+      <c r="D195" s="5" t="n"/>
+      <c r="E195" s="5" t="n"/>
+      <c r="F195" s="7" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="n"/>
+      <c r="B196" s="5" t="n"/>
+      <c r="C196" s="5" t="n"/>
+      <c r="D196" s="5" t="n"/>
+      <c r="E196" s="5" t="n"/>
+      <c r="F196" s="7" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="n"/>
+      <c r="B197" s="5" t="n"/>
+      <c r="C197" s="5" t="n"/>
+      <c r="D197" s="5" t="n"/>
+      <c r="E197" s="5" t="n"/>
+      <c r="F197" s="7" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="n"/>
+      <c r="B198" s="5" t="n"/>
+      <c r="C198" s="5" t="n"/>
+      <c r="D198" s="5" t="n"/>
+      <c r="E198" s="5" t="n"/>
+      <c r="F198" s="7" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="n"/>
+      <c r="B199" s="5" t="n"/>
+      <c r="C199" s="5" t="n"/>
+      <c r="D199" s="5" t="n"/>
+      <c r="E199" s="5" t="n"/>
+      <c r="F199" s="7" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="n"/>
+      <c r="B200" s="5" t="n"/>
+      <c r="C200" s="5" t="n"/>
+      <c r="D200" s="5" t="n"/>
+      <c r="E200" s="5" t="n"/>
+      <c r="F200" s="7" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="n"/>
+      <c r="B201" s="5" t="n"/>
+      <c r="C201" s="5" t="n"/>
+      <c r="D201" s="5" t="n"/>
+      <c r="E201" s="5" t="n"/>
+      <c r="F201" s="7" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="n"/>
+      <c r="B202" s="5" t="n"/>
+      <c r="C202" s="5" t="n"/>
+      <c r="D202" s="5" t="n"/>
+      <c r="E202" s="5" t="n"/>
+      <c r="F202" s="7" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="n"/>
+      <c r="B203" s="5" t="n"/>
+      <c r="C203" s="5" t="n"/>
+      <c r="D203" s="5" t="n"/>
+      <c r="E203" s="5" t="n"/>
+      <c r="F203" s="7" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="n"/>
+      <c r="B204" s="5" t="n"/>
+      <c r="C204" s="5" t="n"/>
+      <c r="D204" s="5" t="n"/>
+      <c r="E204" s="5" t="n"/>
+      <c r="F204" s="7" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="n"/>
+      <c r="B205" s="5" t="n"/>
+      <c r="C205" s="5" t="n"/>
+      <c r="D205" s="5" t="n"/>
+      <c r="E205" s="5" t="n"/>
+      <c r="F205" s="7" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="n"/>
+      <c r="B206" s="5" t="n"/>
+      <c r="C206" s="5" t="n"/>
+      <c r="D206" s="5" t="n"/>
+      <c r="E206" s="5" t="n"/>
+      <c r="F206" s="7" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="n"/>
+      <c r="B207" s="5" t="n"/>
+      <c r="C207" s="5" t="n"/>
+      <c r="D207" s="5" t="n"/>
+      <c r="E207" s="5" t="n"/>
+      <c r="F207" s="7" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="n"/>
+      <c r="B208" s="5" t="n"/>
+      <c r="C208" s="5" t="n"/>
+      <c r="D208" s="5" t="n"/>
+      <c r="E208" s="5" t="n"/>
+      <c r="F208" s="7" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="n"/>
+      <c r="B209" s="5" t="n"/>
+      <c r="C209" s="5" t="n"/>
+      <c r="D209" s="5" t="n"/>
+      <c r="E209" s="5" t="n"/>
+      <c r="F209" s="7" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="n"/>
+      <c r="B210" s="5" t="n"/>
+      <c r="C210" s="5" t="n"/>
+      <c r="D210" s="5" t="n"/>
+      <c r="E210" s="5" t="n"/>
+      <c r="F210" s="7" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="n"/>
+      <c r="B211" s="5" t="n"/>
+      <c r="C211" s="5" t="n"/>
+      <c r="D211" s="5" t="n"/>
+      <c r="E211" s="5" t="n"/>
+      <c r="F211" s="7" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="n"/>
+      <c r="B212" s="5" t="n"/>
+      <c r="C212" s="5" t="n"/>
+      <c r="D212" s="5" t="n"/>
+      <c r="E212" s="5" t="n"/>
+      <c r="F212" s="7" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="n"/>
+      <c r="B213" s="5" t="n"/>
+      <c r="C213" s="5" t="n"/>
+      <c r="D213" s="5" t="n"/>
+      <c r="E213" s="5" t="n"/>
+      <c r="F213" s="7" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="n"/>
+      <c r="B214" s="5" t="n"/>
+      <c r="C214" s="5" t="n"/>
+      <c r="D214" s="5" t="n"/>
+      <c r="E214" s="5" t="n"/>
+      <c r="F214" s="7" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="n"/>
+      <c r="B215" s="5" t="n"/>
+      <c r="C215" s="5" t="n"/>
+      <c r="D215" s="5" t="n"/>
+      <c r="E215" s="5" t="n"/>
+      <c r="F215" s="7" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="n"/>
+      <c r="B216" s="5" t="n"/>
+      <c r="C216" s="5" t="n"/>
+      <c r="D216" s="5" t="n"/>
+      <c r="E216" s="5" t="n"/>
+      <c r="F216" s="7" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="n"/>
+      <c r="B217" s="5" t="n"/>
+      <c r="C217" s="5" t="n"/>
+      <c r="D217" s="5" t="n"/>
+      <c r="E217" s="5" t="n"/>
+      <c r="F217" s="7" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="n"/>
+      <c r="B218" s="5" t="n"/>
+      <c r="C218" s="5" t="n"/>
+      <c r="D218" s="5" t="n"/>
+      <c r="E218" s="5" t="n"/>
+      <c r="F218" s="7" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="n"/>
+      <c r="B219" s="5" t="n"/>
+      <c r="C219" s="5" t="n"/>
+      <c r="D219" s="5" t="n"/>
+      <c r="E219" s="5" t="n"/>
+      <c r="F219" s="7" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="n"/>
+      <c r="B220" s="5" t="n"/>
+      <c r="C220" s="5" t="n"/>
+      <c r="D220" s="5" t="n"/>
+      <c r="E220" s="5" t="n"/>
+      <c r="F220" s="7" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="n"/>
+      <c r="B221" s="5" t="n"/>
+      <c r="C221" s="5" t="n"/>
+      <c r="D221" s="5" t="n"/>
+      <c r="E221" s="5" t="n"/>
+      <c r="F221" s="7" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="n"/>
+      <c r="B222" s="5" t="n"/>
+      <c r="C222" s="5" t="n"/>
+      <c r="D222" s="5" t="n"/>
+      <c r="E222" s="5" t="n"/>
+      <c r="F222" s="7" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="n"/>
+      <c r="B223" s="5" t="n"/>
+      <c r="C223" s="5" t="n"/>
+      <c r="D223" s="5" t="n"/>
+      <c r="E223" s="5" t="n"/>
+      <c r="F223" s="7" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="n"/>
+      <c r="B224" s="5" t="n"/>
+      <c r="C224" s="5" t="n"/>
+      <c r="D224" s="5" t="n"/>
+      <c r="E224" s="5" t="n"/>
+      <c r="F224" s="7" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="n"/>
+      <c r="B225" s="5" t="n"/>
+      <c r="C225" s="5" t="n"/>
+      <c r="D225" s="5" t="n"/>
+      <c r="E225" s="5" t="n"/>
+      <c r="F225" s="7" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="n"/>
+      <c r="B226" s="5" t="n"/>
+      <c r="C226" s="5" t="n"/>
+      <c r="D226" s="5" t="n"/>
+      <c r="E226" s="5" t="n"/>
+      <c r="F226" s="7" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="n"/>
+      <c r="B227" s="5" t="n"/>
+      <c r="C227" s="5" t="n"/>
+      <c r="D227" s="5" t="n"/>
+      <c r="E227" s="5" t="n"/>
+      <c r="F227" s="7" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="n"/>
+      <c r="B228" s="5" t="n"/>
+      <c r="C228" s="5" t="n"/>
+      <c r="D228" s="5" t="n"/>
+      <c r="E228" s="5" t="n"/>
+      <c r="F228" s="7" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="n"/>
+      <c r="B229" s="5" t="n"/>
+      <c r="C229" s="5" t="n"/>
+      <c r="D229" s="5" t="n"/>
+      <c r="E229" s="5" t="n"/>
+      <c r="F229" s="7" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="5" t="n"/>
+      <c r="B230" s="5" t="n"/>
+      <c r="C230" s="5" t="n"/>
+      <c r="D230" s="5" t="n"/>
+      <c r="E230" s="5" t="n"/>
+      <c r="F230" s="7" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="n"/>
+      <c r="B231" s="5" t="n"/>
+      <c r="C231" s="5" t="n"/>
+      <c r="D231" s="5" t="n"/>
+      <c r="E231" s="5" t="n"/>
+      <c r="F231" s="7" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="n"/>
+      <c r="B232" s="5" t="n"/>
+      <c r="C232" s="5" t="n"/>
+      <c r="D232" s="5" t="n"/>
+      <c r="E232" s="5" t="n"/>
+      <c r="F232" s="7" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="n"/>
+      <c r="B233" s="5" t="n"/>
+      <c r="C233" s="5" t="n"/>
+      <c r="D233" s="5" t="n"/>
+      <c r="E233" s="5" t="n"/>
+      <c r="F233" s="7" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="5" t="n"/>
+      <c r="B234" s="5" t="n"/>
+      <c r="C234" s="5" t="n"/>
+      <c r="D234" s="5" t="n"/>
+      <c r="E234" s="5" t="n"/>
+      <c r="F234" s="7" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="n"/>
+      <c r="B235" s="5" t="n"/>
+      <c r="C235" s="5" t="n"/>
+      <c r="D235" s="5" t="n"/>
+      <c r="E235" s="5" t="n"/>
+      <c r="F235" s="7" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="n"/>
+      <c r="B236" s="5" t="n"/>
+      <c r="C236" s="5" t="n"/>
+      <c r="D236" s="5" t="n"/>
+      <c r="E236" s="5" t="n"/>
+      <c r="F236" s="7" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="n"/>
+      <c r="B237" s="5" t="n"/>
+      <c r="C237" s="5" t="n"/>
+      <c r="D237" s="5" t="n"/>
+      <c r="E237" s="5" t="n"/>
+      <c r="F237" s="7" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="n"/>
+      <c r="B238" s="5" t="n"/>
+      <c r="C238" s="5" t="n"/>
+      <c r="D238" s="5" t="n"/>
+      <c r="E238" s="5" t="n"/>
+      <c r="F238" s="7" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="n"/>
+      <c r="B239" s="5" t="n"/>
+      <c r="C239" s="5" t="n"/>
+      <c r="D239" s="5" t="n"/>
+      <c r="E239" s="5" t="n"/>
+      <c r="F239" s="7" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="n"/>
+      <c r="B240" s="5" t="n"/>
+      <c r="C240" s="5" t="n"/>
+      <c r="D240" s="5" t="n"/>
+      <c r="E240" s="5" t="n"/>
+      <c r="F240" s="7" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="5" t="n"/>
+      <c r="B241" s="5" t="n"/>
+      <c r="C241" s="5" t="n"/>
+      <c r="D241" s="5" t="n"/>
+      <c r="E241" s="5" t="n"/>
+      <c r="F241" s="7" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="5" t="n"/>
+      <c r="B242" s="5" t="n"/>
+      <c r="C242" s="5" t="n"/>
+      <c r="D242" s="5" t="n"/>
+      <c r="E242" s="5" t="n"/>
+      <c r="F242" s="7" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="n"/>
+      <c r="B243" s="5" t="n"/>
+      <c r="C243" s="5" t="n"/>
+      <c r="D243" s="5" t="n"/>
+      <c r="E243" s="5" t="n"/>
+      <c r="F243" s="7" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="n"/>
+      <c r="B244" s="5" t="n"/>
+      <c r="C244" s="5" t="n"/>
+      <c r="D244" s="5" t="n"/>
+      <c r="E244" s="5" t="n"/>
+      <c r="F244" s="7" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="n"/>
+      <c r="B245" s="5" t="n"/>
+      <c r="C245" s="5" t="n"/>
+      <c r="D245" s="5" t="n"/>
+      <c r="E245" s="5" t="n"/>
+      <c r="F245" s="7" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="n"/>
+      <c r="B246" s="5" t="n"/>
+      <c r="C246" s="5" t="n"/>
+      <c r="D246" s="5" t="n"/>
+      <c r="E246" s="5" t="n"/>
+      <c r="F246" s="7" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="5" t="n"/>
+      <c r="B247" s="5" t="n"/>
+      <c r="C247" s="5" t="n"/>
+      <c r="D247" s="5" t="n"/>
+      <c r="E247" s="5" t="n"/>
+      <c r="F247" s="7" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="5" t="n"/>
+      <c r="B248" s="5" t="n"/>
+      <c r="C248" s="5" t="n"/>
+      <c r="D248" s="5" t="n"/>
+      <c r="E248" s="5" t="n"/>
+      <c r="F248" s="7" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="n"/>
+      <c r="B249" s="5" t="n"/>
+      <c r="C249" s="5" t="n"/>
+      <c r="D249" s="5" t="n"/>
+      <c r="E249" s="5" t="n"/>
+      <c r="F249" s="7" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="5" t="n"/>
+      <c r="B250" s="5" t="n"/>
+      <c r="C250" s="5" t="n"/>
+      <c r="D250" s="5" t="n"/>
+      <c r="E250" s="5" t="n"/>
+      <c r="F250" s="7" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="n"/>
+      <c r="B251" s="5" t="n"/>
+      <c r="C251" s="5" t="n"/>
+      <c r="D251" s="5" t="n"/>
+      <c r="E251" s="5" t="n"/>
+      <c r="F251" s="7" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="5" t="n"/>
+      <c r="B252" s="5" t="n"/>
+      <c r="C252" s="5" t="n"/>
+      <c r="D252" s="5" t="n"/>
+      <c r="E252" s="5" t="n"/>
+      <c r="F252" s="7" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="n"/>
+      <c r="B253" s="5" t="n"/>
+      <c r="C253" s="5" t="n"/>
+      <c r="D253" s="5" t="n"/>
+      <c r="E253" s="5" t="n"/>
+      <c r="F253" s="7" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="5" t="n"/>
+      <c r="B254" s="5" t="n"/>
+      <c r="C254" s="5" t="n"/>
+      <c r="D254" s="5" t="n"/>
+      <c r="E254" s="5" t="n"/>
+      <c r="F254" s="7" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="n"/>
+      <c r="B255" s="5" t="n"/>
+      <c r="C255" s="5" t="n"/>
+      <c r="D255" s="5" t="n"/>
+      <c r="E255" s="5" t="n"/>
+      <c r="F255" s="7" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="5" t="n"/>
+      <c r="B256" s="5" t="n"/>
+      <c r="C256" s="5" t="n"/>
+      <c r="D256" s="5" t="n"/>
+      <c r="E256" s="5" t="n"/>
+      <c r="F256" s="7" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="n"/>
+      <c r="B257" s="5" t="n"/>
+      <c r="C257" s="5" t="n"/>
+      <c r="D257" s="5" t="n"/>
+      <c r="E257" s="5" t="n"/>
+      <c r="F257" s="7" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="5" t="n"/>
+      <c r="B258" s="5" t="n"/>
+      <c r="C258" s="5" t="n"/>
+      <c r="D258" s="5" t="n"/>
+      <c r="E258" s="5" t="n"/>
+      <c r="F258" s="7" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="n"/>
+      <c r="B259" s="5" t="n"/>
+      <c r="C259" s="5" t="n"/>
+      <c r="D259" s="5" t="n"/>
+      <c r="E259" s="5" t="n"/>
+      <c r="F259" s="7" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="n"/>
+      <c r="B260" s="5" t="n"/>
+      <c r="C260" s="5" t="n"/>
+      <c r="D260" s="5" t="n"/>
+      <c r="E260" s="5" t="n"/>
+      <c r="F260" s="7" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="n"/>
+      <c r="B261" s="5" t="n"/>
+      <c r="C261" s="5" t="n"/>
+      <c r="D261" s="5" t="n"/>
+      <c r="E261" s="5" t="n"/>
+      <c r="F261" s="7" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="5" t="n"/>
+      <c r="B262" s="5" t="n"/>
+      <c r="C262" s="5" t="n"/>
+      <c r="D262" s="5" t="n"/>
+      <c r="E262" s="5" t="n"/>
+      <c r="F262" s="7" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="n"/>
+      <c r="B263" s="5" t="n"/>
+      <c r="C263" s="5" t="n"/>
+      <c r="D263" s="5" t="n"/>
+      <c r="E263" s="5" t="n"/>
+      <c r="F263" s="7" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="5" t="n"/>
+      <c r="B264" s="5" t="n"/>
+      <c r="C264" s="5" t="n"/>
+      <c r="D264" s="5" t="n"/>
+      <c r="E264" s="5" t="n"/>
+      <c r="F264" s="7" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="n"/>
+      <c r="B265" s="5" t="n"/>
+      <c r="C265" s="5" t="n"/>
+      <c r="D265" s="5" t="n"/>
+      <c r="E265" s="5" t="n"/>
+      <c r="F265" s="7" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="5" t="n"/>
+      <c r="B266" s="5" t="n"/>
+      <c r="C266" s="5" t="n"/>
+      <c r="D266" s="5" t="n"/>
+      <c r="E266" s="5" t="n"/>
+      <c r="F266" s="7" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="n"/>
+      <c r="B267" s="5" t="n"/>
+      <c r="C267" s="5" t="n"/>
+      <c r="D267" s="5" t="n"/>
+      <c r="E267" s="5" t="n"/>
+      <c r="F267" s="7" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="5" t="n"/>
+      <c r="B268" s="5" t="n"/>
+      <c r="C268" s="5" t="n"/>
+      <c r="D268" s="5" t="n"/>
+      <c r="E268" s="5" t="n"/>
+      <c r="F268" s="7" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="n"/>
+      <c r="B269" s="5" t="n"/>
+      <c r="C269" s="5" t="n"/>
+      <c r="D269" s="5" t="n"/>
+      <c r="E269" s="5" t="n"/>
+      <c r="F269" s="7" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="5" t="n"/>
+      <c r="B270" s="5" t="n"/>
+      <c r="C270" s="5" t="n"/>
+      <c r="D270" s="5" t="n"/>
+      <c r="E270" s="5" t="n"/>
+      <c r="F270" s="7" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="n"/>
+      <c r="B271" s="5" t="n"/>
+      <c r="C271" s="5" t="n"/>
+      <c r="D271" s="5" t="n"/>
+      <c r="E271" s="5" t="n"/>
+      <c r="F271" s="7" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="5" t="n"/>
+      <c r="B272" s="5" t="n"/>
+      <c r="C272" s="5" t="n"/>
+      <c r="D272" s="5" t="n"/>
+      <c r="E272" s="5" t="n"/>
+      <c r="F272" s="7" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="n"/>
+      <c r="B273" s="5" t="n"/>
+      <c r="C273" s="5" t="n"/>
+      <c r="D273" s="5" t="n"/>
+      <c r="E273" s="5" t="n"/>
+      <c r="F273" s="7" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="5" t="n"/>
+      <c r="B274" s="5" t="n"/>
+      <c r="C274" s="5" t="n"/>
+      <c r="D274" s="5" t="n"/>
+      <c r="E274" s="5" t="n"/>
+      <c r="F274" s="7" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="n"/>
+      <c r="B275" s="5" t="n"/>
+      <c r="C275" s="5" t="n"/>
+      <c r="D275" s="5" t="n"/>
+      <c r="E275" s="5" t="n"/>
+      <c r="F275" s="7" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="5" t="n"/>
+      <c r="B276" s="5" t="n"/>
+      <c r="C276" s="5" t="n"/>
+      <c r="D276" s="5" t="n"/>
+      <c r="E276" s="5" t="n"/>
+      <c r="F276" s="7" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="n"/>
+      <c r="B277" s="5" t="n"/>
+      <c r="C277" s="5" t="n"/>
+      <c r="D277" s="5" t="n"/>
+      <c r="E277" s="5" t="n"/>
+      <c r="F277" s="7" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="5" t="n"/>
+      <c r="B278" s="5" t="n"/>
+      <c r="C278" s="5" t="n"/>
+      <c r="D278" s="5" t="n"/>
+      <c r="E278" s="5" t="n"/>
+      <c r="F278" s="7" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="n"/>
+      <c r="B279" s="5" t="n"/>
+      <c r="C279" s="5" t="n"/>
+      <c r="D279" s="5" t="n"/>
+      <c r="E279" s="5" t="n"/>
+      <c r="F279" s="7" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="5" t="n"/>
+      <c r="B280" s="5" t="n"/>
+      <c r="C280" s="5" t="n"/>
+      <c r="D280" s="5" t="n"/>
+      <c r="E280" s="5" t="n"/>
+      <c r="F280" s="7" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="n"/>
+      <c r="B281" s="5" t="n"/>
+      <c r="C281" s="5" t="n"/>
+      <c r="D281" s="5" t="n"/>
+      <c r="E281" s="5" t="n"/>
+      <c r="F281" s="7" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="5" t="n"/>
+      <c r="B282" s="5" t="n"/>
+      <c r="C282" s="5" t="n"/>
+      <c r="D282" s="5" t="n"/>
+      <c r="E282" s="5" t="n"/>
+      <c r="F282" s="7" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="n"/>
+      <c r="B283" s="5" t="n"/>
+      <c r="C283" s="5" t="n"/>
+      <c r="D283" s="5" t="n"/>
+      <c r="E283" s="5" t="n"/>
+      <c r="F283" s="7" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="5" t="n"/>
+      <c r="B284" s="5" t="n"/>
+      <c r="C284" s="5" t="n"/>
+      <c r="D284" s="5" t="n"/>
+      <c r="E284" s="5" t="n"/>
+      <c r="F284" s="7" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="n"/>
+      <c r="B285" s="5" t="n"/>
+      <c r="C285" s="5" t="n"/>
+      <c r="D285" s="5" t="n"/>
+      <c r="E285" s="5" t="n"/>
+      <c r="F285" s="7" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="5" t="n"/>
+      <c r="B286" s="5" t="n"/>
+      <c r="C286" s="5" t="n"/>
+      <c r="D286" s="5" t="n"/>
+      <c r="E286" s="5" t="n"/>
+      <c r="F286" s="7" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="n"/>
+      <c r="B287" s="5" t="n"/>
+      <c r="C287" s="5" t="n"/>
+      <c r="D287" s="5" t="n"/>
+      <c r="E287" s="5" t="n"/>
+      <c r="F287" s="7" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="5" t="n"/>
+      <c r="B288" s="5" t="n"/>
+      <c r="C288" s="5" t="n"/>
+      <c r="D288" s="5" t="n"/>
+      <c r="E288" s="5" t="n"/>
+      <c r="F288" s="7" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="n"/>
+      <c r="B289" s="5" t="n"/>
+      <c r="C289" s="5" t="n"/>
+      <c r="D289" s="5" t="n"/>
+      <c r="E289" s="5" t="n"/>
+      <c r="F289" s="7" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="5" t="n"/>
+      <c r="B290" s="5" t="n"/>
+      <c r="C290" s="5" t="n"/>
+      <c r="D290" s="5" t="n"/>
+      <c r="E290" s="5" t="n"/>
+      <c r="F290" s="7" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="n"/>
+      <c r="B291" s="5" t="n"/>
+      <c r="C291" s="5" t="n"/>
+      <c r="D291" s="5" t="n"/>
+      <c r="E291" s="5" t="n"/>
+      <c r="F291" s="7" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="5" t="n"/>
+      <c r="B292" s="5" t="n"/>
+      <c r="C292" s="5" t="n"/>
+      <c r="D292" s="5" t="n"/>
+      <c r="E292" s="5" t="n"/>
+      <c r="F292" s="7" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="n"/>
+      <c r="B293" s="5" t="n"/>
+      <c r="C293" s="5" t="n"/>
+      <c r="D293" s="5" t="n"/>
+      <c r="E293" s="5" t="n"/>
+      <c r="F293" s="7" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="5" t="n"/>
+      <c r="B294" s="5" t="n"/>
+      <c r="C294" s="5" t="n"/>
+      <c r="D294" s="5" t="n"/>
+      <c r="E294" s="5" t="n"/>
+      <c r="F294" s="7" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="n"/>
+      <c r="B295" s="5" t="n"/>
+      <c r="C295" s="5" t="n"/>
+      <c r="D295" s="5" t="n"/>
+      <c r="E295" s="5" t="n"/>
+      <c r="F295" s="7" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="5" t="n"/>
+      <c r="B296" s="5" t="n"/>
+      <c r="C296" s="5" t="n"/>
+      <c r="D296" s="5" t="n"/>
+      <c r="E296" s="5" t="n"/>
+      <c r="F296" s="7" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="n"/>
+      <c r="B297" s="5" t="n"/>
+      <c r="C297" s="5" t="n"/>
+      <c r="D297" s="5" t="n"/>
+      <c r="E297" s="5" t="n"/>
+      <c r="F297" s="7" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="5" t="n"/>
+      <c r="B298" s="5" t="n"/>
+      <c r="C298" s="5" t="n"/>
+      <c r="D298" s="5" t="n"/>
+      <c r="E298" s="5" t="n"/>
+      <c r="F298" s="7" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="n"/>
+      <c r="B299" s="5" t="n"/>
+      <c r="C299" s="5" t="n"/>
+      <c r="D299" s="5" t="n"/>
+      <c r="E299" s="5" t="n"/>
+      <c r="F299" s="7" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="5" t="n"/>
+      <c r="B300" s="5" t="n"/>
+      <c r="C300" s="5" t="n"/>
+      <c r="D300" s="5" t="n"/>
+      <c r="E300" s="5" t="n"/>
+      <c r="F300" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>